--- a/МО 19.10.2026/Шаблон ЛМК проф ОПО — Машково и Руднево (ред. 19.10.2026).xlsx
+++ b/МО 19.10.2026/Шаблон ЛМК проф ОПО — Машково и Руднево (ред. 19.10.2026).xlsx
@@ -2353,31 +2353,31 @@
     <row r="19" ht="12.75" customHeight="1">
       <c r="A19" s="45" t="inlineStr">
         <is>
-          <t>Вавилин Артур Александрович</t>
+          <t>Ветлянский Александр Александрович</t>
         </is>
       </c>
       <c r="B19" s="46" t="inlineStr">
         <is>
-          <t>06.08.1984</t>
+          <t>22.04.1971</t>
         </is>
       </c>
       <c r="C19" s="47" t="n"/>
       <c r="D19" s="48" t="inlineStr">
         <is>
-          <t>107-160-314 08</t>
+          <t>068-669-037 17</t>
         </is>
       </c>
       <c r="E19" s="49" t="n"/>
       <c r="F19" s="50" t="n"/>
       <c r="G19" s="51" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H19" s="49" t="n"/>
       <c r="I19" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 3 разряда</t>
+          <t>Сборщик стеклопластиковых изделий 5 разряда</t>
         </is>
       </c>
       <c r="J19" s="52" t="inlineStr">
@@ -2437,31 +2437,31 @@
     <row r="20" ht="12.75" customHeight="1">
       <c r="A20" s="45" t="inlineStr">
         <is>
-          <t>Ветлянский Александр Александрович</t>
+          <t>Зайцев Андрей Александрович</t>
         </is>
       </c>
       <c r="B20" s="46" t="inlineStr">
         <is>
-          <t>22.04.1971</t>
+          <t>13.03.1987</t>
         </is>
       </c>
       <c r="C20" s="47" t="n"/>
       <c r="D20" s="48" t="inlineStr">
         <is>
-          <t>068-669-037 17</t>
+          <t>126-638-025 58</t>
         </is>
       </c>
       <c r="E20" s="49" t="n"/>
       <c r="F20" s="50" t="n"/>
       <c r="G20" s="51" t="inlineStr">
         <is>
-          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H20" s="49" t="n"/>
       <c r="I20" s="52" t="inlineStr">
         <is>
-          <t>Сборщик стеклопластиковых изделий 5 разряда</t>
+          <t>Облицовщик деталей мебели 3 разряда</t>
         </is>
       </c>
       <c r="J20" s="52" t="inlineStr">
@@ -2521,18 +2521,18 @@
     <row r="21" ht="12.75" customHeight="1">
       <c r="A21" s="45" t="inlineStr">
         <is>
-          <t>Зайцев Андрей Александрович</t>
+          <t>Захаров Юрий Викторович</t>
         </is>
       </c>
       <c r="B21" s="46" t="inlineStr">
         <is>
-          <t>13.03.1987</t>
+          <t>29.11.1978</t>
         </is>
       </c>
       <c r="C21" s="47" t="n"/>
       <c r="D21" s="48" t="inlineStr">
         <is>
-          <t>126-638-025 58</t>
+          <t>094-525-535 85</t>
         </is>
       </c>
       <c r="E21" s="49" t="n"/>
@@ -2545,7 +2545,7 @@
       <c r="H21" s="49" t="n"/>
       <c r="I21" s="52" t="inlineStr">
         <is>
-          <t>Облицовщик деталей мебели 3 разряда</t>
+          <t>Техник-сборщик 6 разряда</t>
         </is>
       </c>
       <c r="J21" s="52" t="inlineStr">
@@ -2605,18 +2605,18 @@
     <row r="22" ht="12.75" customHeight="1">
       <c r="A22" s="45" t="inlineStr">
         <is>
-          <t>Захаров Юрий Викторович</t>
+          <t>Кляцкин Антон Борисович</t>
         </is>
       </c>
       <c r="B22" s="46" t="inlineStr">
         <is>
-          <t>29.11.1978</t>
+          <t>23.04.1996</t>
         </is>
       </c>
       <c r="C22" s="47" t="n"/>
       <c r="D22" s="48" t="inlineStr">
         <is>
-          <t>094-525-535 85</t>
+          <t>185-050-199 62</t>
         </is>
       </c>
       <c r="E22" s="49" t="n"/>
@@ -2629,7 +2629,7 @@
       <c r="H22" s="49" t="n"/>
       <c r="I22" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 6 разряда</t>
+          <t>Техник-сборщик 3 разряда</t>
         </is>
       </c>
       <c r="J22" s="52" t="inlineStr">
@@ -2689,18 +2689,18 @@
     <row r="23" ht="12.75" customHeight="1">
       <c r="A23" s="45" t="inlineStr">
         <is>
-          <t>Кляцкин Антон Борисович</t>
+          <t>Кротков Александр Юрьевич</t>
         </is>
       </c>
       <c r="B23" s="46" t="inlineStr">
         <is>
-          <t>23.04.1996</t>
+          <t>26.12.1968</t>
         </is>
       </c>
       <c r="C23" s="47" t="n"/>
       <c r="D23" s="48" t="inlineStr">
         <is>
-          <t>185-050-199 62</t>
+          <t>015-826-776 65</t>
         </is>
       </c>
       <c r="E23" s="49" t="n"/>
@@ -2713,7 +2713,7 @@
       <c r="H23" s="49" t="n"/>
       <c r="I23" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 3 разряда</t>
+          <t>Столяр 4 разряда</t>
         </is>
       </c>
       <c r="J23" s="52" t="inlineStr">
@@ -2773,18 +2773,18 @@
     <row r="24" ht="12.75" customHeight="1">
       <c r="A24" s="45" t="inlineStr">
         <is>
-          <t>Котов Кирилл Олегович</t>
+          <t>Кукушкин Дмитрий Вячеславович</t>
         </is>
       </c>
       <c r="B24" s="46" t="inlineStr">
         <is>
-          <t>17.10.1982</t>
+          <t>17.07.1975</t>
         </is>
       </c>
       <c r="C24" s="47" t="n"/>
       <c r="D24" s="48" t="inlineStr">
         <is>
-          <t>138-621-610 58</t>
+          <t>124-975-726 92</t>
         </is>
       </c>
       <c r="E24" s="49" t="n"/>
@@ -2797,7 +2797,7 @@
       <c r="H24" s="49" t="n"/>
       <c r="I24" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 3 разряда</t>
+          <t>Техник-сборщик 4 разряда</t>
         </is>
       </c>
       <c r="J24" s="52" t="inlineStr">
@@ -2857,31 +2857,31 @@
     <row r="25" ht="12.75" customHeight="1">
       <c r="A25" s="45" t="inlineStr">
         <is>
-          <t>Кротков Александр Юрьевич</t>
+          <t>Кукушкин Максим Дмитриевич</t>
         </is>
       </c>
       <c r="B25" s="46" t="inlineStr">
         <is>
-          <t>26.12.1968</t>
+          <t>09.02.1998</t>
         </is>
       </c>
       <c r="C25" s="47" t="n"/>
       <c r="D25" s="48" t="inlineStr">
         <is>
-          <t>015-826-776 65</t>
+          <t>119-780-403 76</t>
         </is>
       </c>
       <c r="E25" s="49" t="n"/>
       <c r="F25" s="50" t="n"/>
       <c r="G25" s="51" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H25" s="49" t="n"/>
       <c r="I25" s="52" t="inlineStr">
         <is>
-          <t>Столяр 4 разряда</t>
+          <t>Сборщик стеклопластиковых изделий 3 разряда</t>
         </is>
       </c>
       <c r="J25" s="52" t="inlineStr">
@@ -2941,18 +2941,18 @@
     <row r="26" ht="12.75" customHeight="1">
       <c r="A26" s="45" t="inlineStr">
         <is>
-          <t>Кукушкин Дмитрий Вячеславович</t>
+          <t>Макарский Станислав Иванович</t>
         </is>
       </c>
       <c r="B26" s="46" t="inlineStr">
         <is>
-          <t>17.07.1975</t>
+          <t>09.02.1957</t>
         </is>
       </c>
       <c r="C26" s="47" t="n"/>
       <c r="D26" s="48" t="inlineStr">
         <is>
-          <t>124-975-726 92</t>
+          <t>022-469-805 48</t>
         </is>
       </c>
       <c r="E26" s="49" t="n"/>
@@ -2965,7 +2965,7 @@
       <c r="H26" s="49" t="n"/>
       <c r="I26" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 4 разряда</t>
+          <t>Техник-сборщик 5 разряда</t>
         </is>
       </c>
       <c r="J26" s="52" t="inlineStr">
@@ -3025,31 +3025,31 @@
     <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="45" t="inlineStr">
         <is>
-          <t>Кукушкин Максим Дмитриевич</t>
+          <t>Малышкин Сергей Константинович</t>
         </is>
       </c>
       <c r="B27" s="46" t="inlineStr">
         <is>
-          <t>09.02.1998</t>
+          <t>15.05.1974</t>
         </is>
       </c>
       <c r="C27" s="47" t="n"/>
       <c r="D27" s="48" t="inlineStr">
         <is>
-          <t>119-780-403 76</t>
+          <t>014-881-954 68</t>
         </is>
       </c>
       <c r="E27" s="49" t="n"/>
       <c r="F27" s="50" t="n"/>
       <c r="G27" s="51" t="inlineStr">
         <is>
-          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H27" s="49" t="n"/>
       <c r="I27" s="52" t="inlineStr">
         <is>
-          <t>Сборщик стеклопластиковых изделий 3 разряда</t>
+          <t>Техник-сборщик 6 разряда</t>
         </is>
       </c>
       <c r="J27" s="52" t="inlineStr">
@@ -3109,18 +3109,18 @@
     <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="45" t="inlineStr">
         <is>
-          <t>Макарский Станислав Иванович</t>
+          <t>Маркарян Роман Рубикович</t>
         </is>
       </c>
       <c r="B28" s="46" t="inlineStr">
         <is>
-          <t>09.02.1957</t>
+          <t>22.05.1976</t>
         </is>
       </c>
       <c r="C28" s="47" t="n"/>
       <c r="D28" s="48" t="inlineStr">
         <is>
-          <t>022-469-805 48</t>
+          <t>001-946-406 22</t>
         </is>
       </c>
       <c r="E28" s="49" t="n"/>
@@ -3133,7 +3133,7 @@
       <c r="H28" s="49" t="n"/>
       <c r="I28" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 5 разряда</t>
+          <t>Техник-сборщик 6 разряда</t>
         </is>
       </c>
       <c r="J28" s="52" t="inlineStr">
@@ -3193,31 +3193,31 @@
     <row r="29" ht="12.75" customHeight="1">
       <c r="A29" s="45" t="inlineStr">
         <is>
-          <t>Малышкин Сергей Константинович</t>
+          <t>Матухно Константин Викторович</t>
         </is>
       </c>
       <c r="B29" s="46" t="inlineStr">
         <is>
-          <t>15.05.1974</t>
+          <t>07.07.1976</t>
         </is>
       </c>
       <c r="C29" s="47" t="n"/>
       <c r="D29" s="48" t="inlineStr">
         <is>
-          <t>014-881-954 68</t>
+          <t>193-398-956 38</t>
         </is>
       </c>
       <c r="E29" s="49" t="n"/>
       <c r="F29" s="50" t="n"/>
       <c r="G29" s="51" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.4, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="H29" s="49" t="n"/>
       <c r="I29" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 6 разряда</t>
+          <t>Бригадир</t>
         </is>
       </c>
       <c r="J29" s="52" t="inlineStr">
@@ -3277,18 +3277,18 @@
     <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="45" t="inlineStr">
         <is>
-          <t>Маркарян Роман Рубикович</t>
+          <t>Михиенков Валерий Евгеньевич</t>
         </is>
       </c>
       <c r="B30" s="46" t="inlineStr">
         <is>
-          <t>22.05.1976</t>
+          <t>28.10.1973</t>
         </is>
       </c>
       <c r="C30" s="47" t="n"/>
       <c r="D30" s="48" t="inlineStr">
         <is>
-          <t>001-946-406 22</t>
+          <t>001-024-618 61</t>
         </is>
       </c>
       <c r="E30" s="49" t="n"/>
@@ -3301,7 +3301,7 @@
       <c r="H30" s="49" t="n"/>
       <c r="I30" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 6 разряда</t>
+          <t>Техник-сборщик 4 разряда</t>
         </is>
       </c>
       <c r="J30" s="52" t="inlineStr">
@@ -3361,31 +3361,31 @@
     <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="45" t="inlineStr">
         <is>
-          <t>Матухно Константин Викторович</t>
+          <t>Морозов Олег Валерьевич</t>
         </is>
       </c>
       <c r="B31" s="46" t="inlineStr">
         <is>
-          <t>07.07.1976</t>
+          <t>02.10.1974</t>
         </is>
       </c>
       <c r="C31" s="47" t="n"/>
       <c r="D31" s="48" t="inlineStr">
         <is>
-          <t>193-398-956 38</t>
+          <t>005-308-630 08</t>
         </is>
       </c>
       <c r="E31" s="49" t="n"/>
       <c r="F31" s="50" t="n"/>
       <c r="G31" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="H31" s="49" t="n"/>
       <c r="I31" s="52" t="inlineStr">
         <is>
-          <t>Бригадир</t>
+          <t>Оператор станков с ЧПУ 4 разряда</t>
         </is>
       </c>
       <c r="J31" s="52" t="inlineStr">
@@ -3445,18 +3445,18 @@
     <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="45" t="inlineStr">
         <is>
-          <t>Михиенков Валерий Евгеньевич</t>
+          <t>Мураев Вадим Викторович</t>
         </is>
       </c>
       <c r="B32" s="46" t="inlineStr">
         <is>
-          <t>28.10.1973</t>
+          <t>20.07.1983</t>
         </is>
       </c>
       <c r="C32" s="47" t="n"/>
       <c r="D32" s="48" t="inlineStr">
         <is>
-          <t>001-024-618 61</t>
+          <t>139-113-351 38</t>
         </is>
       </c>
       <c r="E32" s="49" t="n"/>
@@ -3469,7 +3469,7 @@
       <c r="H32" s="49" t="n"/>
       <c r="I32" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 4 разряда</t>
+          <t>Техник-сборщик 5 разряда</t>
         </is>
       </c>
       <c r="J32" s="52" t="inlineStr">
@@ -3529,31 +3529,31 @@
     <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="45" t="inlineStr">
         <is>
-          <t>Морозов Олег Валерьевич</t>
+          <t>Нерозников Роман Анатольевич</t>
         </is>
       </c>
       <c r="B33" s="46" t="inlineStr">
         <is>
-          <t>02.10.1974</t>
+          <t>08.06.1990</t>
         </is>
       </c>
       <c r="C33" s="47" t="n"/>
       <c r="D33" s="48" t="inlineStr">
         <is>
-          <t>005-308-630 08</t>
+          <t>136-604-917 62</t>
         </is>
       </c>
       <c r="E33" s="49" t="n"/>
       <c r="F33" s="50" t="n"/>
       <c r="G33" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.4.4, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="H33" s="49" t="n"/>
       <c r="I33" s="52" t="inlineStr">
         <is>
-          <t>Оператор станков с ЧПУ 4 разряда</t>
+          <t>Мастер участка</t>
         </is>
       </c>
       <c r="J33" s="52" t="inlineStr">
@@ -3613,31 +3613,31 @@
     <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="45" t="inlineStr">
         <is>
-          <t>Мураев Вадим Викторович</t>
+          <t>Никитин Валерий Сергеевич</t>
         </is>
       </c>
       <c r="B34" s="46" t="inlineStr">
         <is>
-          <t>20.07.1983</t>
+          <t>31.05.1983</t>
         </is>
       </c>
       <c r="C34" s="47" t="n"/>
       <c r="D34" s="48" t="inlineStr">
         <is>
-          <t>139-113-351 38</t>
+          <t>125-426-379 49</t>
         </is>
       </c>
       <c r="E34" s="49" t="n"/>
       <c r="F34" s="50" t="n"/>
       <c r="G34" s="51" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.4, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="H34" s="49" t="n"/>
       <c r="I34" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 5 разряда</t>
+          <t>Мастер участка</t>
         </is>
       </c>
       <c r="J34" s="52" t="inlineStr">
@@ -3697,31 +3697,31 @@
     <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="45" t="inlineStr">
         <is>
-          <t>Нерозников Роман Анатольевич</t>
+          <t>Пантюхов Вячеслав Владимирович</t>
         </is>
       </c>
       <c r="B35" s="46" t="inlineStr">
         <is>
-          <t>08.06.1990</t>
+          <t>25.03.1988</t>
         </is>
       </c>
       <c r="C35" s="47" t="n"/>
       <c r="D35" s="48" t="inlineStr">
         <is>
-          <t>136-604-917 62</t>
+          <t>210-350-970 09</t>
         </is>
       </c>
       <c r="E35" s="49" t="n"/>
       <c r="F35" s="50" t="n"/>
       <c r="G35" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H35" s="49" t="n"/>
       <c r="I35" s="52" t="inlineStr">
         <is>
-          <t>Мастер участка</t>
+          <t>Облицовщик деталей мебели 4 разряда</t>
         </is>
       </c>
       <c r="J35" s="52" t="inlineStr">
@@ -3781,31 +3781,31 @@
     <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="45" t="inlineStr">
         <is>
-          <t>Никитин Валерий Сергеевич</t>
+          <t>Петушков Дмитрий Сергеевич</t>
         </is>
       </c>
       <c r="B36" s="46" t="inlineStr">
         <is>
-          <t>31.05.1983</t>
+          <t>13.12.1972</t>
         </is>
       </c>
       <c r="C36" s="47" t="n"/>
       <c r="D36" s="48" t="inlineStr">
         <is>
-          <t>125-426-379 49</t>
+          <t>020-391-812 10</t>
         </is>
       </c>
       <c r="E36" s="49" t="n"/>
       <c r="F36" s="50" t="n"/>
       <c r="G36" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H36" s="49" t="n"/>
       <c r="I36" s="52" t="inlineStr">
         <is>
-          <t>Мастер участка</t>
+          <t>Техник-сборщик 4 разряда</t>
         </is>
       </c>
       <c r="J36" s="52" t="inlineStr">
@@ -3865,31 +3865,31 @@
     <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="45" t="inlineStr">
         <is>
-          <t>Пантюхов Вячеслав Владимирович</t>
+          <t>Пичугин Александр Владимирович</t>
         </is>
       </c>
       <c r="B37" s="46" t="inlineStr">
         <is>
-          <t>25.03.1988</t>
+          <t>01.06.1981</t>
         </is>
       </c>
       <c r="C37" s="47" t="n"/>
       <c r="D37" s="48" t="inlineStr">
         <is>
-          <t>210-350-970 09</t>
+          <t>083-981-603 02</t>
         </is>
       </c>
       <c r="E37" s="49" t="n"/>
       <c r="F37" s="50" t="n"/>
       <c r="G37" s="51" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H37" s="49" t="n"/>
       <c r="I37" s="52" t="inlineStr">
         <is>
-          <t>Облицовщик деталей мебели 4 разряда</t>
+          <t>Сборщик стеклопластиковых изделий 4 разряда</t>
         </is>
       </c>
       <c r="J37" s="52" t="inlineStr">
@@ -3949,18 +3949,18 @@
     <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="45" t="inlineStr">
         <is>
-          <t>Петушков Дмитрий Сергеевич</t>
+          <t>Полудкин Роман Владимирович</t>
         </is>
       </c>
       <c r="B38" s="46" t="inlineStr">
         <is>
-          <t>13.12.1972</t>
+          <t>26.10.1979</t>
         </is>
       </c>
       <c r="C38" s="47" t="n"/>
       <c r="D38" s="48" t="inlineStr">
         <is>
-          <t>020-391-812 10</t>
+          <t>144-132-917 33</t>
         </is>
       </c>
       <c r="E38" s="49" t="n"/>
@@ -4033,31 +4033,31 @@
     <row r="39" ht="12.75" customHeight="1">
       <c r="A39" s="45" t="inlineStr">
         <is>
-          <t>Пичугин Александр Владимирович</t>
+          <t>Рыжков Олег Николаевич</t>
         </is>
       </c>
       <c r="B39" s="46" t="inlineStr">
         <is>
-          <t>01.06.1981</t>
+          <t>16.07.1970</t>
         </is>
       </c>
       <c r="C39" s="47" t="n"/>
       <c r="D39" s="48" t="inlineStr">
         <is>
-          <t>083-981-603 02</t>
+          <t>005-503-166 98</t>
         </is>
       </c>
       <c r="E39" s="49" t="n"/>
       <c r="F39" s="50" t="n"/>
       <c r="G39" s="51" t="inlineStr">
         <is>
-          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H39" s="49" t="n"/>
       <c r="I39" s="52" t="inlineStr">
         <is>
-          <t>Сборщик стеклопластиковых изделий 4 разряда</t>
+          <t>Техник-сборщик 4 разряда</t>
         </is>
       </c>
       <c r="J39" s="52" t="inlineStr">
@@ -4117,18 +4117,18 @@
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="45" t="inlineStr">
         <is>
-          <t>Полудкин Роман Владимирович</t>
+          <t>Савельев Станислав Юрьевич</t>
         </is>
       </c>
       <c r="B40" s="46" t="inlineStr">
         <is>
-          <t>26.10.1979</t>
+          <t>29.12.1974</t>
         </is>
       </c>
       <c r="C40" s="47" t="n"/>
       <c r="D40" s="48" t="inlineStr">
         <is>
-          <t>144-132-917 33</t>
+          <t>010-143-907 80</t>
         </is>
       </c>
       <c r="E40" s="49" t="n"/>
@@ -4141,7 +4141,7 @@
       <c r="H40" s="49" t="n"/>
       <c r="I40" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 4 разряда</t>
+          <t>Техник-сборщик 6 разряда</t>
         </is>
       </c>
       <c r="J40" s="52" t="inlineStr">
@@ -4201,18 +4201,18 @@
     <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="45" t="inlineStr">
         <is>
-          <t>Рыжков Олег Николаевич</t>
+          <t>Селиванов Алексей Алексеевич</t>
         </is>
       </c>
       <c r="B41" s="46" t="inlineStr">
         <is>
-          <t>16.07.1970</t>
+          <t>03.06.1977</t>
         </is>
       </c>
       <c r="C41" s="47" t="n"/>
       <c r="D41" s="48" t="inlineStr">
         <is>
-          <t>005-503-166 98</t>
+          <t>001-946-559 38</t>
         </is>
       </c>
       <c r="E41" s="49" t="n"/>
@@ -4225,7 +4225,7 @@
       <c r="H41" s="49" t="n"/>
       <c r="I41" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 4 разряда</t>
+          <t>Техник-сборщик 6 разряда</t>
         </is>
       </c>
       <c r="J41" s="52" t="inlineStr">
@@ -4285,18 +4285,18 @@
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="45" t="inlineStr">
         <is>
-          <t>Савельев Станислав Юрьевич</t>
+          <t>Семенов Александр Александрович</t>
         </is>
       </c>
       <c r="B42" s="46" t="inlineStr">
         <is>
-          <t>29.12.1974</t>
+          <t>26.07.1990</t>
         </is>
       </c>
       <c r="C42" s="47" t="n"/>
       <c r="D42" s="48" t="inlineStr">
         <is>
-          <t>010-143-907 80</t>
+          <t>135-859-904 06</t>
         </is>
       </c>
       <c r="E42" s="49" t="n"/>
@@ -4309,7 +4309,7 @@
       <c r="H42" s="49" t="n"/>
       <c r="I42" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 6 разряда</t>
+          <t>Техник-сборщик 3 разряда</t>
         </is>
       </c>
       <c r="J42" s="52" t="inlineStr">
@@ -4369,18 +4369,18 @@
     <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="45" t="inlineStr">
         <is>
-          <t>Селиванов Алексей Алексеевич</t>
+          <t>Степанов Валентин Владимирович</t>
         </is>
       </c>
       <c r="B43" s="46" t="inlineStr">
         <is>
-          <t>03.06.1977</t>
+          <t>26.04.1979</t>
         </is>
       </c>
       <c r="C43" s="47" t="n"/>
       <c r="D43" s="48" t="inlineStr">
         <is>
-          <t>001-946-559 38</t>
+          <t>024-274-750 37</t>
         </is>
       </c>
       <c r="E43" s="49" t="n"/>
@@ -4393,7 +4393,7 @@
       <c r="H43" s="49" t="n"/>
       <c r="I43" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 6 разряда</t>
+          <t>Техник-сборщик 4 разряда</t>
         </is>
       </c>
       <c r="J43" s="52" t="inlineStr">
@@ -4453,31 +4453,31 @@
     <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="45" t="inlineStr">
         <is>
-          <t>Семенов Александр Александрович</t>
+          <t>Тимошенко Александр Олегович</t>
         </is>
       </c>
       <c r="B44" s="46" t="inlineStr">
         <is>
-          <t>26.07.1990</t>
+          <t>02.10.1972</t>
         </is>
       </c>
       <c r="C44" s="47" t="n"/>
       <c r="D44" s="48" t="inlineStr">
         <is>
-          <t>135-859-904 06</t>
+          <t>046-587-145 87</t>
         </is>
       </c>
       <c r="E44" s="49" t="n"/>
       <c r="F44" s="50" t="n"/>
       <c r="G44" s="51" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H44" s="49" t="n"/>
       <c r="I44" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 3 разряда</t>
+          <t>Сборщик стеклопластиковых изделий 4 разряда</t>
         </is>
       </c>
       <c r="J44" s="52" t="inlineStr">
@@ -4537,18 +4537,18 @@
     <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="45" t="inlineStr">
         <is>
-          <t>Степанов Валентин Владимирович</t>
+          <t>Трушков Сергей Викторович</t>
         </is>
       </c>
       <c r="B45" s="46" t="inlineStr">
         <is>
-          <t>26.04.1979</t>
+          <t>22.06.1963</t>
         </is>
       </c>
       <c r="C45" s="47" t="n"/>
       <c r="D45" s="48" t="inlineStr">
         <is>
-          <t>024-274-750 37</t>
+          <t>007-748-523 64</t>
         </is>
       </c>
       <c r="E45" s="49" t="n"/>
@@ -4561,7 +4561,7 @@
       <c r="H45" s="49" t="n"/>
       <c r="I45" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 4 разряда</t>
+          <t>Техник-сборщик 6 разряда</t>
         </is>
       </c>
       <c r="J45" s="52" t="inlineStr">
@@ -4621,31 +4621,31 @@
     <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="45" t="inlineStr">
         <is>
-          <t>Тимошенко Александр Олегович</t>
+          <t>Хасянов Ильфат Шамильевич</t>
         </is>
       </c>
       <c r="B46" s="46" t="inlineStr">
         <is>
-          <t>02.10.1972</t>
+          <t>06.11.1966</t>
         </is>
       </c>
       <c r="C46" s="47" t="n"/>
       <c r="D46" s="48" t="inlineStr">
         <is>
-          <t>046-587-145 87</t>
+          <t>136-335-182 48</t>
         </is>
       </c>
       <c r="E46" s="49" t="n"/>
       <c r="F46" s="50" t="n"/>
       <c r="G46" s="51" t="inlineStr">
         <is>
-          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="H46" s="49" t="n"/>
       <c r="I46" s="52" t="inlineStr">
         <is>
-          <t>Сборщик стеклопластиковых изделий 4 разряда</t>
+          <t>Оператор-наладчик станков с ЧПУ</t>
         </is>
       </c>
       <c r="J46" s="52" t="inlineStr">
@@ -4705,31 +4705,31 @@
     <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="45" t="inlineStr">
         <is>
-          <t>Трушков Сергей Викторович</t>
+          <t>Цибин Николай Дмитриевич</t>
         </is>
       </c>
       <c r="B47" s="46" t="inlineStr">
         <is>
-          <t>22.06.1963</t>
+          <t>27.03.1995</t>
         </is>
       </c>
       <c r="C47" s="47" t="n"/>
       <c r="D47" s="48" t="inlineStr">
         <is>
-          <t>007-748-523 64</t>
+          <t>194-624-665 04</t>
         </is>
       </c>
       <c r="E47" s="49" t="n"/>
       <c r="F47" s="50" t="n"/>
       <c r="G47" s="51" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.4, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="H47" s="49" t="n"/>
       <c r="I47" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 6 разряда</t>
+          <t>Бригадир</t>
         </is>
       </c>
       <c r="J47" s="52" t="inlineStr">
@@ -4789,31 +4789,31 @@
     <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="45" t="inlineStr">
         <is>
-          <t>Хасянов Ильфат Шамильевич</t>
+          <t>Черносвитов Дмитрий Львович</t>
         </is>
       </c>
       <c r="B48" s="46" t="inlineStr">
         <is>
-          <t>06.11.1966</t>
+          <t>04.04.1967</t>
         </is>
       </c>
       <c r="C48" s="47" t="n"/>
       <c r="D48" s="48" t="inlineStr">
         <is>
-          <t>136-335-182 48</t>
+          <t>007-748-524 65</t>
         </is>
       </c>
       <c r="E48" s="49" t="n"/>
       <c r="F48" s="50" t="n"/>
       <c r="G48" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H48" s="49" t="n"/>
       <c r="I48" s="52" t="inlineStr">
         <is>
-          <t>Оператор-наладчик станков с ЧПУ</t>
+          <t>Техник-сборщик 6 разряда</t>
         </is>
       </c>
       <c r="J48" s="52" t="inlineStr">
@@ -4873,31 +4873,31 @@
     <row r="49" ht="12.75" customHeight="1">
       <c r="A49" s="45" t="inlineStr">
         <is>
-          <t>Цибин Николай Дмитриевич</t>
+          <t>Шеин Андрей Геннадьевич</t>
         </is>
       </c>
       <c r="B49" s="46" t="inlineStr">
         <is>
-          <t>27.03.1995</t>
+          <t>05.11.1974</t>
         </is>
       </c>
       <c r="C49" s="47" t="n"/>
       <c r="D49" s="48" t="inlineStr">
         <is>
-          <t>194-624-665 04</t>
+          <t>221-741-613 29</t>
         </is>
       </c>
       <c r="E49" s="49" t="n"/>
       <c r="F49" s="50" t="n"/>
       <c r="G49" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H49" s="49" t="n"/>
       <c r="I49" s="52" t="inlineStr">
         <is>
-          <t>Бригадир</t>
+          <t>Техник-сборщик 4 разряда</t>
         </is>
       </c>
       <c r="J49" s="52" t="inlineStr">
@@ -4957,36 +4957,36 @@
     <row r="50" ht="12.75" customHeight="1">
       <c r="A50" s="45" t="inlineStr">
         <is>
-          <t>Черносвитов Дмитрий Львович</t>
+          <t>Агапов Максим Владимирович</t>
         </is>
       </c>
       <c r="B50" s="46" t="inlineStr">
         <is>
-          <t>04.04.1967</t>
+          <t>26.08.1978</t>
         </is>
       </c>
       <c r="C50" s="47" t="n"/>
       <c r="D50" s="48" t="inlineStr">
         <is>
-          <t>007-748-524 65</t>
+          <t>026-872-766 87</t>
         </is>
       </c>
       <c r="E50" s="49" t="n"/>
       <c r="F50" s="50" t="n"/>
       <c r="G50" s="51" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="H50" s="49" t="n"/>
       <c r="I50" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 6 разряда</t>
+          <t>Токарь 6 разряда</t>
         </is>
       </c>
       <c r="J50" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Механический участок МШ</t>
         </is>
       </c>
       <c r="K50" s="53" t="n"/>
@@ -5041,36 +5041,36 @@
     <row r="51" ht="12.75" customHeight="1">
       <c r="A51" s="45" t="inlineStr">
         <is>
-          <t>Шеин Андрей Геннадьевич</t>
+          <t>Артёмов Антон Анатольевич</t>
         </is>
       </c>
       <c r="B51" s="46" t="inlineStr">
         <is>
-          <t>05.11.1974</t>
+          <t>21.10.1993</t>
         </is>
       </c>
       <c r="C51" s="47" t="n"/>
       <c r="D51" s="48" t="inlineStr">
         <is>
-          <t>221-741-613 29</t>
+          <t>165-479-892 29</t>
         </is>
       </c>
       <c r="E51" s="49" t="n"/>
       <c r="F51" s="50" t="n"/>
       <c r="G51" s="51" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="H51" s="49" t="n"/>
       <c r="I51" s="52" t="inlineStr">
         <is>
-          <t>Техник-сборщик 4 разряда</t>
+          <t>Токарь 6 разряда</t>
         </is>
       </c>
       <c r="J51" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Механический участок МШ</t>
         </is>
       </c>
       <c r="K51" s="53" t="n"/>
@@ -5125,18 +5125,18 @@
     <row r="52" ht="12.75" customHeight="1">
       <c r="A52" s="45" t="inlineStr">
         <is>
-          <t>Агапов Максим Владимирович</t>
+          <t>Бондин Денис Игоревич</t>
         </is>
       </c>
       <c r="B52" s="46" t="inlineStr">
         <is>
-          <t>26.08.1978</t>
+          <t>14.03.1993</t>
         </is>
       </c>
       <c r="C52" s="47" t="n"/>
       <c r="D52" s="48" t="inlineStr">
         <is>
-          <t>026-872-766 87</t>
+          <t>140-734-085 34</t>
         </is>
       </c>
       <c r="E52" s="49" t="n"/>
@@ -5149,7 +5149,7 @@
       <c r="H52" s="49" t="n"/>
       <c r="I52" s="52" t="inlineStr">
         <is>
-          <t>Токарь 6 разряда</t>
+          <t>Оператор-наладчик станков с ЧПУ</t>
         </is>
       </c>
       <c r="J52" s="52" t="inlineStr">
@@ -5209,18 +5209,18 @@
     <row r="53" ht="12.75" customHeight="1">
       <c r="A53" s="45" t="inlineStr">
         <is>
-          <t>Артёмов Антон Анатольевич</t>
+          <t>Горелов Андрей Сергеевич</t>
         </is>
       </c>
       <c r="B53" s="46" t="inlineStr">
         <is>
-          <t>21.10.1993</t>
+          <t>05.06.1996</t>
         </is>
       </c>
       <c r="C53" s="47" t="n"/>
       <c r="D53" s="48" t="inlineStr">
         <is>
-          <t>165-479-892 29</t>
+          <t>167-946-540 25</t>
         </is>
       </c>
       <c r="E53" s="49" t="n"/>
@@ -5233,7 +5233,7 @@
       <c r="H53" s="49" t="n"/>
       <c r="I53" s="52" t="inlineStr">
         <is>
-          <t>Токарь 6 разряда</t>
+          <t>Оператор-наладчик станков с ЧПУ</t>
         </is>
       </c>
       <c r="J53" s="52" t="inlineStr">
@@ -5293,18 +5293,18 @@
     <row r="54" ht="12.75" customHeight="1">
       <c r="A54" s="45" t="inlineStr">
         <is>
-          <t>Бондин Денис Игоревич</t>
+          <t>Зинченко Денис Андреевич</t>
         </is>
       </c>
       <c r="B54" s="46" t="inlineStr">
         <is>
-          <t>14.03.1993</t>
+          <t>30.09.1996</t>
         </is>
       </c>
       <c r="C54" s="47" t="n"/>
       <c r="D54" s="48" t="inlineStr">
         <is>
-          <t>140-734-085 34</t>
+          <t>188-742-387 29</t>
         </is>
       </c>
       <c r="E54" s="49" t="n"/>
@@ -5377,18 +5377,18 @@
     <row r="55" ht="12.75" customHeight="1">
       <c r="A55" s="45" t="inlineStr">
         <is>
-          <t>Горелов Андрей Сергеевич</t>
+          <t>Клюг Андрей Эдуардович</t>
         </is>
       </c>
       <c r="B55" s="46" t="inlineStr">
         <is>
-          <t>05.06.1996</t>
+          <t>05.04.1962</t>
         </is>
       </c>
       <c r="C55" s="47" t="n"/>
       <c r="D55" s="48" t="inlineStr">
         <is>
-          <t>167-946-540 25</t>
+          <t>001-549-740 21</t>
         </is>
       </c>
       <c r="E55" s="49" t="n"/>
@@ -5401,7 +5401,7 @@
       <c r="H55" s="49" t="n"/>
       <c r="I55" s="52" t="inlineStr">
         <is>
-          <t>Оператор-наладчик станков с ЧПУ</t>
+          <t>Фрезеровщик 5 разряда</t>
         </is>
       </c>
       <c r="J55" s="52" t="inlineStr">
@@ -5461,18 +5461,18 @@
     <row r="56" ht="12.75" customHeight="1">
       <c r="A56" s="45" t="inlineStr">
         <is>
-          <t>Зинченко Денис Андреевич</t>
+          <t>Кулешов Руслан Викторович</t>
         </is>
       </c>
       <c r="B56" s="46" t="inlineStr">
         <is>
-          <t>30.09.1996</t>
+          <t>07.02.1990</t>
         </is>
       </c>
       <c r="C56" s="47" t="n"/>
       <c r="D56" s="48" t="inlineStr">
         <is>
-          <t>188-742-387 29</t>
+          <t>157-905-167 93</t>
         </is>
       </c>
       <c r="E56" s="49" t="n"/>
@@ -5545,18 +5545,18 @@
     <row r="57" ht="12.75" customHeight="1">
       <c r="A57" s="45" t="inlineStr">
         <is>
-          <t>Клюг Андрей Эдуардович</t>
+          <t>Нагаев Дмитрий Александрович</t>
         </is>
       </c>
       <c r="B57" s="46" t="inlineStr">
         <is>
-          <t>05.04.1962</t>
+          <t>16.02.1991</t>
         </is>
       </c>
       <c r="C57" s="47" t="n"/>
       <c r="D57" s="48" t="inlineStr">
         <is>
-          <t>001-549-740 21</t>
+          <t>149-980-959 42</t>
         </is>
       </c>
       <c r="E57" s="49" t="n"/>
@@ -5569,7 +5569,7 @@
       <c r="H57" s="49" t="n"/>
       <c r="I57" s="52" t="inlineStr">
         <is>
-          <t>Фрезеровщик 5 разряда</t>
+          <t>Оператор-наладчик станков с ЧПУ</t>
         </is>
       </c>
       <c r="J57" s="52" t="inlineStr">
@@ -5629,18 +5629,18 @@
     <row r="58" ht="12.75" customHeight="1">
       <c r="A58" s="45" t="inlineStr">
         <is>
-          <t>Кулешов Руслан Викторович</t>
+          <t>Назин Владислав Сергеевич</t>
         </is>
       </c>
       <c r="B58" s="46" t="inlineStr">
         <is>
-          <t>07.02.1990</t>
+          <t>14.02.1997</t>
         </is>
       </c>
       <c r="C58" s="47" t="n"/>
       <c r="D58" s="48" t="inlineStr">
         <is>
-          <t>157-905-167 93</t>
+          <t>193-344-670 87</t>
         </is>
       </c>
       <c r="E58" s="49" t="n"/>
@@ -5653,7 +5653,7 @@
       <c r="H58" s="49" t="n"/>
       <c r="I58" s="52" t="inlineStr">
         <is>
-          <t>Оператор-наладчик станков с ЧПУ</t>
+          <t>Оператор станков с ЧПУ 5 разряда</t>
         </is>
       </c>
       <c r="J58" s="52" t="inlineStr">
@@ -5713,18 +5713,18 @@
     <row r="59" ht="12.75" customHeight="1">
       <c r="A59" s="45" t="inlineStr">
         <is>
-          <t>Нагаев Дмитрий Александрович</t>
+          <t>Орлов Михаил Юрьевич</t>
         </is>
       </c>
       <c r="B59" s="46" t="inlineStr">
         <is>
-          <t>16.02.1991</t>
+          <t>12.04.1987</t>
         </is>
       </c>
       <c r="C59" s="47" t="n"/>
       <c r="D59" s="48" t="inlineStr">
         <is>
-          <t>149-980-959 42</t>
+          <t>151-145-322 16</t>
         </is>
       </c>
       <c r="E59" s="49" t="n"/>
@@ -5737,7 +5737,7 @@
       <c r="H59" s="49" t="n"/>
       <c r="I59" s="52" t="inlineStr">
         <is>
-          <t>Оператор-наладчик станков с ЧПУ</t>
+          <t>Оператор станков с ЧПУ 5 разряда</t>
         </is>
       </c>
       <c r="J59" s="52" t="inlineStr">
@@ -5797,18 +5797,18 @@
     <row r="60" ht="12.75" customHeight="1">
       <c r="A60" s="45" t="inlineStr">
         <is>
-          <t>Назин Владислав Сергеевич</t>
+          <t>Потапкин Илья Анатольевич</t>
         </is>
       </c>
       <c r="B60" s="46" t="inlineStr">
         <is>
-          <t>14.02.1997</t>
+          <t>26.07.1995</t>
         </is>
       </c>
       <c r="C60" s="47" t="n"/>
       <c r="D60" s="48" t="inlineStr">
         <is>
-          <t>193-344-670 87</t>
+          <t>138-513-714 62</t>
         </is>
       </c>
       <c r="E60" s="49" t="n"/>
@@ -5821,7 +5821,7 @@
       <c r="H60" s="49" t="n"/>
       <c r="I60" s="52" t="inlineStr">
         <is>
-          <t>Оператор станков с ЧПУ 5 разряда</t>
+          <t>Токарь 6 разряда</t>
         </is>
       </c>
       <c r="J60" s="52" t="inlineStr">
@@ -5881,18 +5881,18 @@
     <row r="61" ht="12.75" customHeight="1">
       <c r="A61" s="45" t="inlineStr">
         <is>
-          <t>Орлов Михаил Юрьевич</t>
+          <t>Саранцев Петр Дмитриевич</t>
         </is>
       </c>
       <c r="B61" s="46" t="inlineStr">
         <is>
-          <t>12.04.1987</t>
+          <t>16.05.2001</t>
         </is>
       </c>
       <c r="C61" s="47" t="n"/>
       <c r="D61" s="48" t="inlineStr">
         <is>
-          <t>151-145-322 16</t>
+          <t>150-514-561 27</t>
         </is>
       </c>
       <c r="E61" s="49" t="n"/>
@@ -5905,7 +5905,7 @@
       <c r="H61" s="49" t="n"/>
       <c r="I61" s="52" t="inlineStr">
         <is>
-          <t>Оператор станков с ЧПУ 5 разряда</t>
+          <t>Токарь 5 разряда</t>
         </is>
       </c>
       <c r="J61" s="52" t="inlineStr">
@@ -5965,18 +5965,18 @@
     <row r="62" ht="12.75" customHeight="1">
       <c r="A62" s="45" t="inlineStr">
         <is>
-          <t>Потапкин Илья Анатольевич</t>
+          <t>Тарасов Борис Анатольевич</t>
         </is>
       </c>
       <c r="B62" s="46" t="inlineStr">
         <is>
-          <t>26.07.1995</t>
+          <t>20.04.1959</t>
         </is>
       </c>
       <c r="C62" s="47" t="n"/>
       <c r="D62" s="48" t="inlineStr">
         <is>
-          <t>138-513-714 62</t>
+          <t>013-505-131 89</t>
         </is>
       </c>
       <c r="E62" s="49" t="n"/>
@@ -5989,7 +5989,7 @@
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="52" t="inlineStr">
         <is>
-          <t>Токарь 6 разряда</t>
+          <t>Фрезеровщик 6 разряда</t>
         </is>
       </c>
       <c r="J62" s="52" t="inlineStr">
@@ -6049,31 +6049,31 @@
     <row r="63" ht="12.75" customHeight="1">
       <c r="A63" s="45" t="inlineStr">
         <is>
-          <t>Саранцев Петр Дмитриевич</t>
+          <t>Фокина Светлана Геннадиевна</t>
         </is>
       </c>
       <c r="B63" s="46" t="inlineStr">
         <is>
-          <t>16.05.2001</t>
+          <t>18.10.1975</t>
         </is>
       </c>
       <c r="C63" s="47" t="n"/>
       <c r="D63" s="48" t="inlineStr">
         <is>
-          <t>150-514-561 27</t>
+          <t>108-330-307 13</t>
         </is>
       </c>
       <c r="E63" s="49" t="n"/>
       <c r="F63" s="50" t="n"/>
       <c r="G63" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.4.4, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="H63" s="49" t="n"/>
       <c r="I63" s="52" t="inlineStr">
         <is>
-          <t>Токарь 5 разряда</t>
+          <t>Мастер участка</t>
         </is>
       </c>
       <c r="J63" s="52" t="inlineStr">
@@ -6133,18 +6133,18 @@
     <row r="64" ht="12.75" customHeight="1">
       <c r="A64" s="45" t="inlineStr">
         <is>
-          <t>Тарасов Борис Анатольевич</t>
+          <t>Юдаков Алексей Викторович</t>
         </is>
       </c>
       <c r="B64" s="46" t="inlineStr">
         <is>
-          <t>20.04.1959</t>
+          <t>26.03.1980</t>
         </is>
       </c>
       <c r="C64" s="47" t="n"/>
       <c r="D64" s="48" t="inlineStr">
         <is>
-          <t>013-505-131 89</t>
+          <t>043-924-645 63</t>
         </is>
       </c>
       <c r="E64" s="49" t="n"/>
@@ -6157,7 +6157,7 @@
       <c r="H64" s="49" t="n"/>
       <c r="I64" s="52" t="inlineStr">
         <is>
-          <t>Фрезеровщик 6 разряда</t>
+          <t>Токарь 5 разряда</t>
         </is>
       </c>
       <c r="J64" s="52" t="inlineStr">
@@ -6217,36 +6217,36 @@
     <row r="65" ht="12.75" customHeight="1">
       <c r="A65" s="45" t="inlineStr">
         <is>
-          <t>Фокина Светлана Геннадиевна</t>
+          <t>Птицын Юрий Юрьевич</t>
         </is>
       </c>
       <c r="B65" s="46" t="inlineStr">
         <is>
-          <t>18.10.1975</t>
+          <t>26.01.1988</t>
         </is>
       </c>
       <c r="C65" s="47" t="n"/>
       <c r="D65" s="48" t="inlineStr">
         <is>
-          <t>108-330-307 13</t>
+          <t>128-866-839 20</t>
         </is>
       </c>
       <c r="E65" s="49" t="n"/>
       <c r="F65" s="50" t="n"/>
       <c r="G65" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="H65" s="49" t="n"/>
       <c r="I65" s="52" t="inlineStr">
         <is>
-          <t>Мастер участка</t>
+          <t>Оператор-наладчик станков с ЧПУ</t>
         </is>
       </c>
       <c r="J65" s="52" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Механический участок Р</t>
         </is>
       </c>
       <c r="K65" s="53" t="n"/>
@@ -6301,36 +6301,36 @@
     <row r="66" ht="12.75" customHeight="1">
       <c r="A66" s="45" t="inlineStr">
         <is>
-          <t>Юдаков Алексей Викторович</t>
+          <t>Беспалов Виталий Анатольевич</t>
         </is>
       </c>
       <c r="B66" s="46" t="inlineStr">
         <is>
-          <t>26.03.1980</t>
+          <t>07.09.1966</t>
         </is>
       </c>
       <c r="C66" s="47" t="n"/>
       <c r="D66" s="48" t="inlineStr">
         <is>
-          <t>043-924-645 63</t>
+          <t>018-261-947 51</t>
         </is>
       </c>
       <c r="E66" s="49" t="n"/>
       <c r="F66" s="50" t="n"/>
       <c r="G66" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.4.7, п.4.8, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="H66" s="49" t="n"/>
       <c r="I66" s="52" t="inlineStr">
         <is>
-          <t>Токарь 5 разряда</t>
+          <t>Контролер КПП</t>
         </is>
       </c>
       <c r="J66" s="52" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Отдел режима МШ</t>
         </is>
       </c>
       <c r="K66" s="53" t="n"/>
@@ -6385,36 +6385,36 @@
     <row r="67" ht="12.75" customHeight="1">
       <c r="A67" s="45" t="inlineStr">
         <is>
-          <t>Птицын Юрий Юрьевич</t>
+          <t>Волгин Анатолий Иванович</t>
         </is>
       </c>
       <c r="B67" s="46" t="inlineStr">
         <is>
-          <t>26.01.1988</t>
+          <t>14.11.1961</t>
         </is>
       </c>
       <c r="C67" s="47" t="n"/>
       <c r="D67" s="48" t="inlineStr">
         <is>
-          <t>128-866-839 20</t>
+          <t>119-885-518 11</t>
         </is>
       </c>
       <c r="E67" s="49" t="n"/>
       <c r="F67" s="50" t="n"/>
       <c r="G67" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.4.7, п.4.8, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="H67" s="49" t="n"/>
       <c r="I67" s="52" t="inlineStr">
         <is>
-          <t>Оператор-наладчик станков с ЧПУ</t>
+          <t>Контролер КПП</t>
         </is>
       </c>
       <c r="J67" s="52" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Отдел режима МШ</t>
         </is>
       </c>
       <c r="K67" s="53" t="n"/>
@@ -6469,18 +6469,18 @@
     <row r="68" ht="12.75" customHeight="1">
       <c r="A68" s="45" t="inlineStr">
         <is>
-          <t>Беспалов Виталий Анатольевич</t>
+          <t>Гусев Александр Николаевич</t>
         </is>
       </c>
       <c r="B68" s="46" t="inlineStr">
         <is>
-          <t>07.09.1966</t>
+          <t>28.01.1957</t>
         </is>
       </c>
       <c r="C68" s="47" t="n"/>
       <c r="D68" s="48" t="inlineStr">
         <is>
-          <t>018-261-947 51</t>
+          <t>095-183-086 86</t>
         </is>
       </c>
       <c r="E68" s="49" t="n"/>
@@ -6553,18 +6553,18 @@
     <row r="69" ht="12.75" customHeight="1">
       <c r="A69" s="45" t="inlineStr">
         <is>
-          <t>Волгин Анатолий Иванович</t>
+          <t>Дудукин Сергей Вячеславович</t>
         </is>
       </c>
       <c r="B69" s="46" t="inlineStr">
         <is>
-          <t>14.11.1961</t>
+          <t>08.06.1972</t>
         </is>
       </c>
       <c r="C69" s="47" t="n"/>
       <c r="D69" s="48" t="inlineStr">
         <is>
-          <t>119-885-518 11</t>
+          <t>058-429-200 71</t>
         </is>
       </c>
       <c r="E69" s="49" t="n"/>
@@ -6637,18 +6637,18 @@
     <row r="70" ht="12.75" customHeight="1">
       <c r="A70" s="45" t="inlineStr">
         <is>
-          <t>Гусев Александр Николаевич</t>
+          <t>Звягин Евгений Иванович</t>
         </is>
       </c>
       <c r="B70" s="46" t="inlineStr">
         <is>
-          <t>28.01.1957</t>
+          <t>01.05.1973</t>
         </is>
       </c>
       <c r="C70" s="47" t="n"/>
       <c r="D70" s="48" t="inlineStr">
         <is>
-          <t>095-183-086 86</t>
+          <t>036-392-199 66</t>
         </is>
       </c>
       <c r="E70" s="49" t="n"/>
@@ -6721,18 +6721,18 @@
     <row r="71" ht="12.75" customHeight="1">
       <c r="A71" s="45" t="inlineStr">
         <is>
-          <t>Дудукин Сергей Вячеславович</t>
+          <t>Камбулатов Эсенбулат Камбулатович</t>
         </is>
       </c>
       <c r="B71" s="46" t="inlineStr">
         <is>
-          <t>08.06.1972</t>
+          <t>17.04.1964</t>
         </is>
       </c>
       <c r="C71" s="47" t="n"/>
       <c r="D71" s="48" t="inlineStr">
         <is>
-          <t>058-429-200 71</t>
+          <t>116-987-951 17</t>
         </is>
       </c>
       <c r="E71" s="49" t="n"/>
@@ -6745,7 +6745,7 @@
       <c r="H71" s="49" t="n"/>
       <c r="I71" s="52" t="inlineStr">
         <is>
-          <t>Контролер КПП</t>
+          <t>Контролер КПП-старший смены</t>
         </is>
       </c>
       <c r="J71" s="52" t="inlineStr">
@@ -6805,18 +6805,18 @@
     <row r="72" ht="12.75" customHeight="1">
       <c r="A72" s="45" t="inlineStr">
         <is>
-          <t>Звягин Евгений Иванович</t>
+          <t>Макаренко Алексей Иванович</t>
         </is>
       </c>
       <c r="B72" s="46" t="inlineStr">
         <is>
-          <t>01.05.1973</t>
+          <t>15.05.1964</t>
         </is>
       </c>
       <c r="C72" s="47" t="n"/>
       <c r="D72" s="48" t="inlineStr">
         <is>
-          <t>036-392-199 66</t>
+          <t>065-048-140 45</t>
         </is>
       </c>
       <c r="E72" s="49" t="n"/>
@@ -6889,18 +6889,18 @@
     <row r="73" ht="12.75" customHeight="1">
       <c r="A73" s="45" t="inlineStr">
         <is>
-          <t>Камбулатов Эсенбулат Камбулатович</t>
+          <t>Матвицкий Виктор Владимирович</t>
         </is>
       </c>
       <c r="B73" s="46" t="inlineStr">
         <is>
-          <t>17.04.1964</t>
+          <t>22.09.1967</t>
         </is>
       </c>
       <c r="C73" s="47" t="n"/>
       <c r="D73" s="48" t="inlineStr">
         <is>
-          <t>116-987-951 17</t>
+          <t>142-240-380 11</t>
         </is>
       </c>
       <c r="E73" s="49" t="n"/>
@@ -6913,7 +6913,7 @@
       <c r="H73" s="49" t="n"/>
       <c r="I73" s="52" t="inlineStr">
         <is>
-          <t>Контролер КПП-старший смены</t>
+          <t>Контролер КПП</t>
         </is>
       </c>
       <c r="J73" s="52" t="inlineStr">
@@ -6973,18 +6973,18 @@
     <row r="74" ht="12.75" customHeight="1">
       <c r="A74" s="45" t="inlineStr">
         <is>
-          <t>Макаренко Алексей Иванович</t>
+          <t>Рукин Денис Игоревич</t>
         </is>
       </c>
       <c r="B74" s="46" t="inlineStr">
         <is>
-          <t>15.05.1964</t>
+          <t>23.03.1989</t>
         </is>
       </c>
       <c r="C74" s="47" t="n"/>
       <c r="D74" s="48" t="inlineStr">
         <is>
-          <t>065-048-140 45</t>
+          <t>145-858-529 07</t>
         </is>
       </c>
       <c r="E74" s="49" t="n"/>
@@ -6997,7 +6997,7 @@
       <c r="H74" s="49" t="n"/>
       <c r="I74" s="52" t="inlineStr">
         <is>
-          <t>Контролер КПП</t>
+          <t>Старший охраны объекта</t>
         </is>
       </c>
       <c r="J74" s="52" t="inlineStr">
@@ -7057,36 +7057,36 @@
     <row r="75" ht="12.75" customHeight="1">
       <c r="A75" s="45" t="inlineStr">
         <is>
-          <t>Матвицкий Виктор Владимирович</t>
+          <t>Ермакова Наталья Васильевна</t>
         </is>
       </c>
       <c r="B75" s="46" t="inlineStr">
         <is>
-          <t>22.09.1967</t>
+          <t>15.03.1983</t>
         </is>
       </c>
       <c r="C75" s="47" t="n"/>
       <c r="D75" s="48" t="inlineStr">
         <is>
-          <t>142-240-380 11</t>
+          <t>084-319-031 57</t>
         </is>
       </c>
       <c r="E75" s="49" t="n"/>
       <c r="F75" s="50" t="n"/>
       <c r="G75" s="51" t="inlineStr">
         <is>
-          <t>п.4.7, п.4.8, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="H75" s="49" t="n"/>
       <c r="I75" s="52" t="inlineStr">
         <is>
-          <t>Контролер КПП</t>
+          <t>Контролер 1 категории</t>
         </is>
       </c>
       <c r="J75" s="52" t="inlineStr">
         <is>
-          <t>Отдел режима МШ</t>
+          <t>Отдел технического контроля М</t>
         </is>
       </c>
       <c r="K75" s="53" t="n"/>
@@ -7141,36 +7141,36 @@
     <row r="76" ht="12.75" customHeight="1">
       <c r="A76" s="45" t="inlineStr">
         <is>
-          <t>Рукин Денис Игоревич</t>
+          <t>Шрамко Наталья Викторовна</t>
         </is>
       </c>
       <c r="B76" s="46" t="inlineStr">
         <is>
-          <t>23.03.1989</t>
+          <t>08.04.1980</t>
         </is>
       </c>
       <c r="C76" s="47" t="n"/>
       <c r="D76" s="48" t="inlineStr">
         <is>
-          <t>145-858-529 07</t>
+          <t>209-966-113 96</t>
         </is>
       </c>
       <c r="E76" s="49" t="n"/>
       <c r="F76" s="50" t="n"/>
       <c r="G76" s="51" t="inlineStr">
         <is>
-          <t>п.4.7, п.4.8, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="H76" s="49" t="n"/>
       <c r="I76" s="52" t="inlineStr">
         <is>
-          <t>Старший охраны объекта</t>
+          <t>Контролер 1 категории</t>
         </is>
       </c>
       <c r="J76" s="52" t="inlineStr">
         <is>
-          <t>Отдел режима МШ</t>
+          <t>Отдел технического контроля М</t>
         </is>
       </c>
       <c r="K76" s="53" t="n"/>
@@ -7225,18 +7225,18 @@
     <row r="77" ht="12.75" customHeight="1">
       <c r="A77" s="45" t="inlineStr">
         <is>
-          <t>Ермакова Наталья Васильевна</t>
+          <t>Ястребов Александр Сергеевич</t>
         </is>
       </c>
       <c r="B77" s="46" t="inlineStr">
         <is>
-          <t>15.03.1983</t>
+          <t>21.04.1985</t>
         </is>
       </c>
       <c r="C77" s="47" t="n"/>
       <c r="D77" s="48" t="inlineStr">
         <is>
-          <t>084-319-031 57</t>
+          <t>077-644-645 06</t>
         </is>
       </c>
       <c r="E77" s="49" t="n"/>
@@ -7249,7 +7249,7 @@
       <c r="H77" s="49" t="n"/>
       <c r="I77" s="52" t="inlineStr">
         <is>
-          <t>Контролер 1 категории</t>
+          <t>Инженер 1 категории</t>
         </is>
       </c>
       <c r="J77" s="52" t="inlineStr">
@@ -7309,18 +7309,18 @@
     <row r="78" ht="12.75" customHeight="1">
       <c r="A78" s="45" t="inlineStr">
         <is>
-          <t>Шрамко Наталья Викторовна</t>
+          <t>Божьева Ирина Вячеславовна</t>
         </is>
       </c>
       <c r="B78" s="46" t="inlineStr">
         <is>
-          <t>08.04.1980</t>
+          <t>14.09.1983</t>
         </is>
       </c>
       <c r="C78" s="47" t="n"/>
       <c r="D78" s="48" t="inlineStr">
         <is>
-          <t>209-966-113 96</t>
+          <t>125-706-271 46</t>
         </is>
       </c>
       <c r="E78" s="49" t="n"/>
@@ -7333,12 +7333,12 @@
       <c r="H78" s="49" t="n"/>
       <c r="I78" s="52" t="inlineStr">
         <is>
-          <t>Контролер 1 категории</t>
+          <t>Инженер 3 категории</t>
         </is>
       </c>
       <c r="J78" s="52" t="inlineStr">
         <is>
-          <t>Отдел технического контроля М</t>
+          <t>Отдел технического контроля МШ</t>
         </is>
       </c>
       <c r="K78" s="53" t="n"/>
@@ -7393,18 +7393,18 @@
     <row r="79" ht="12.75" customHeight="1">
       <c r="A79" s="45" t="inlineStr">
         <is>
-          <t>Ястребов Александр Сергеевич</t>
+          <t>Васильева Алина Владимировна</t>
         </is>
       </c>
       <c r="B79" s="46" t="inlineStr">
         <is>
-          <t>21.04.1985</t>
+          <t>28.02.1987</t>
         </is>
       </c>
       <c r="C79" s="47" t="n"/>
       <c r="D79" s="48" t="inlineStr">
         <is>
-          <t>077-644-645 06</t>
+          <t>126-910-880 65</t>
         </is>
       </c>
       <c r="E79" s="49" t="n"/>
@@ -7417,12 +7417,12 @@
       <c r="H79" s="49" t="n"/>
       <c r="I79" s="52" t="inlineStr">
         <is>
-          <t>Инженер 1 категории</t>
+          <t>Контролер 1 категории</t>
         </is>
       </c>
       <c r="J79" s="52" t="inlineStr">
         <is>
-          <t>Отдел технического контроля М</t>
+          <t>Отдел технического контроля МШ</t>
         </is>
       </c>
       <c r="K79" s="53" t="n"/>
@@ -7477,18 +7477,18 @@
     <row r="80" ht="12.75" customHeight="1">
       <c r="A80" s="45" t="inlineStr">
         <is>
-          <t>Божьева Ирина Вячеславовна</t>
+          <t>Райкова Ирина Алексеевна</t>
         </is>
       </c>
       <c r="B80" s="46" t="inlineStr">
         <is>
-          <t>14.09.1983</t>
+          <t>27.04.2001</t>
         </is>
       </c>
       <c r="C80" s="47" t="n"/>
       <c r="D80" s="48" t="inlineStr">
         <is>
-          <t>125-706-271 46</t>
+          <t>171-161-045 24</t>
         </is>
       </c>
       <c r="E80" s="49" t="n"/>
@@ -7501,7 +7501,7 @@
       <c r="H80" s="49" t="n"/>
       <c r="I80" s="52" t="inlineStr">
         <is>
-          <t>Инженер 3 категории</t>
+          <t>Контролер 1 категории</t>
         </is>
       </c>
       <c r="J80" s="52" t="inlineStr">
@@ -7561,36 +7561,36 @@
     <row r="81" ht="12.75" customHeight="1">
       <c r="A81" s="45" t="inlineStr">
         <is>
-          <t>Васильева Алина Владимировна</t>
+          <t>Акимов Михаил Александрович</t>
         </is>
       </c>
       <c r="B81" s="46" t="inlineStr">
         <is>
-          <t>28.02.1987</t>
+          <t>24.12.1971</t>
         </is>
       </c>
       <c r="C81" s="47" t="n"/>
       <c r="D81" s="48" t="inlineStr">
         <is>
-          <t>126-910-880 65</t>
+          <t>004-922-399 35</t>
         </is>
       </c>
       <c r="E81" s="49" t="n"/>
       <c r="F81" s="50" t="n"/>
       <c r="G81" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18</t>
         </is>
       </c>
       <c r="H81" s="49" t="n"/>
       <c r="I81" s="52" t="inlineStr">
         <is>
-          <t>Контролер 1 категории</t>
+          <t>Водитель автомобиля-экспедитор</t>
         </is>
       </c>
       <c r="J81" s="52" t="inlineStr">
         <is>
-          <t>Отдел технического контроля МШ</t>
+          <t>Отдел транспортного обеспечения МШ</t>
         </is>
       </c>
       <c r="K81" s="53" t="n"/>
@@ -7602,8 +7602,16 @@
       <c r="Q81" s="48" t="n"/>
       <c r="R81" s="49" t="n"/>
       <c r="S81" s="49" t="n"/>
-      <c r="T81" s="49" t="n"/>
-      <c r="U81" s="55" t="n"/>
+      <c r="T81" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U81" s="55" t="inlineStr">
+        <is>
+          <t>п.1 Прил.№2: управление транспортными средствами.</t>
+        </is>
+      </c>
       <c r="V81" s="49" t="n"/>
       <c r="W81" s="49" t="n"/>
       <c r="X81" s="48" t="n"/>
@@ -7645,36 +7653,36 @@
     <row r="82" ht="12.75" customHeight="1">
       <c r="A82" s="45" t="inlineStr">
         <is>
-          <t>Райкова Ирина Алексеевна</t>
+          <t>Батуревич Юрий Викторович</t>
         </is>
       </c>
       <c r="B82" s="46" t="inlineStr">
         <is>
-          <t>27.04.2001</t>
+          <t>11.04.1952</t>
         </is>
       </c>
       <c r="C82" s="47" t="n"/>
       <c r="D82" s="48" t="inlineStr">
         <is>
-          <t>171-161-045 24</t>
+          <t>173-721-383 69</t>
         </is>
       </c>
       <c r="E82" s="49" t="n"/>
       <c r="F82" s="50" t="n"/>
       <c r="G82" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18</t>
         </is>
       </c>
       <c r="H82" s="49" t="n"/>
       <c r="I82" s="52" t="inlineStr">
         <is>
-          <t>Контролер 1 категории</t>
+          <t>Водитель автомобиля-экспедитор</t>
         </is>
       </c>
       <c r="J82" s="52" t="inlineStr">
         <is>
-          <t>Отдел технического контроля МШ</t>
+          <t>Отдел транспортного обеспечения МШ</t>
         </is>
       </c>
       <c r="K82" s="53" t="n"/>
@@ -7686,8 +7694,16 @@
       <c r="Q82" s="48" t="n"/>
       <c r="R82" s="49" t="n"/>
       <c r="S82" s="49" t="n"/>
-      <c r="T82" s="49" t="n"/>
-      <c r="U82" s="55" t="n"/>
+      <c r="T82" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U82" s="55" t="inlineStr">
+        <is>
+          <t>п.1 Прил.№2: управление транспортными средствами.</t>
+        </is>
+      </c>
       <c r="V82" s="49" t="n"/>
       <c r="W82" s="49" t="n"/>
       <c r="X82" s="48" t="n"/>
@@ -7729,18 +7745,18 @@
     <row r="83" ht="12.75" customHeight="1">
       <c r="A83" s="45" t="inlineStr">
         <is>
-          <t>Акимов Михаил Александрович</t>
+          <t>Василенко Александр Иванович</t>
         </is>
       </c>
       <c r="B83" s="46" t="inlineStr">
         <is>
-          <t>24.12.1971</t>
+          <t>22.08.1970</t>
         </is>
       </c>
       <c r="C83" s="47" t="n"/>
       <c r="D83" s="48" t="inlineStr">
         <is>
-          <t>004-922-399 35</t>
+          <t>048-246-089 68</t>
         </is>
       </c>
       <c r="E83" s="49" t="n"/>
@@ -7821,18 +7837,18 @@
     <row r="84" ht="12.75" customHeight="1">
       <c r="A84" s="45" t="inlineStr">
         <is>
-          <t>Батуревич Юрий Викторович</t>
+          <t>Грязнов Анатолий Николаевич</t>
         </is>
       </c>
       <c r="B84" s="46" t="inlineStr">
         <is>
-          <t>11.04.1952</t>
+          <t>30.08.1952</t>
         </is>
       </c>
       <c r="C84" s="47" t="n"/>
       <c r="D84" s="48" t="inlineStr">
         <is>
-          <t>173-721-383 69</t>
+          <t>005-174-739 27</t>
         </is>
       </c>
       <c r="E84" s="49" t="n"/>
@@ -7913,18 +7929,18 @@
     <row r="85" ht="12.75" customHeight="1">
       <c r="A85" s="45" t="inlineStr">
         <is>
-          <t>Василенко Александр Иванович</t>
+          <t>Евдокимов Игорь Валентинович</t>
         </is>
       </c>
       <c r="B85" s="46" t="inlineStr">
         <is>
-          <t>22.08.1970</t>
+          <t>24.05.1966</t>
         </is>
       </c>
       <c r="C85" s="47" t="n"/>
       <c r="D85" s="48" t="inlineStr">
         <is>
-          <t>048-246-089 68</t>
+          <t>023-728-201 27</t>
         </is>
       </c>
       <c r="E85" s="49" t="n"/>
@@ -8005,18 +8021,18 @@
     <row r="86" ht="12.75" customHeight="1">
       <c r="A86" s="45" t="inlineStr">
         <is>
-          <t>Грязнов Анатолий Николаевич</t>
+          <t>Ерофеев Олег Игоревич</t>
         </is>
       </c>
       <c r="B86" s="46" t="inlineStr">
         <is>
-          <t>30.08.1952</t>
+          <t>25.01.1984</t>
         </is>
       </c>
       <c r="C86" s="47" t="n"/>
       <c r="D86" s="48" t="inlineStr">
         <is>
-          <t>005-174-739 27</t>
+          <t>132-461-481 33</t>
         </is>
       </c>
       <c r="E86" s="49" t="n"/>
@@ -8097,18 +8113,18 @@
     <row r="87" ht="12.75" customHeight="1">
       <c r="A87" s="45" t="inlineStr">
         <is>
-          <t>Евдокимов Игорь Валентинович</t>
+          <t>Жигунов Вячеслав Владимирович</t>
         </is>
       </c>
       <c r="B87" s="46" t="inlineStr">
         <is>
-          <t>24.05.1966</t>
+          <t>13.05.1967</t>
         </is>
       </c>
       <c r="C87" s="47" t="n"/>
       <c r="D87" s="48" t="inlineStr">
         <is>
-          <t>023-728-201 27</t>
+          <t>055-410-989 55</t>
         </is>
       </c>
       <c r="E87" s="49" t="n"/>
@@ -8189,18 +8205,18 @@
     <row r="88" ht="12.75" customHeight="1">
       <c r="A88" s="45" t="inlineStr">
         <is>
-          <t>Ерофеев Олег Игоревич</t>
+          <t>Крутяков Сергей Владимирович</t>
         </is>
       </c>
       <c r="B88" s="46" t="inlineStr">
         <is>
-          <t>25.01.1984</t>
+          <t>14.01.1960</t>
         </is>
       </c>
       <c r="C88" s="47" t="n"/>
       <c r="D88" s="48" t="inlineStr">
         <is>
-          <t>132-461-481 33</t>
+          <t>065-715-189 77</t>
         </is>
       </c>
       <c r="E88" s="49" t="n"/>
@@ -8281,18 +8297,18 @@
     <row r="89" ht="12.75" customHeight="1">
       <c r="A89" s="45" t="inlineStr">
         <is>
-          <t>Жигунов Вячеслав Владимирович</t>
+          <t>Лучкин Евгений Иванович</t>
         </is>
       </c>
       <c r="B89" s="46" t="inlineStr">
         <is>
-          <t>13.05.1967</t>
+          <t>11.12.1964</t>
         </is>
       </c>
       <c r="C89" s="47" t="n"/>
       <c r="D89" s="48" t="inlineStr">
         <is>
-          <t>055-410-989 55</t>
+          <t>078-244-872 99</t>
         </is>
       </c>
       <c r="E89" s="49" t="n"/>
@@ -8373,36 +8389,36 @@
     <row r="90" ht="12.75" customHeight="1">
       <c r="A90" s="45" t="inlineStr">
         <is>
-          <t>Крутяков Сергей Владимирович</t>
+          <t>Абрамович Светлана Николаевна</t>
         </is>
       </c>
       <c r="B90" s="46" t="inlineStr">
         <is>
-          <t>14.01.1960</t>
+          <t>27.05.1967</t>
         </is>
       </c>
       <c r="C90" s="47" t="n"/>
       <c r="D90" s="48" t="inlineStr">
         <is>
-          <t>065-715-189 77</t>
+          <t>056-122-002 07</t>
         </is>
       </c>
       <c r="E90" s="49" t="n"/>
       <c r="F90" s="50" t="n"/>
       <c r="G90" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18</t>
+          <t>п.4.4, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="H90" s="49" t="n"/>
       <c r="I90" s="52" t="inlineStr">
         <is>
-          <t>Водитель автомобиля-экспедитор</t>
+          <t>Диспетчер</t>
         </is>
       </c>
       <c r="J90" s="52" t="inlineStr">
         <is>
-          <t>Отдел транспортного обеспечения МШ</t>
+          <t>Планово-диспетчерский отдел МШ</t>
         </is>
       </c>
       <c r="K90" s="53" t="n"/>
@@ -8414,16 +8430,8 @@
       <c r="Q90" s="48" t="n"/>
       <c r="R90" s="49" t="n"/>
       <c r="S90" s="49" t="n"/>
-      <c r="T90" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U90" s="55" t="inlineStr">
-        <is>
-          <t>п.1 Прил.№2: управление транспортными средствами.</t>
-        </is>
-      </c>
+      <c r="T90" s="49" t="n"/>
+      <c r="U90" s="55" t="n"/>
       <c r="V90" s="49" t="n"/>
       <c r="W90" s="49" t="n"/>
       <c r="X90" s="48" t="n"/>
@@ -8465,36 +8473,36 @@
     <row r="91" ht="12.75" customHeight="1">
       <c r="A91" s="45" t="inlineStr">
         <is>
-          <t>Лучкин Евгений Иванович</t>
+          <t>Баранникова Елена Александровна</t>
         </is>
       </c>
       <c r="B91" s="46" t="inlineStr">
         <is>
-          <t>11.12.1964</t>
+          <t>21.11.1990</t>
         </is>
       </c>
       <c r="C91" s="47" t="n"/>
       <c r="D91" s="48" t="inlineStr">
         <is>
-          <t>078-244-872 99</t>
+          <t>146-226-387 60</t>
         </is>
       </c>
       <c r="E91" s="49" t="n"/>
       <c r="F91" s="50" t="n"/>
       <c r="G91" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18</t>
+          <t>п.4.4, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="H91" s="49" t="n"/>
       <c r="I91" s="52" t="inlineStr">
         <is>
-          <t>Водитель автомобиля-экспедитор</t>
+          <t>Диспетчер</t>
         </is>
       </c>
       <c r="J91" s="52" t="inlineStr">
         <is>
-          <t>Отдел транспортного обеспечения МШ</t>
+          <t>Планово-диспетчерский отдел МШ</t>
         </is>
       </c>
       <c r="K91" s="53" t="n"/>
@@ -8506,16 +8514,8 @@
       <c r="Q91" s="48" t="n"/>
       <c r="R91" s="49" t="n"/>
       <c r="S91" s="49" t="n"/>
-      <c r="T91" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U91" s="55" t="inlineStr">
-        <is>
-          <t>п.1 Прил.№2: управление транспортными средствами.</t>
-        </is>
-      </c>
+      <c r="T91" s="49" t="n"/>
+      <c r="U91" s="55" t="n"/>
       <c r="V91" s="49" t="n"/>
       <c r="W91" s="49" t="n"/>
       <c r="X91" s="48" t="n"/>
@@ -8557,18 +8557,18 @@
     <row r="92" ht="12.75" customHeight="1">
       <c r="A92" s="45" t="inlineStr">
         <is>
-          <t>Абрамович Светлана Николаевна</t>
+          <t>Гришин Алексей Владимирович</t>
         </is>
       </c>
       <c r="B92" s="46" t="inlineStr">
         <is>
-          <t>27.05.1967</t>
+          <t>27.06.1967</t>
         </is>
       </c>
       <c r="C92" s="47" t="n"/>
       <c r="D92" s="48" t="inlineStr">
         <is>
-          <t>056-122-002 07</t>
+          <t>063-210-456 13</t>
         </is>
       </c>
       <c r="E92" s="49" t="n"/>
@@ -8641,18 +8641,18 @@
     <row r="93" ht="12.75" customHeight="1">
       <c r="A93" s="45" t="inlineStr">
         <is>
-          <t>Баранникова Елена Александровна</t>
+          <t>Гришина Неля Евгеньевна</t>
         </is>
       </c>
       <c r="B93" s="46" t="inlineStr">
         <is>
-          <t>21.11.1990</t>
+          <t>30.07.1974</t>
         </is>
       </c>
       <c r="C93" s="47" t="n"/>
       <c r="D93" s="48" t="inlineStr">
         <is>
-          <t>146-226-387 60</t>
+          <t>045-075-814 51</t>
         </is>
       </c>
       <c r="E93" s="49" t="n"/>
@@ -8665,7 +8665,7 @@
       <c r="H93" s="49" t="n"/>
       <c r="I93" s="52" t="inlineStr">
         <is>
-          <t>Диспетчер</t>
+          <t>Ведущий диспетчер</t>
         </is>
       </c>
       <c r="J93" s="52" t="inlineStr">
@@ -8725,18 +8725,18 @@
     <row r="94" ht="12.75" customHeight="1">
       <c r="A94" s="45" t="inlineStr">
         <is>
-          <t>Гришин Алексей Владимирович</t>
+          <t>Запотылок Алена Владимировна</t>
         </is>
       </c>
       <c r="B94" s="46" t="inlineStr">
         <is>
-          <t>27.06.1967</t>
+          <t>03.08.1993</t>
         </is>
       </c>
       <c r="C94" s="47" t="n"/>
       <c r="D94" s="48" t="inlineStr">
         <is>
-          <t>063-210-456 13</t>
+          <t>172-727-596 97</t>
         </is>
       </c>
       <c r="E94" s="49" t="n"/>
@@ -8749,7 +8749,7 @@
       <c r="H94" s="49" t="n"/>
       <c r="I94" s="52" t="inlineStr">
         <is>
-          <t>Диспетчер</t>
+          <t>Ведущий диспетчер</t>
         </is>
       </c>
       <c r="J94" s="52" t="inlineStr">
@@ -8809,18 +8809,18 @@
     <row r="95" ht="12.75" customHeight="1">
       <c r="A95" s="45" t="inlineStr">
         <is>
-          <t>Гришина Неля Евгеньевна</t>
+          <t>Зубехин Григорий Александрович</t>
         </is>
       </c>
       <c r="B95" s="46" t="inlineStr">
         <is>
-          <t>30.07.1974</t>
+          <t>18.09.2004</t>
         </is>
       </c>
       <c r="C95" s="47" t="n"/>
       <c r="D95" s="48" t="inlineStr">
         <is>
-          <t>045-075-814 51</t>
+          <t>175-923-904 05</t>
         </is>
       </c>
       <c r="E95" s="49" t="n"/>
@@ -8833,7 +8833,7 @@
       <c r="H95" s="49" t="n"/>
       <c r="I95" s="52" t="inlineStr">
         <is>
-          <t>Ведущий диспетчер</t>
+          <t>Диспетчер</t>
         </is>
       </c>
       <c r="J95" s="52" t="inlineStr">
@@ -8893,18 +8893,18 @@
     <row r="96" ht="12.75" customHeight="1">
       <c r="A96" s="45" t="inlineStr">
         <is>
-          <t>Запотылок Алена Владимировна</t>
+          <t>Кадиева Наталья Борисовна</t>
         </is>
       </c>
       <c r="B96" s="46" t="inlineStr">
         <is>
-          <t>03.08.1993</t>
+          <t>17.07.1974</t>
         </is>
       </c>
       <c r="C96" s="47" t="n"/>
       <c r="D96" s="48" t="inlineStr">
         <is>
-          <t>172-727-596 97</t>
+          <t>068-646-413 00</t>
         </is>
       </c>
       <c r="E96" s="49" t="n"/>
@@ -8917,7 +8917,7 @@
       <c r="H96" s="49" t="n"/>
       <c r="I96" s="52" t="inlineStr">
         <is>
-          <t>Ведущий диспетчер</t>
+          <t>Диспетчер</t>
         </is>
       </c>
       <c r="J96" s="52" t="inlineStr">
@@ -8977,18 +8977,18 @@
     <row r="97" ht="12.75" customHeight="1">
       <c r="A97" s="45" t="inlineStr">
         <is>
-          <t>Зубехин Григорий Александрович</t>
+          <t>Лапкин Виталий Олегович</t>
         </is>
       </c>
       <c r="B97" s="46" t="inlineStr">
         <is>
-          <t>18.09.2004</t>
+          <t>22.11.1990</t>
         </is>
       </c>
       <c r="C97" s="47" t="n"/>
       <c r="D97" s="48" t="inlineStr">
         <is>
-          <t>175-923-904 05</t>
+          <t>105-950-943 60</t>
         </is>
       </c>
       <c r="E97" s="49" t="n"/>
@@ -9061,18 +9061,18 @@
     <row r="98" ht="12.75" customHeight="1">
       <c r="A98" s="45" t="inlineStr">
         <is>
-          <t>Кадиева Наталья Борисовна</t>
+          <t>Лапкина Анастасия Владимировна</t>
         </is>
       </c>
       <c r="B98" s="46" t="inlineStr">
         <is>
-          <t>17.07.1974</t>
+          <t>06.10.1991</t>
         </is>
       </c>
       <c r="C98" s="47" t="n"/>
       <c r="D98" s="48" t="inlineStr">
         <is>
-          <t>068-646-413 00</t>
+          <t>154-812-410 51</t>
         </is>
       </c>
       <c r="E98" s="49" t="n"/>
@@ -9145,18 +9145,18 @@
     <row r="99" ht="12.75" customHeight="1">
       <c r="A99" s="45" t="inlineStr">
         <is>
-          <t>Лапкин Виталий Олегович</t>
+          <t>Паукова Наталья Владимировна</t>
         </is>
       </c>
       <c r="B99" s="46" t="inlineStr">
         <is>
-          <t>22.11.1990</t>
+          <t>12.07.1976</t>
         </is>
       </c>
       <c r="C99" s="47" t="n"/>
       <c r="D99" s="48" t="inlineStr">
         <is>
-          <t>105-950-943 60</t>
+          <t>110-039-153 84</t>
         </is>
       </c>
       <c r="E99" s="49" t="n"/>
@@ -9169,7 +9169,7 @@
       <c r="H99" s="49" t="n"/>
       <c r="I99" s="52" t="inlineStr">
         <is>
-          <t>Диспетчер</t>
+          <t>Ведущий диспетчер</t>
         </is>
       </c>
       <c r="J99" s="52" t="inlineStr">
@@ -9229,18 +9229,18 @@
     <row r="100" ht="12.75" customHeight="1">
       <c r="A100" s="45" t="inlineStr">
         <is>
-          <t>Лапкина Анастасия Владимировна</t>
+          <t>Полозов Василий Борисович</t>
         </is>
       </c>
       <c r="B100" s="46" t="inlineStr">
         <is>
-          <t>06.10.1991</t>
+          <t>29.03.1987</t>
         </is>
       </c>
       <c r="C100" s="47" t="n"/>
       <c r="D100" s="48" t="inlineStr">
         <is>
-          <t>154-812-410 51</t>
+          <t>115-043-181 03</t>
         </is>
       </c>
       <c r="E100" s="49" t="n"/>
@@ -9253,7 +9253,7 @@
       <c r="H100" s="49" t="n"/>
       <c r="I100" s="52" t="inlineStr">
         <is>
-          <t>Диспетчер</t>
+          <t>Ведущий инженер</t>
         </is>
       </c>
       <c r="J100" s="52" t="inlineStr">
@@ -9313,18 +9313,18 @@
     <row r="101" ht="12.75" customHeight="1">
       <c r="A101" s="45" t="inlineStr">
         <is>
-          <t>Паукова Наталья Владимировна</t>
+          <t>Попова Юлия Александровна</t>
         </is>
       </c>
       <c r="B101" s="46" t="inlineStr">
         <is>
-          <t>12.07.1976</t>
+          <t>31.10.1987</t>
         </is>
       </c>
       <c r="C101" s="47" t="n"/>
       <c r="D101" s="48" t="inlineStr">
         <is>
-          <t>110-039-153 84</t>
+          <t>152-324-399 42</t>
         </is>
       </c>
       <c r="E101" s="49" t="n"/>
@@ -9337,7 +9337,7 @@
       <c r="H101" s="49" t="n"/>
       <c r="I101" s="52" t="inlineStr">
         <is>
-          <t>Ведущий диспетчер</t>
+          <t>Ведущий специалист по учету</t>
         </is>
       </c>
       <c r="J101" s="52" t="inlineStr">
@@ -9397,18 +9397,18 @@
     <row r="102" ht="12.75" customHeight="1">
       <c r="A102" s="45" t="inlineStr">
         <is>
-          <t>Полозов Василий Борисович</t>
+          <t>Хлыщенко Александр Александрович</t>
         </is>
       </c>
       <c r="B102" s="46" t="inlineStr">
         <is>
-          <t>29.03.1987</t>
+          <t>25.07.1989</t>
         </is>
       </c>
       <c r="C102" s="47" t="n"/>
       <c r="D102" s="48" t="inlineStr">
         <is>
-          <t>115-043-181 03</t>
+          <t>166-507-435 79</t>
         </is>
       </c>
       <c r="E102" s="49" t="n"/>
@@ -9481,36 +9481,36 @@
     <row r="103" ht="12.75" customHeight="1">
       <c r="A103" s="45" t="inlineStr">
         <is>
-          <t>Попова Юлия Александровна</t>
+          <t>Петина Ирина Викторовна</t>
         </is>
       </c>
       <c r="B103" s="46" t="inlineStr">
         <is>
-          <t>31.10.1987</t>
+          <t>14.10.1990</t>
         </is>
       </c>
       <c r="C103" s="47" t="n"/>
       <c r="D103" s="48" t="inlineStr">
         <is>
-          <t>152-324-399 42</t>
+          <t>138-565-749 05</t>
         </is>
       </c>
       <c r="E103" s="49" t="n"/>
       <c r="F103" s="50" t="n"/>
       <c r="G103" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.1, п.6.2</t>
         </is>
       </c>
       <c r="H103" s="49" t="n"/>
       <c r="I103" s="52" t="inlineStr">
         <is>
-          <t>Ведущий специалист по учету</t>
+          <t>Оператор склада</t>
         </is>
       </c>
       <c r="J103" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел МШ</t>
+          <t>Склад (МШ н/д)</t>
         </is>
       </c>
       <c r="K103" s="53" t="n"/>
@@ -9565,36 +9565,36 @@
     <row r="104" ht="12.75" customHeight="1">
       <c r="A104" s="45" t="inlineStr">
         <is>
-          <t>Хлыщенко Александр Александрович</t>
+          <t>Агалиев Рафаэл Рашидович</t>
         </is>
       </c>
       <c r="B104" s="46" t="inlineStr">
         <is>
-          <t>25.07.1989</t>
+          <t>22.03.1996</t>
         </is>
       </c>
       <c r="C104" s="47" t="n"/>
       <c r="D104" s="48" t="inlineStr">
         <is>
-          <t>166-507-435 79</t>
+          <t>184-005-664 54</t>
         </is>
       </c>
       <c r="E104" s="49" t="n"/>
       <c r="F104" s="50" t="n"/>
       <c r="G104" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1</t>
         </is>
       </c>
       <c r="H104" s="49" t="n"/>
       <c r="I104" s="52" t="inlineStr">
         <is>
-          <t>Ведущий инженер</t>
+          <t>Кладовщик-комплектовщик</t>
         </is>
       </c>
       <c r="J104" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел МШ</t>
+          <t>Склад МШ</t>
         </is>
       </c>
       <c r="K104" s="53" t="n"/>
@@ -9606,8 +9606,16 @@
       <c r="Q104" s="48" t="n"/>
       <c r="R104" s="49" t="n"/>
       <c r="S104" s="49" t="n"/>
-      <c r="T104" s="49" t="n"/>
-      <c r="U104" s="55" t="n"/>
+      <c r="T104" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U104" s="55" t="inlineStr">
+        <is>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+        </is>
+      </c>
       <c r="V104" s="49" t="n"/>
       <c r="W104" s="49" t="n"/>
       <c r="X104" s="48" t="n"/>
@@ -9649,18 +9657,18 @@
     <row r="105" ht="12.75" customHeight="1">
       <c r="A105" s="45" t="inlineStr">
         <is>
-          <t>Петина Ирина Викторовна</t>
+          <t>Балкивская Людмила Алексеевна</t>
         </is>
       </c>
       <c r="B105" s="46" t="inlineStr">
         <is>
-          <t>14.10.1990</t>
+          <t>05.01.1960</t>
         </is>
       </c>
       <c r="C105" s="47" t="n"/>
       <c r="D105" s="48" t="inlineStr">
         <is>
-          <t>138-565-749 05</t>
+          <t>018-959-483 08</t>
         </is>
       </c>
       <c r="E105" s="49" t="n"/>
@@ -9673,12 +9681,12 @@
       <c r="H105" s="49" t="n"/>
       <c r="I105" s="52" t="inlineStr">
         <is>
-          <t>Оператор склада</t>
+          <t>Старший кладовщик</t>
         </is>
       </c>
       <c r="J105" s="52" t="inlineStr">
         <is>
-          <t>Склад (МШ н/д)</t>
+          <t>Склад МШ</t>
         </is>
       </c>
       <c r="K105" s="53" t="n"/>
@@ -9733,31 +9741,31 @@
     <row r="106" ht="12.75" customHeight="1">
       <c r="A106" s="45" t="inlineStr">
         <is>
-          <t>Агалиев Рафаэл Рашидович</t>
+          <t>Богатырев Николай Владимирович</t>
         </is>
       </c>
       <c r="B106" s="46" t="inlineStr">
         <is>
-          <t>22.03.1996</t>
+          <t>21.05.1976</t>
         </is>
       </c>
       <c r="C106" s="47" t="n"/>
       <c r="D106" s="48" t="inlineStr">
         <is>
-          <t>184-005-664 54</t>
+          <t>008-865-339 77</t>
         </is>
       </c>
       <c r="E106" s="49" t="n"/>
       <c r="F106" s="50" t="n"/>
       <c r="G106" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1</t>
+          <t>п.1.49.2, п.1.49.14, п.1.50, п.4.3.1, п.4.4, п.6.2</t>
         </is>
       </c>
       <c r="H106" s="49" t="n"/>
       <c r="I106" s="52" t="inlineStr">
         <is>
-          <t>Кладовщик-комплектовщик</t>
+          <t>Лаборант</t>
         </is>
       </c>
       <c r="J106" s="52" t="inlineStr">
@@ -9774,16 +9782,8 @@
       <c r="Q106" s="48" t="n"/>
       <c r="R106" s="49" t="n"/>
       <c r="S106" s="49" t="n"/>
-      <c r="T106" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U106" s="55" t="inlineStr">
-        <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
-        </is>
-      </c>
+      <c r="T106" s="49" t="n"/>
+      <c r="U106" s="55" t="n"/>
       <c r="V106" s="49" t="n"/>
       <c r="W106" s="49" t="n"/>
       <c r="X106" s="48" t="n"/>
@@ -9825,18 +9825,18 @@
     <row r="107" ht="12.75" customHeight="1">
       <c r="A107" s="45" t="inlineStr">
         <is>
-          <t>Балкивская Людмила Алексеевна</t>
+          <t>Густов Александр Витальевич</t>
         </is>
       </c>
       <c r="B107" s="46" t="inlineStr">
         <is>
-          <t>05.01.1960</t>
+          <t>03.01.1985</t>
         </is>
       </c>
       <c r="C107" s="47" t="n"/>
       <c r="D107" s="48" t="inlineStr">
         <is>
-          <t>018-959-483 08</t>
+          <t>134-854-450 71</t>
         </is>
       </c>
       <c r="E107" s="49" t="n"/>
@@ -9849,7 +9849,7 @@
       <c r="H107" s="49" t="n"/>
       <c r="I107" s="52" t="inlineStr">
         <is>
-          <t>Старший кладовщик</t>
+          <t>Кладовщик</t>
         </is>
       </c>
       <c r="J107" s="52" t="inlineStr">
@@ -9909,31 +9909,31 @@
     <row r="108" ht="12.75" customHeight="1">
       <c r="A108" s="45" t="inlineStr">
         <is>
-          <t>Богатырев Николай Владимирович</t>
+          <t>Дягин Александр Александрович</t>
         </is>
       </c>
       <c r="B108" s="46" t="inlineStr">
         <is>
-          <t>21.05.1976</t>
+          <t>21.11.1996</t>
         </is>
       </c>
       <c r="C108" s="47" t="n"/>
       <c r="D108" s="48" t="inlineStr">
         <is>
-          <t>008-865-339 77</t>
+          <t>176-939-404 26</t>
         </is>
       </c>
       <c r="E108" s="49" t="n"/>
       <c r="F108" s="50" t="n"/>
       <c r="G108" s="51" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.1.50, п.4.3.1, п.4.4, п.6.2</t>
+          <t>п.4.4, п.5.1, п.6.2</t>
         </is>
       </c>
       <c r="H108" s="49" t="n"/>
       <c r="I108" s="52" t="inlineStr">
         <is>
-          <t>Лаборант</t>
+          <t>Кладовщик</t>
         </is>
       </c>
       <c r="J108" s="52" t="inlineStr">
@@ -9993,31 +9993,31 @@
     <row r="109" ht="12.75" customHeight="1">
       <c r="A109" s="45" t="inlineStr">
         <is>
-          <t>Густов Александр Витальевич</t>
+          <t>Каменев Дмитрий Викторович</t>
         </is>
       </c>
       <c r="B109" s="46" t="inlineStr">
         <is>
-          <t>03.01.1985</t>
+          <t>29.10.1975</t>
         </is>
       </c>
       <c r="C109" s="47" t="n"/>
       <c r="D109" s="48" t="inlineStr">
         <is>
-          <t>134-854-450 71</t>
+          <t>154-183-856 74</t>
         </is>
       </c>
       <c r="E109" s="49" t="n"/>
       <c r="F109" s="50" t="n"/>
       <c r="G109" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.6.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1</t>
         </is>
       </c>
       <c r="H109" s="49" t="n"/>
       <c r="I109" s="52" t="inlineStr">
         <is>
-          <t>Кладовщик</t>
+          <t>Кладовщик-комплектовщик</t>
         </is>
       </c>
       <c r="J109" s="52" t="inlineStr">
@@ -10034,8 +10034,16 @@
       <c r="Q109" s="48" t="n"/>
       <c r="R109" s="49" t="n"/>
       <c r="S109" s="49" t="n"/>
-      <c r="T109" s="49" t="n"/>
-      <c r="U109" s="55" t="n"/>
+      <c r="T109" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U109" s="55" t="inlineStr">
+        <is>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+        </is>
+      </c>
       <c r="V109" s="49" t="n"/>
       <c r="W109" s="49" t="n"/>
       <c r="X109" s="48" t="n"/>
@@ -10077,18 +10085,18 @@
     <row r="110" ht="12.75" customHeight="1">
       <c r="A110" s="45" t="inlineStr">
         <is>
-          <t>Дягин Александр Александрович</t>
+          <t>Карпачева Татьяна Владимировна</t>
         </is>
       </c>
       <c r="B110" s="46" t="inlineStr">
         <is>
-          <t>21.11.1996</t>
+          <t>17.01.1985</t>
         </is>
       </c>
       <c r="C110" s="47" t="n"/>
       <c r="D110" s="48" t="inlineStr">
         <is>
-          <t>176-939-404 26</t>
+          <t>104-597-939 81</t>
         </is>
       </c>
       <c r="E110" s="49" t="n"/>
@@ -10101,7 +10109,7 @@
       <c r="H110" s="49" t="n"/>
       <c r="I110" s="52" t="inlineStr">
         <is>
-          <t>Кладовщик</t>
+          <t>Старший кладовщик</t>
         </is>
       </c>
       <c r="J110" s="52" t="inlineStr">
@@ -10161,31 +10169,31 @@
     <row r="111" ht="12.75" customHeight="1">
       <c r="A111" s="45" t="inlineStr">
         <is>
-          <t>Каменев Дмитрий Викторович</t>
+          <t>Кирбенева Татьяна Александровна</t>
         </is>
       </c>
       <c r="B111" s="46" t="inlineStr">
         <is>
-          <t>29.10.1975</t>
+          <t>22.06.1987</t>
         </is>
       </c>
       <c r="C111" s="47" t="n"/>
       <c r="D111" s="48" t="inlineStr">
         <is>
-          <t>154-183-856 74</t>
+          <t>118-108-755 46</t>
         </is>
       </c>
       <c r="E111" s="49" t="n"/>
       <c r="F111" s="50" t="n"/>
       <c r="G111" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1</t>
+          <t>п.4.4, п.5.1, п.6.2</t>
         </is>
       </c>
       <c r="H111" s="49" t="n"/>
       <c r="I111" s="52" t="inlineStr">
         <is>
-          <t>Кладовщик-комплектовщик</t>
+          <t>Оператор склада</t>
         </is>
       </c>
       <c r="J111" s="52" t="inlineStr">
@@ -10202,16 +10210,8 @@
       <c r="Q111" s="48" t="n"/>
       <c r="R111" s="49" t="n"/>
       <c r="S111" s="49" t="n"/>
-      <c r="T111" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U111" s="55" t="inlineStr">
-        <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
-        </is>
-      </c>
+      <c r="T111" s="49" t="n"/>
+      <c r="U111" s="55" t="n"/>
       <c r="V111" s="49" t="n"/>
       <c r="W111" s="49" t="n"/>
       <c r="X111" s="48" t="n"/>
@@ -10253,31 +10253,31 @@
     <row r="112" ht="12.75" customHeight="1">
       <c r="A112" s="45" t="inlineStr">
         <is>
-          <t>Карпачева Татьяна Владимировна</t>
+          <t>Ласкавый Андрей Викторович</t>
         </is>
       </c>
       <c r="B112" s="46" t="inlineStr">
         <is>
-          <t>17.01.1985</t>
+          <t>03.01.1980</t>
         </is>
       </c>
       <c r="C112" s="47" t="n"/>
       <c r="D112" s="48" t="inlineStr">
         <is>
-          <t>104-597-939 81</t>
+          <t>171-022-718 20</t>
         </is>
       </c>
       <c r="E112" s="49" t="n"/>
       <c r="F112" s="50" t="n"/>
       <c r="G112" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.6.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1</t>
         </is>
       </c>
       <c r="H112" s="49" t="n"/>
       <c r="I112" s="52" t="inlineStr">
         <is>
-          <t>Старший кладовщик</t>
+          <t>Кладовщик-комплектовщик</t>
         </is>
       </c>
       <c r="J112" s="52" t="inlineStr">
@@ -10294,8 +10294,16 @@
       <c r="Q112" s="48" t="n"/>
       <c r="R112" s="49" t="n"/>
       <c r="S112" s="49" t="n"/>
-      <c r="T112" s="49" t="n"/>
-      <c r="U112" s="55" t="n"/>
+      <c r="T112" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U112" s="55" t="inlineStr">
+        <is>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+        </is>
+      </c>
       <c r="V112" s="49" t="n"/>
       <c r="W112" s="49" t="n"/>
       <c r="X112" s="48" t="n"/>
@@ -10337,18 +10345,18 @@
     <row r="113" ht="12.75" customHeight="1">
       <c r="A113" s="45" t="inlineStr">
         <is>
-          <t>Кирбенева Татьяна Александровна</t>
+          <t>Лягинова Анастасия Витальевна</t>
         </is>
       </c>
       <c r="B113" s="46" t="inlineStr">
         <is>
-          <t>22.06.1987</t>
+          <t>31.01.1992</t>
         </is>
       </c>
       <c r="C113" s="47" t="n"/>
       <c r="D113" s="48" t="inlineStr">
         <is>
-          <t>118-108-755 46</t>
+          <t>133-655-426 56</t>
         </is>
       </c>
       <c r="E113" s="49" t="n"/>
@@ -10421,18 +10429,18 @@
     <row r="114" ht="12.75" customHeight="1">
       <c r="A114" s="45" t="inlineStr">
         <is>
-          <t>Ласкавый Андрей Викторович</t>
+          <t>Моряков Константин Викторович</t>
         </is>
       </c>
       <c r="B114" s="46" t="inlineStr">
         <is>
-          <t>03.01.1980</t>
+          <t>06.04.1971</t>
         </is>
       </c>
       <c r="C114" s="47" t="n"/>
       <c r="D114" s="48" t="inlineStr">
         <is>
-          <t>171-022-718 20</t>
+          <t>116-163-416 26</t>
         </is>
       </c>
       <c r="E114" s="49" t="n"/>
@@ -10513,18 +10521,18 @@
     <row r="115" ht="12.75" customHeight="1">
       <c r="A115" s="45" t="inlineStr">
         <is>
-          <t>Лягинова Анастасия Витальевна</t>
+          <t>Нестеров Аркадий Николаевич</t>
         </is>
       </c>
       <c r="B115" s="46" t="inlineStr">
         <is>
-          <t>31.01.1992</t>
+          <t>07.04.1987</t>
         </is>
       </c>
       <c r="C115" s="47" t="n"/>
       <c r="D115" s="48" t="inlineStr">
         <is>
-          <t>133-655-426 56</t>
+          <t>168-793-135 24</t>
         </is>
       </c>
       <c r="E115" s="49" t="n"/>
@@ -10537,7 +10545,7 @@
       <c r="H115" s="49" t="n"/>
       <c r="I115" s="52" t="inlineStr">
         <is>
-          <t>Оператор склада</t>
+          <t>Старший кладовщик</t>
         </is>
       </c>
       <c r="J115" s="52" t="inlineStr">
@@ -10597,31 +10605,31 @@
     <row r="116" ht="12.75" customHeight="1">
       <c r="A116" s="45" t="inlineStr">
         <is>
-          <t>Моряков Константин Викторович</t>
+          <t>Ноженко Екатерина Сергеевна</t>
         </is>
       </c>
       <c r="B116" s="46" t="inlineStr">
         <is>
-          <t>06.04.1971</t>
+          <t>09.04.1981</t>
         </is>
       </c>
       <c r="C116" s="47" t="n"/>
       <c r="D116" s="48" t="inlineStr">
         <is>
-          <t>116-163-416 26</t>
+          <t>075-854-992 25</t>
         </is>
       </c>
       <c r="E116" s="49" t="n"/>
       <c r="F116" s="50" t="n"/>
       <c r="G116" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1</t>
+          <t>п.4.4, п.5.1, п.6.2</t>
         </is>
       </c>
       <c r="H116" s="49" t="n"/>
       <c r="I116" s="52" t="inlineStr">
         <is>
-          <t>Кладовщик-комплектовщик</t>
+          <t>Кладовщик</t>
         </is>
       </c>
       <c r="J116" s="52" t="inlineStr">
@@ -10638,16 +10646,8 @@
       <c r="Q116" s="48" t="n"/>
       <c r="R116" s="49" t="n"/>
       <c r="S116" s="49" t="n"/>
-      <c r="T116" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U116" s="55" t="inlineStr">
-        <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
-        </is>
-      </c>
+      <c r="T116" s="49" t="n"/>
+      <c r="U116" s="55" t="n"/>
       <c r="V116" s="49" t="n"/>
       <c r="W116" s="49" t="n"/>
       <c r="X116" s="48" t="n"/>
@@ -10689,18 +10689,18 @@
     <row r="117" ht="12.75" customHeight="1">
       <c r="A117" s="45" t="inlineStr">
         <is>
-          <t>Нестеров Аркадий Николаевич</t>
+          <t>Прохорова Маргарита Александровна</t>
         </is>
       </c>
       <c r="B117" s="46" t="inlineStr">
         <is>
-          <t>07.04.1987</t>
+          <t>07.03.1993</t>
         </is>
       </c>
       <c r="C117" s="47" t="n"/>
       <c r="D117" s="48" t="inlineStr">
         <is>
-          <t>168-793-135 24</t>
+          <t>177-840-039 96</t>
         </is>
       </c>
       <c r="E117" s="49" t="n"/>
@@ -10713,7 +10713,7 @@
       <c r="H117" s="49" t="n"/>
       <c r="I117" s="52" t="inlineStr">
         <is>
-          <t>Старший кладовщик</t>
+          <t>Кладовщик</t>
         </is>
       </c>
       <c r="J117" s="52" t="inlineStr">
@@ -10773,18 +10773,18 @@
     <row r="118" ht="12.75" customHeight="1">
       <c r="A118" s="45" t="inlineStr">
         <is>
-          <t>Ноженко Екатерина Сергеевна</t>
+          <t>Султанов Тимур Боирович</t>
         </is>
       </c>
       <c r="B118" s="46" t="inlineStr">
         <is>
-          <t>09.04.1981</t>
+          <t>16.09.1995</t>
         </is>
       </c>
       <c r="C118" s="47" t="n"/>
       <c r="D118" s="48" t="inlineStr">
         <is>
-          <t>075-854-992 25</t>
+          <t>175-804-278 91</t>
         </is>
       </c>
       <c r="E118" s="49" t="n"/>
@@ -10857,31 +10857,31 @@
     <row r="119" ht="12.75" customHeight="1">
       <c r="A119" s="45" t="inlineStr">
         <is>
-          <t>Прохорова Маргарита Александровна</t>
+          <t>Хохлов Александр Николаевич</t>
         </is>
       </c>
       <c r="B119" s="46" t="inlineStr">
         <is>
-          <t>07.03.1993</t>
+          <t>21.07.1969</t>
         </is>
       </c>
       <c r="C119" s="47" t="n"/>
       <c r="D119" s="48" t="inlineStr">
         <is>
-          <t>177-840-039 96</t>
+          <t>021-344-684 14</t>
         </is>
       </c>
       <c r="E119" s="49" t="n"/>
       <c r="F119" s="50" t="n"/>
       <c r="G119" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.6.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1</t>
         </is>
       </c>
       <c r="H119" s="49" t="n"/>
       <c r="I119" s="52" t="inlineStr">
         <is>
-          <t>Кладовщик</t>
+          <t>Кладовщик-комплектовщик</t>
         </is>
       </c>
       <c r="J119" s="52" t="inlineStr">
@@ -10898,8 +10898,16 @@
       <c r="Q119" s="48" t="n"/>
       <c r="R119" s="49" t="n"/>
       <c r="S119" s="49" t="n"/>
-      <c r="T119" s="49" t="n"/>
-      <c r="U119" s="55" t="n"/>
+      <c r="T119" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U119" s="55" t="inlineStr">
+        <is>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+        </is>
+      </c>
       <c r="V119" s="49" t="n"/>
       <c r="W119" s="49" t="n"/>
       <c r="X119" s="48" t="n"/>
@@ -10941,36 +10949,36 @@
     <row r="120" ht="12.75" customHeight="1">
       <c r="A120" s="45" t="inlineStr">
         <is>
-          <t>Султанов Тимур Боирович</t>
+          <t>Бугаев Сергей Петрович</t>
         </is>
       </c>
       <c r="B120" s="46" t="inlineStr">
         <is>
-          <t>16.09.1995</t>
+          <t>28.03.1961</t>
         </is>
       </c>
       <c r="C120" s="47" t="n"/>
       <c r="D120" s="48" t="inlineStr">
         <is>
-          <t>175-804-278 91</t>
+          <t>013-828-060 30</t>
         </is>
       </c>
       <c r="E120" s="49" t="n"/>
       <c r="F120" s="50" t="n"/>
       <c r="G120" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.6.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H120" s="49" t="n"/>
       <c r="I120" s="52" t="inlineStr">
         <is>
-          <t>Кладовщик</t>
+          <t>Слесарь механосборочных работ 6 разряда</t>
         </is>
       </c>
       <c r="J120" s="52" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Слесарный участок МШ</t>
         </is>
       </c>
       <c r="K120" s="53" t="n"/>
@@ -11025,36 +11033,36 @@
     <row r="121" ht="12.75" customHeight="1">
       <c r="A121" s="45" t="inlineStr">
         <is>
-          <t>Хохлов Александр Николаевич</t>
+          <t>Виноградов Валерий Валерьевич</t>
         </is>
       </c>
       <c r="B121" s="46" t="inlineStr">
         <is>
-          <t>21.07.1969</t>
+          <t>01.09.1967</t>
         </is>
       </c>
       <c r="C121" s="47" t="n"/>
       <c r="D121" s="48" t="inlineStr">
         <is>
-          <t>021-344-684 14</t>
+          <t>027-155-239 36</t>
         </is>
       </c>
       <c r="E121" s="49" t="n"/>
       <c r="F121" s="50" t="n"/>
       <c r="G121" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H121" s="49" t="n"/>
       <c r="I121" s="52" t="inlineStr">
         <is>
-          <t>Кладовщик-комплектовщик</t>
+          <t>Слесарь механосборочных работ 4 разряда</t>
         </is>
       </c>
       <c r="J121" s="52" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Слесарный участок МШ</t>
         </is>
       </c>
       <c r="K121" s="53" t="n"/>
@@ -11066,16 +11074,8 @@
       <c r="Q121" s="48" t="n"/>
       <c r="R121" s="49" t="n"/>
       <c r="S121" s="49" t="n"/>
-      <c r="T121" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U121" s="55" t="inlineStr">
-        <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
-        </is>
-      </c>
+      <c r="T121" s="49" t="n"/>
+      <c r="U121" s="55" t="n"/>
       <c r="V121" s="49" t="n"/>
       <c r="W121" s="49" t="n"/>
       <c r="X121" s="48" t="n"/>
@@ -11117,18 +11117,18 @@
     <row r="122" ht="12.75" customHeight="1">
       <c r="A122" s="45" t="inlineStr">
         <is>
-          <t>Бугаев Сергей Петрович</t>
+          <t>Епифанов Александр Сергеевич</t>
         </is>
       </c>
       <c r="B122" s="46" t="inlineStr">
         <is>
-          <t>28.03.1961</t>
+          <t>15.08.2000</t>
         </is>
       </c>
       <c r="C122" s="47" t="n"/>
       <c r="D122" s="48" t="inlineStr">
         <is>
-          <t>013-828-060 30</t>
+          <t>125-308-387 41</t>
         </is>
       </c>
       <c r="E122" s="49" t="n"/>
@@ -11141,7 +11141,7 @@
       <c r="H122" s="49" t="n"/>
       <c r="I122" s="52" t="inlineStr">
         <is>
-          <t>Слесарь механосборочных работ 6 разряда</t>
+          <t>Слесарь механосборочных работ 5 разряда</t>
         </is>
       </c>
       <c r="J122" s="52" t="inlineStr">
@@ -11201,18 +11201,18 @@
     <row r="123" ht="12.75" customHeight="1">
       <c r="A123" s="45" t="inlineStr">
         <is>
-          <t>Виноградов Валерий Валерьевич</t>
+          <t>Карантышов Андрей Витальевич</t>
         </is>
       </c>
       <c r="B123" s="46" t="inlineStr">
         <is>
-          <t>01.09.1967</t>
+          <t>25.02.1970</t>
         </is>
       </c>
       <c r="C123" s="47" t="n"/>
       <c r="D123" s="48" t="inlineStr">
         <is>
-          <t>027-155-239 36</t>
+          <t>009-102-880 16</t>
         </is>
       </c>
       <c r="E123" s="49" t="n"/>
@@ -11285,18 +11285,18 @@
     <row r="124" ht="12.75" customHeight="1">
       <c r="A124" s="45" t="inlineStr">
         <is>
-          <t>Епифанов Александр Сергеевич</t>
+          <t>Макаренков Святослав Михайлович</t>
         </is>
       </c>
       <c r="B124" s="46" t="inlineStr">
         <is>
-          <t>15.08.2000</t>
+          <t>19.05.1986</t>
         </is>
       </c>
       <c r="C124" s="47" t="n"/>
       <c r="D124" s="48" t="inlineStr">
         <is>
-          <t>125-308-387 41</t>
+          <t>125-643-377 57</t>
         </is>
       </c>
       <c r="E124" s="49" t="n"/>
@@ -11309,7 +11309,7 @@
       <c r="H124" s="49" t="n"/>
       <c r="I124" s="52" t="inlineStr">
         <is>
-          <t>Слесарь механосборочных работ 5 разряда</t>
+          <t>Слесарь механосборочных работ 6 разряда</t>
         </is>
       </c>
       <c r="J124" s="52" t="inlineStr">
@@ -11369,18 +11369,18 @@
     <row r="125" ht="12.75" customHeight="1">
       <c r="A125" s="45" t="inlineStr">
         <is>
-          <t>Карантышов Андрей Витальевич</t>
+          <t>Рыскин Вадим Вячеславович</t>
         </is>
       </c>
       <c r="B125" s="46" t="inlineStr">
         <is>
-          <t>25.02.1970</t>
+          <t>01.05.1991</t>
         </is>
       </c>
       <c r="C125" s="47" t="n"/>
       <c r="D125" s="48" t="inlineStr">
         <is>
-          <t>009-102-880 16</t>
+          <t>162-290-093 48</t>
         </is>
       </c>
       <c r="E125" s="49" t="n"/>
@@ -11453,18 +11453,18 @@
     <row r="126" ht="12.75" customHeight="1">
       <c r="A126" s="45" t="inlineStr">
         <is>
-          <t>Макаренков Святослав Михайлович</t>
+          <t>Савичев Сергей Сергеевич</t>
         </is>
       </c>
       <c r="B126" s="46" t="inlineStr">
         <is>
-          <t>19.05.1986</t>
+          <t>03.04.1994</t>
         </is>
       </c>
       <c r="C126" s="47" t="n"/>
       <c r="D126" s="48" t="inlineStr">
         <is>
-          <t>125-643-377 57</t>
+          <t>178-876-680 60</t>
         </is>
       </c>
       <c r="E126" s="49" t="n"/>
@@ -11537,18 +11537,18 @@
     <row r="127" ht="12.75" customHeight="1">
       <c r="A127" s="45" t="inlineStr">
         <is>
-          <t>Рыскин Вадим Вячеславович</t>
+          <t>Сафонов Роман Валерьевич</t>
         </is>
       </c>
       <c r="B127" s="46" t="inlineStr">
         <is>
-          <t>01.05.1991</t>
+          <t>05.03.1977</t>
         </is>
       </c>
       <c r="C127" s="47" t="n"/>
       <c r="D127" s="48" t="inlineStr">
         <is>
-          <t>162-290-093 48</t>
+          <t>037-650-815 64</t>
         </is>
       </c>
       <c r="E127" s="49" t="n"/>
@@ -11561,7 +11561,7 @@
       <c r="H127" s="49" t="n"/>
       <c r="I127" s="52" t="inlineStr">
         <is>
-          <t>Слесарь механосборочных работ 4 разряда</t>
+          <t>Слесарь механосборочных работ 6 разряда</t>
         </is>
       </c>
       <c r="J127" s="52" t="inlineStr">
@@ -11621,18 +11621,18 @@
     <row r="128" ht="12.75" customHeight="1">
       <c r="A128" s="45" t="inlineStr">
         <is>
-          <t>Савичев Сергей Сергеевич</t>
+          <t>Семененко Александр Михайлович</t>
         </is>
       </c>
       <c r="B128" s="46" t="inlineStr">
         <is>
-          <t>03.04.1994</t>
+          <t>14.12.1978</t>
         </is>
       </c>
       <c r="C128" s="47" t="n"/>
       <c r="D128" s="48" t="inlineStr">
         <is>
-          <t>178-876-680 60</t>
+          <t>072-837-641 87</t>
         </is>
       </c>
       <c r="E128" s="49" t="n"/>
@@ -11645,7 +11645,7 @@
       <c r="H128" s="49" t="n"/>
       <c r="I128" s="52" t="inlineStr">
         <is>
-          <t>Слесарь механосборочных работ 6 разряда</t>
+          <t>Слесарь механосборочных работ 5 разряда</t>
         </is>
       </c>
       <c r="J128" s="52" t="inlineStr">
@@ -11705,18 +11705,18 @@
     <row r="129" ht="12.75" customHeight="1">
       <c r="A129" s="45" t="inlineStr">
         <is>
-          <t>Сафонов Роман Валерьевич</t>
+          <t>Сорокин Игорь Анатольевич</t>
         </is>
       </c>
       <c r="B129" s="46" t="inlineStr">
         <is>
-          <t>05.03.1977</t>
+          <t>24.11.1959</t>
         </is>
       </c>
       <c r="C129" s="47" t="n"/>
       <c r="D129" s="48" t="inlineStr">
         <is>
-          <t>037-650-815 64</t>
+          <t>019-127-850 48</t>
         </is>
       </c>
       <c r="E129" s="49" t="n"/>
@@ -11729,7 +11729,7 @@
       <c r="H129" s="49" t="n"/>
       <c r="I129" s="52" t="inlineStr">
         <is>
-          <t>Слесарь механосборочных работ 6 разряда</t>
+          <t>Слесарь механосборочных работ 5 разряда</t>
         </is>
       </c>
       <c r="J129" s="52" t="inlineStr">
@@ -11789,18 +11789,18 @@
     <row r="130" ht="12.75" customHeight="1">
       <c r="A130" s="45" t="inlineStr">
         <is>
-          <t>Семененко Александр Михайлович</t>
+          <t>Терёхин Кирилл Павлович</t>
         </is>
       </c>
       <c r="B130" s="46" t="inlineStr">
         <is>
-          <t>14.12.1978</t>
+          <t>31.03.2001</t>
         </is>
       </c>
       <c r="C130" s="47" t="n"/>
       <c r="D130" s="48" t="inlineStr">
         <is>
-          <t>072-837-641 87</t>
+          <t>195-688-598 63</t>
         </is>
       </c>
       <c r="E130" s="49" t="n"/>
@@ -11813,7 +11813,7 @@
       <c r="H130" s="49" t="n"/>
       <c r="I130" s="52" t="inlineStr">
         <is>
-          <t>Слесарь механосборочных работ 5 разряда</t>
+          <t>Слесарь механосборочных работ 4 разряда</t>
         </is>
       </c>
       <c r="J130" s="52" t="inlineStr">
@@ -11873,18 +11873,18 @@
     <row r="131" ht="12.75" customHeight="1">
       <c r="A131" s="45" t="inlineStr">
         <is>
-          <t>Сорокин Игорь Анатольевич</t>
+          <t>Филимонов Андрей Владимирович</t>
         </is>
       </c>
       <c r="B131" s="46" t="inlineStr">
         <is>
-          <t>24.11.1959</t>
+          <t>16.05.1986</t>
         </is>
       </c>
       <c r="C131" s="47" t="n"/>
       <c r="D131" s="48" t="inlineStr">
         <is>
-          <t>019-127-850 48</t>
+          <t>119-562-041 56</t>
         </is>
       </c>
       <c r="E131" s="49" t="n"/>
@@ -11897,7 +11897,7 @@
       <c r="H131" s="49" t="n"/>
       <c r="I131" s="52" t="inlineStr">
         <is>
-          <t>Слесарь механосборочных работ 5 разряда</t>
+          <t>Слесарь механосборочных работ 6 разряда</t>
         </is>
       </c>
       <c r="J131" s="52" t="inlineStr">
@@ -11957,36 +11957,36 @@
     <row r="132" ht="12.75" customHeight="1">
       <c r="A132" s="45" t="inlineStr">
         <is>
-          <t>Терёхин Кирилл Павлович</t>
+          <t>Бизюков Сергей Иванович</t>
         </is>
       </c>
       <c r="B132" s="46" t="inlineStr">
         <is>
-          <t>31.03.2001</t>
+          <t>18.06.1971</t>
         </is>
       </c>
       <c r="C132" s="47" t="n"/>
       <c r="D132" s="48" t="inlineStr">
         <is>
-          <t>195-688-598 63</t>
+          <t>003-360-060 81</t>
         </is>
       </c>
       <c r="E132" s="49" t="n"/>
       <c r="F132" s="50" t="n"/>
       <c r="G132" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.2.3, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.6.2, п.9</t>
         </is>
       </c>
       <c r="H132" s="49" t="n"/>
       <c r="I132" s="52" t="inlineStr">
         <is>
-          <t>Слесарь механосборочных работ 4 разряда</t>
+          <t>Электромонтер по ремонту и обслуживанию электрооборудования 5 разряда</t>
         </is>
       </c>
       <c r="J132" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Служба главного инженера МШ</t>
         </is>
       </c>
       <c r="K132" s="53" t="n"/>
@@ -11998,8 +11998,16 @@
       <c r="Q132" s="48" t="n"/>
       <c r="R132" s="49" t="n"/>
       <c r="S132" s="49" t="n"/>
-      <c r="T132" s="49" t="n"/>
-      <c r="U132" s="55" t="n"/>
+      <c r="T132" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U132" s="55" t="inlineStr">
+        <is>
+          <t>п.11 Прил.№2: обслуживание электроустановок предприятия.</t>
+        </is>
+      </c>
       <c r="V132" s="49" t="n"/>
       <c r="W132" s="49" t="n"/>
       <c r="X132" s="48" t="n"/>
@@ -12041,36 +12049,36 @@
     <row r="133" ht="12.75" customHeight="1">
       <c r="A133" s="45" t="inlineStr">
         <is>
-          <t>Филимонов Андрей Владимирович</t>
+          <t>Долженко Александр Сергеевич</t>
         </is>
       </c>
       <c r="B133" s="46" t="inlineStr">
         <is>
-          <t>16.05.1986</t>
+          <t>08.10.1983</t>
         </is>
       </c>
       <c r="C133" s="47" t="n"/>
       <c r="D133" s="48" t="inlineStr">
         <is>
-          <t>119-562-041 56</t>
+          <t>171-022-712 14</t>
         </is>
       </c>
       <c r="E133" s="49" t="n"/>
       <c r="F133" s="50" t="n"/>
       <c r="G133" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.2.3, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.6.2, п.9</t>
         </is>
       </c>
       <c r="H133" s="49" t="n"/>
       <c r="I133" s="52" t="inlineStr">
         <is>
-          <t>Слесарь механосборочных работ 6 разряда</t>
+          <t>Электромонтер по ремонту и обслуживанию электрооборудования 4 разряда</t>
         </is>
       </c>
       <c r="J133" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Служба главного инженера МШ</t>
         </is>
       </c>
       <c r="K133" s="53" t="n"/>
@@ -12082,8 +12090,16 @@
       <c r="Q133" s="48" t="n"/>
       <c r="R133" s="49" t="n"/>
       <c r="S133" s="49" t="n"/>
-      <c r="T133" s="49" t="n"/>
-      <c r="U133" s="55" t="n"/>
+      <c r="T133" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U133" s="55" t="inlineStr">
+        <is>
+          <t>п.11 Прил.№2: обслуживание электроустановок предприятия.</t>
+        </is>
+      </c>
       <c r="V133" s="49" t="n"/>
       <c r="W133" s="49" t="n"/>
       <c r="X133" s="48" t="n"/>
@@ -12125,18 +12141,18 @@
     <row r="134" ht="12.75" customHeight="1">
       <c r="A134" s="45" t="inlineStr">
         <is>
-          <t>Бизюков Сергей Иванович</t>
+          <t>Жусев Алексей Анатольевич</t>
         </is>
       </c>
       <c r="B134" s="46" t="inlineStr">
         <is>
-          <t>18.06.1971</t>
+          <t>07.01.1974</t>
         </is>
       </c>
       <c r="C134" s="47" t="n"/>
       <c r="D134" s="48" t="inlineStr">
         <is>
-          <t>003-360-060 81</t>
+          <t>001-565-599 28</t>
         </is>
       </c>
       <c r="E134" s="49" t="n"/>
@@ -12149,7 +12165,7 @@
       <c r="H134" s="49" t="n"/>
       <c r="I134" s="52" t="inlineStr">
         <is>
-          <t>Электромонтер по ремонту и обслуживанию электрооборудования 5 разряда</t>
+          <t>Инженер-электрик</t>
         </is>
       </c>
       <c r="J134" s="52" t="inlineStr">
@@ -12217,31 +12233,31 @@
     <row r="135" ht="12.75" customHeight="1">
       <c r="A135" s="45" t="inlineStr">
         <is>
-          <t>Грачев Андрей Николаевич</t>
+          <t>Иванов Андрей Петрович</t>
         </is>
       </c>
       <c r="B135" s="46" t="inlineStr">
         <is>
-          <t>02.02.1982</t>
+          <t>06.01.1977</t>
         </is>
       </c>
       <c r="C135" s="47" t="n"/>
       <c r="D135" s="48" t="inlineStr">
         <is>
-          <t>117-128-099 40</t>
+          <t>220-998-823 95</t>
         </is>
       </c>
       <c r="E135" s="49" t="n"/>
       <c r="F135" s="50" t="n"/>
       <c r="G135" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.4, п.5.1, п.6.2, п.15</t>
+          <t>п.4.3.1, п.4.4, п.4.7, п.4.8, п.5.1, п.6.1</t>
         </is>
       </c>
       <c r="H135" s="49" t="n"/>
       <c r="I135" s="52" t="inlineStr">
         <is>
-          <t>Слесарь-ремонтник 5 разряда</t>
+          <t>Рабочий по комплексному обслуживанию и ремонту зданий 3 разряда</t>
         </is>
       </c>
       <c r="J135" s="52" t="inlineStr">
@@ -12301,31 +12317,31 @@
     <row r="136" ht="12.75" customHeight="1">
       <c r="A136" s="45" t="inlineStr">
         <is>
-          <t>Долженко Александр Сергеевич</t>
+          <t>Иванов Владимир Максимович</t>
         </is>
       </c>
       <c r="B136" s="46" t="inlineStr">
         <is>
-          <t>08.10.1983</t>
+          <t>17.09.2002</t>
         </is>
       </c>
       <c r="C136" s="47" t="n"/>
       <c r="D136" s="48" t="inlineStr">
         <is>
-          <t>171-022-712 14</t>
+          <t>212-785-886 87</t>
         </is>
       </c>
       <c r="E136" s="49" t="n"/>
       <c r="F136" s="50" t="n"/>
       <c r="G136" s="51" t="inlineStr">
         <is>
-          <t>п.4.2.3, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.6.2, п.9</t>
+          <t>п.4.3.1, п.4.4, п.4.7, п.4.8, п.5.1, п.6.1</t>
         </is>
       </c>
       <c r="H136" s="49" t="n"/>
       <c r="I136" s="52" t="inlineStr">
         <is>
-          <t>Электромонтер по ремонту и обслуживанию электрооборудования 4 разряда</t>
+          <t>Рабочий по комплексному обслуживанию и ремонту зданий 3 разряда</t>
         </is>
       </c>
       <c r="J136" s="52" t="inlineStr">
@@ -12342,16 +12358,8 @@
       <c r="Q136" s="48" t="n"/>
       <c r="R136" s="49" t="n"/>
       <c r="S136" s="49" t="n"/>
-      <c r="T136" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U136" s="55" t="inlineStr">
-        <is>
-          <t>п.11 Прил.№2: обслуживание электроустановок предприятия.</t>
-        </is>
-      </c>
+      <c r="T136" s="49" t="n"/>
+      <c r="U136" s="55" t="n"/>
       <c r="V136" s="49" t="n"/>
       <c r="W136" s="49" t="n"/>
       <c r="X136" s="48" t="n"/>
@@ -12393,31 +12401,31 @@
     <row r="137" ht="12.75" customHeight="1">
       <c r="A137" s="45" t="inlineStr">
         <is>
-          <t>Жусев Алексей Анатольевич</t>
+          <t>Калинин Дмитрий Александрович</t>
         </is>
       </c>
       <c r="B137" s="46" t="inlineStr">
         <is>
-          <t>07.01.1974</t>
+          <t>31.05.1984</t>
         </is>
       </c>
       <c r="C137" s="47" t="n"/>
       <c r="D137" s="48" t="inlineStr">
         <is>
-          <t>001-565-599 28</t>
+          <t>106-022-515 91</t>
         </is>
       </c>
       <c r="E137" s="49" t="n"/>
       <c r="F137" s="50" t="n"/>
       <c r="G137" s="51" t="inlineStr">
         <is>
-          <t>п.4.2.3, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.6.2, п.9</t>
+          <t>п.4.4, п.5.2, п.6.2</t>
         </is>
       </c>
       <c r="H137" s="49" t="n"/>
       <c r="I137" s="52" t="inlineStr">
         <is>
-          <t>Инженер-электрик</t>
+          <t>Главный энергетик</t>
         </is>
       </c>
       <c r="J137" s="52" t="inlineStr">
@@ -12441,7 +12449,7 @@
       </c>
       <c r="U137" s="55" t="inlineStr">
         <is>
-          <t>п.11 Прил.№2: обслуживание электроустановок предприятия.</t>
+          <t>п.11–12 Прил.№2: электроустановки и объекты теплоснабжения.</t>
         </is>
       </c>
       <c r="V137" s="49" t="n"/>
@@ -12485,31 +12493,31 @@
     <row r="138" ht="12.75" customHeight="1">
       <c r="A138" s="45" t="inlineStr">
         <is>
-          <t>Иванов Андрей Петрович</t>
+          <t>Кармазин Александр Николаевич</t>
         </is>
       </c>
       <c r="B138" s="46" t="inlineStr">
         <is>
-          <t>06.01.1977</t>
+          <t>07.07.1987</t>
         </is>
       </c>
       <c r="C138" s="47" t="n"/>
       <c r="D138" s="48" t="inlineStr">
         <is>
-          <t>220-998-823 95</t>
+          <t>210-586-598 60</t>
         </is>
       </c>
       <c r="E138" s="49" t="n"/>
       <c r="F138" s="50" t="n"/>
       <c r="G138" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.4, п.4.7, п.4.8, п.5.1, п.6.1</t>
+          <t>п.4.3.1, п.4.4, п.5.1, п.5.2, п.6.2</t>
         </is>
       </c>
       <c r="H138" s="49" t="n"/>
       <c r="I138" s="52" t="inlineStr">
         <is>
-          <t>Рабочий по комплексному обслуживанию и ремонту зданий 3 разряда</t>
+          <t>Инженер по эксплуатации зданий и сооружений</t>
         </is>
       </c>
       <c r="J138" s="52" t="inlineStr">
@@ -12569,31 +12577,31 @@
     <row r="139" ht="12.75" customHeight="1">
       <c r="A139" s="45" t="inlineStr">
         <is>
-          <t>Иванов Владимир Максимович</t>
+          <t>Климов Дмитрий Николаевич</t>
         </is>
       </c>
       <c r="B139" s="46" t="inlineStr">
         <is>
-          <t>17.09.2002</t>
+          <t>05.04.1975</t>
         </is>
       </c>
       <c r="C139" s="47" t="n"/>
       <c r="D139" s="48" t="inlineStr">
         <is>
-          <t>212-785-886 87</t>
+          <t>052-280-369 35</t>
         </is>
       </c>
       <c r="E139" s="49" t="n"/>
       <c r="F139" s="50" t="n"/>
       <c r="G139" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.4, п.4.7, п.4.8, п.5.1, п.6.1</t>
+          <t>п.4.2.3, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.6.2, п.9</t>
         </is>
       </c>
       <c r="H139" s="49" t="n"/>
       <c r="I139" s="52" t="inlineStr">
         <is>
-          <t>Рабочий по комплексному обслуживанию и ремонту зданий 3 разряда</t>
+          <t>Электромонтер по ремонту и обслуживанию электрооборудования 4 разряда</t>
         </is>
       </c>
       <c r="J139" s="52" t="inlineStr">
@@ -12610,8 +12618,16 @@
       <c r="Q139" s="48" t="n"/>
       <c r="R139" s="49" t="n"/>
       <c r="S139" s="49" t="n"/>
-      <c r="T139" s="49" t="n"/>
-      <c r="U139" s="55" t="n"/>
+      <c r="T139" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U139" s="55" t="inlineStr">
+        <is>
+          <t>п.11 Прил.№2: обслуживание электроустановок предприятия.</t>
+        </is>
+      </c>
       <c r="V139" s="49" t="n"/>
       <c r="W139" s="49" t="n"/>
       <c r="X139" s="48" t="n"/>
@@ -12653,31 +12669,31 @@
     <row r="140" ht="12.75" customHeight="1">
       <c r="A140" s="45" t="inlineStr">
         <is>
-          <t>Калинин Дмитрий Александрович</t>
+          <t>Королев Владислав Владимирович</t>
         </is>
       </c>
       <c r="B140" s="46" t="inlineStr">
         <is>
-          <t>31.05.1984</t>
+          <t>22.09.2000</t>
         </is>
       </c>
       <c r="C140" s="47" t="n"/>
       <c r="D140" s="48" t="inlineStr">
         <is>
-          <t>106-022-515 91</t>
+          <t>141-523-358 26</t>
         </is>
       </c>
       <c r="E140" s="49" t="n"/>
       <c r="F140" s="50" t="n"/>
       <c r="G140" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.2, п.6.2</t>
+          <t>п.4.3.1, п.4.4, п.4.7, п.4.8, п.5.1, п.6.1</t>
         </is>
       </c>
       <c r="H140" s="49" t="n"/>
       <c r="I140" s="52" t="inlineStr">
         <is>
-          <t>Главный энергетик</t>
+          <t>Разнорабочий</t>
         </is>
       </c>
       <c r="J140" s="52" t="inlineStr">
@@ -12694,16 +12710,8 @@
       <c r="Q140" s="48" t="n"/>
       <c r="R140" s="49" t="n"/>
       <c r="S140" s="49" t="n"/>
-      <c r="T140" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U140" s="55" t="inlineStr">
-        <is>
-          <t>п.11–12 Прил.№2: электроустановки и объекты теплоснабжения.</t>
-        </is>
-      </c>
+      <c r="T140" s="49" t="n"/>
+      <c r="U140" s="55" t="n"/>
       <c r="V140" s="49" t="n"/>
       <c r="W140" s="49" t="n"/>
       <c r="X140" s="48" t="n"/>
@@ -12745,31 +12753,31 @@
     <row r="141" ht="12.75" customHeight="1">
       <c r="A141" s="45" t="inlineStr">
         <is>
-          <t>Кармазин Александр Николаевич</t>
+          <t>Найденов Андрей Александрович</t>
         </is>
       </c>
       <c r="B141" s="46" t="inlineStr">
         <is>
-          <t>07.07.1987</t>
+          <t>24.02.2002</t>
         </is>
       </c>
       <c r="C141" s="47" t="n"/>
       <c r="D141" s="48" t="inlineStr">
         <is>
-          <t>210-586-598 60</t>
+          <t>192-312-367 53</t>
         </is>
       </c>
       <c r="E141" s="49" t="n"/>
       <c r="F141" s="50" t="n"/>
       <c r="G141" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.4, п.5.1, п.5.2, п.6.2</t>
+          <t>п.4.3.1, п.4.4, п.4.7, п.4.8, п.5.1, п.6.1</t>
         </is>
       </c>
       <c r="H141" s="49" t="n"/>
       <c r="I141" s="52" t="inlineStr">
         <is>
-          <t>Инженер по эксплуатации зданий и сооружений</t>
+          <t>Рабочий по комплексному обслуживанию и ремонту зданий 3 разряда</t>
         </is>
       </c>
       <c r="J141" s="52" t="inlineStr">
@@ -12829,31 +12837,31 @@
     <row r="142" ht="12.75" customHeight="1">
       <c r="A142" s="45" t="inlineStr">
         <is>
-          <t>Климов Дмитрий Николаевич</t>
+          <t>Омельченко Вячеслав Васильевич</t>
         </is>
       </c>
       <c r="B142" s="46" t="inlineStr">
         <is>
-          <t>05.04.1975</t>
+          <t>27.07.1972</t>
         </is>
       </c>
       <c r="C142" s="47" t="n"/>
       <c r="D142" s="48" t="inlineStr">
         <is>
-          <t>052-280-369 35</t>
+          <t>004-366-161 15</t>
         </is>
       </c>
       <c r="E142" s="49" t="n"/>
       <c r="F142" s="50" t="n"/>
       <c r="G142" s="51" t="inlineStr">
         <is>
-          <t>п.4.2.3, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.6.2, п.9</t>
+          <t>п.4.3.1, п.4.4, п.4.7, п.4.8, п.5.1, п.6.1</t>
         </is>
       </c>
       <c r="H142" s="49" t="n"/>
       <c r="I142" s="52" t="inlineStr">
         <is>
-          <t>Электромонтер по ремонту и обслуживанию электрооборудования 4 разряда</t>
+          <t>Разнорабочий</t>
         </is>
       </c>
       <c r="J142" s="52" t="inlineStr">
@@ -12870,16 +12878,8 @@
       <c r="Q142" s="48" t="n"/>
       <c r="R142" s="49" t="n"/>
       <c r="S142" s="49" t="n"/>
-      <c r="T142" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U142" s="55" t="inlineStr">
-        <is>
-          <t>п.11 Прил.№2: обслуживание электроустановок предприятия.</t>
-        </is>
-      </c>
+      <c r="T142" s="49" t="n"/>
+      <c r="U142" s="55" t="n"/>
       <c r="V142" s="49" t="n"/>
       <c r="W142" s="49" t="n"/>
       <c r="X142" s="48" t="n"/>
@@ -12921,31 +12921,31 @@
     <row r="143" ht="12.75" customHeight="1">
       <c r="A143" s="45" t="inlineStr">
         <is>
-          <t>Королев Владислав Владимирович</t>
+          <t>Старовойтов Владимир Владимирович</t>
         </is>
       </c>
       <c r="B143" s="46" t="inlineStr">
         <is>
-          <t>22.09.2000</t>
+          <t>07.06.1990</t>
         </is>
       </c>
       <c r="C143" s="47" t="n"/>
       <c r="D143" s="48" t="inlineStr">
         <is>
-          <t>141-523-358 26</t>
+          <t>198-503-440 98</t>
         </is>
       </c>
       <c r="E143" s="49" t="n"/>
       <c r="F143" s="50" t="n"/>
       <c r="G143" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.4, п.4.7, п.4.8, п.5.1, п.6.1</t>
+          <t>п.4.4, п.5.2, п.6.2</t>
         </is>
       </c>
       <c r="H143" s="49" t="n"/>
       <c r="I143" s="52" t="inlineStr">
         <is>
-          <t>Разнорабочий</t>
+          <t>Главный механик</t>
         </is>
       </c>
       <c r="J143" s="52" t="inlineStr">
@@ -13005,31 +13005,31 @@
     <row r="144" ht="12.75" customHeight="1">
       <c r="A144" s="45" t="inlineStr">
         <is>
-          <t>Найденов Андрей Александрович</t>
+          <t>Трушаков Владимир Александрович</t>
         </is>
       </c>
       <c r="B144" s="46" t="inlineStr">
         <is>
-          <t>24.02.2002</t>
+          <t>14.07.1958</t>
         </is>
       </c>
       <c r="C144" s="47" t="n"/>
       <c r="D144" s="48" t="inlineStr">
         <is>
-          <t>192-312-367 53</t>
+          <t>024-184-963 47</t>
         </is>
       </c>
       <c r="E144" s="49" t="n"/>
       <c r="F144" s="50" t="n"/>
       <c r="G144" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.4, п.4.7, п.4.8, п.5.1, п.6.1</t>
+          <t>п.1.50, п.4.3.2, п.4.4, п.4.7, п.4.8, п.5.1, п.5.2, п.6.2, п.15</t>
         </is>
       </c>
       <c r="H144" s="49" t="n"/>
       <c r="I144" s="52" t="inlineStr">
         <is>
-          <t>Рабочий по комплексному обслуживанию и ремонту зданий 3 разряда</t>
+          <t>Механик</t>
         </is>
       </c>
       <c r="J144" s="52" t="inlineStr">
@@ -13089,31 +13089,31 @@
     <row r="145" ht="12.75" customHeight="1">
       <c r="A145" s="45" t="inlineStr">
         <is>
-          <t>Омельченко Вячеслав Васильевич</t>
+          <t>Хромов Павел Николаевич</t>
         </is>
       </c>
       <c r="B145" s="46" t="inlineStr">
         <is>
-          <t>27.07.1972</t>
+          <t>18.04.1963</t>
         </is>
       </c>
       <c r="C145" s="47" t="n"/>
       <c r="D145" s="48" t="inlineStr">
         <is>
-          <t>004-366-161 15</t>
+          <t>023-445-725 30</t>
         </is>
       </c>
       <c r="E145" s="49" t="n"/>
       <c r="F145" s="50" t="n"/>
       <c r="G145" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.4, п.4.7, п.4.8, п.5.1, п.6.1</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.4.6, п.5.1, п.6.2</t>
         </is>
       </c>
       <c r="H145" s="49" t="n"/>
       <c r="I145" s="52" t="inlineStr">
         <is>
-          <t>Разнорабочий</t>
+          <t>Механик-наладчик</t>
         </is>
       </c>
       <c r="J145" s="52" t="inlineStr">
@@ -13173,36 +13173,36 @@
     <row r="146" ht="12.75" customHeight="1">
       <c r="A146" s="45" t="inlineStr">
         <is>
-          <t>Старовойтов Владимир Владимирович</t>
+          <t>Богданов Александр Викторович</t>
         </is>
       </c>
       <c r="B146" s="46" t="inlineStr">
         <is>
-          <t>07.06.1990</t>
+          <t>09.09.1989</t>
         </is>
       </c>
       <c r="C146" s="47" t="n"/>
       <c r="D146" s="48" t="inlineStr">
         <is>
-          <t>198-503-440 98</t>
+          <t>105-875-041 55</t>
         </is>
       </c>
       <c r="E146" s="49" t="n"/>
       <c r="F146" s="50" t="n"/>
       <c r="G146" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.2, п.6.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.4.9, п.5.1, п.5.2, п.6.2, п.9</t>
         </is>
       </c>
       <c r="H146" s="49" t="n"/>
       <c r="I146" s="52" t="inlineStr">
         <is>
-          <t>Главный механик</t>
+          <t>Электромонтажник 5 разряда</t>
         </is>
       </c>
       <c r="J146" s="52" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Участок РЭО МШ</t>
         </is>
       </c>
       <c r="K146" s="53" t="n"/>
@@ -13214,8 +13214,16 @@
       <c r="Q146" s="48" t="n"/>
       <c r="R146" s="49" t="n"/>
       <c r="S146" s="49" t="n"/>
-      <c r="T146" s="49" t="n"/>
-      <c r="U146" s="55" t="n"/>
+      <c r="T146" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U146" s="55" t="inlineStr">
+        <is>
+          <t>п.11 Прил.№2: монтаж, наладка, техническое обслуживание, ремонт электроустановок.</t>
+        </is>
+      </c>
       <c r="V146" s="49" t="n"/>
       <c r="W146" s="49" t="n"/>
       <c r="X146" s="48" t="n"/>
@@ -13257,36 +13265,36 @@
     <row r="147" ht="12.75" customHeight="1">
       <c r="A147" s="45" t="inlineStr">
         <is>
-          <t>Трушаков Владимир Александрович</t>
+          <t>Озорнов Игорь Валерьевич</t>
         </is>
       </c>
       <c r="B147" s="46" t="inlineStr">
         <is>
-          <t>14.07.1958</t>
+          <t>28.06.1976</t>
         </is>
       </c>
       <c r="C147" s="47" t="n"/>
       <c r="D147" s="48" t="inlineStr">
         <is>
-          <t>024-184-963 47</t>
+          <t>097-033-687 88</t>
         </is>
       </c>
       <c r="E147" s="49" t="n"/>
       <c r="F147" s="50" t="n"/>
       <c r="G147" s="51" t="inlineStr">
         <is>
-          <t>п.1.50, п.4.3.2, п.4.4, п.4.7, п.4.8, п.5.1, п.5.2, п.6.2, п.15</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.4.9, п.5.1, п.5.2, п.6.2, п.9</t>
         </is>
       </c>
       <c r="H147" s="49" t="n"/>
       <c r="I147" s="52" t="inlineStr">
         <is>
-          <t>Механик</t>
+          <t>Электромонтажник 5 разряда</t>
         </is>
       </c>
       <c r="J147" s="52" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Участок РЭО МШ</t>
         </is>
       </c>
       <c r="K147" s="53" t="n"/>
@@ -13298,8 +13306,16 @@
       <c r="Q147" s="48" t="n"/>
       <c r="R147" s="49" t="n"/>
       <c r="S147" s="49" t="n"/>
-      <c r="T147" s="49" t="n"/>
-      <c r="U147" s="55" t="n"/>
+      <c r="T147" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U147" s="55" t="inlineStr">
+        <is>
+          <t>п.11 Прил.№2: монтаж, наладка, техническое обслуживание, ремонт электроустановок.</t>
+        </is>
+      </c>
       <c r="V147" s="49" t="n"/>
       <c r="W147" s="49" t="n"/>
       <c r="X147" s="48" t="n"/>
@@ -13341,36 +13357,36 @@
     <row r="148" ht="12.75" customHeight="1">
       <c r="A148" s="45" t="inlineStr">
         <is>
-          <t>Хромов Павел Николаевич</t>
+          <t>Романов Дмитрий Евгеньевич</t>
         </is>
       </c>
       <c r="B148" s="46" t="inlineStr">
         <is>
-          <t>18.04.1963</t>
+          <t>16.10.1967</t>
         </is>
       </c>
       <c r="C148" s="47" t="n"/>
       <c r="D148" s="48" t="inlineStr">
         <is>
-          <t>023-445-725 30</t>
+          <t>038-809-902 92</t>
         </is>
       </c>
       <c r="E148" s="49" t="n"/>
       <c r="F148" s="50" t="n"/>
       <c r="G148" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.4.6, п.5.1, п.6.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.4.9, п.5.1, п.5.2, п.6.2, п.9</t>
         </is>
       </c>
       <c r="H148" s="49" t="n"/>
       <c r="I148" s="52" t="inlineStr">
         <is>
-          <t>Механик-наладчик</t>
+          <t>Электромонтажник 5 разряда</t>
         </is>
       </c>
       <c r="J148" s="52" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Участок РЭО МШ</t>
         </is>
       </c>
       <c r="K148" s="53" t="n"/>
@@ -13382,8 +13398,16 @@
       <c r="Q148" s="48" t="n"/>
       <c r="R148" s="49" t="n"/>
       <c r="S148" s="49" t="n"/>
-      <c r="T148" s="49" t="n"/>
-      <c r="U148" s="55" t="n"/>
+      <c r="T148" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U148" s="55" t="inlineStr">
+        <is>
+          <t>п.11 Прил.№2: монтаж, наладка, техническое обслуживание, ремонт электроустановок.</t>
+        </is>
+      </c>
       <c r="V148" s="49" t="n"/>
       <c r="W148" s="49" t="n"/>
       <c r="X148" s="48" t="n"/>
@@ -13425,18 +13449,18 @@
     <row r="149" ht="12.75" customHeight="1">
       <c r="A149" s="45" t="inlineStr">
         <is>
-          <t>Богданов Александр Викторович</t>
+          <t>Шабалин Александр Сергеевич</t>
         </is>
       </c>
       <c r="B149" s="46" t="inlineStr">
         <is>
-          <t>09.09.1989</t>
+          <t>16.01.1963</t>
         </is>
       </c>
       <c r="C149" s="47" t="n"/>
       <c r="D149" s="48" t="inlineStr">
         <is>
-          <t>105-875-041 55</t>
+          <t>192-436-177 81</t>
         </is>
       </c>
       <c r="E149" s="49" t="n"/>
@@ -13517,36 +13541,36 @@
     <row r="150" ht="12.75" customHeight="1">
       <c r="A150" s="45" t="inlineStr">
         <is>
-          <t>Озорнов Игорь Валерьевич</t>
+          <t>Алманова Дойна Виореловна</t>
         </is>
       </c>
       <c r="B150" s="46" t="inlineStr">
         <is>
-          <t>28.06.1976</t>
+          <t>11.06.1974</t>
         </is>
       </c>
       <c r="C150" s="47" t="n"/>
       <c r="D150" s="48" t="inlineStr">
         <is>
-          <t>097-033-687 88</t>
+          <t>063-582-034 56</t>
         </is>
       </c>
       <c r="E150" s="49" t="n"/>
       <c r="F150" s="50" t="n"/>
       <c r="G150" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.4.9, п.5.1, п.5.2, п.6.2, п.9</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H150" s="49" t="n"/>
       <c r="I150" s="52" t="inlineStr">
         <is>
-          <t>Электромонтажник 5 разряда</t>
+          <t>Облицовщик деталей мебели 4 разряда</t>
         </is>
       </c>
       <c r="J150" s="52" t="inlineStr">
         <is>
-          <t>Участок РЭО МШ</t>
+          <t>Участок декоративной отделки МШ</t>
         </is>
       </c>
       <c r="K150" s="53" t="n"/>
@@ -13558,16 +13582,8 @@
       <c r="Q150" s="48" t="n"/>
       <c r="R150" s="49" t="n"/>
       <c r="S150" s="49" t="n"/>
-      <c r="T150" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U150" s="55" t="inlineStr">
-        <is>
-          <t>п.11 Прил.№2: монтаж, наладка, техническое обслуживание, ремонт электроустановок.</t>
-        </is>
-      </c>
+      <c r="T150" s="49" t="n"/>
+      <c r="U150" s="55" t="n"/>
       <c r="V150" s="49" t="n"/>
       <c r="W150" s="49" t="n"/>
       <c r="X150" s="48" t="n"/>
@@ -13609,36 +13625,36 @@
     <row r="151" ht="12.75" customHeight="1">
       <c r="A151" s="45" t="inlineStr">
         <is>
-          <t>Романов Дмитрий Евгеньевич</t>
+          <t>Габбасов Евгений Рафисович</t>
         </is>
       </c>
       <c r="B151" s="46" t="inlineStr">
         <is>
-          <t>16.10.1967</t>
+          <t>11.10.1984</t>
         </is>
       </c>
       <c r="C151" s="47" t="n"/>
       <c r="D151" s="48" t="inlineStr">
         <is>
-          <t>038-809-902 92</t>
+          <t>071-662-070 50</t>
         </is>
       </c>
       <c r="E151" s="49" t="n"/>
       <c r="F151" s="50" t="n"/>
       <c r="G151" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.4.9, п.5.1, п.5.2, п.6.2, п.9</t>
+          <t>п.4.4, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="H151" s="49" t="n"/>
       <c r="I151" s="52" t="inlineStr">
         <is>
-          <t>Электромонтажник 5 разряда</t>
+          <t>Бригадир</t>
         </is>
       </c>
       <c r="J151" s="52" t="inlineStr">
         <is>
-          <t>Участок РЭО МШ</t>
+          <t>Участок декоративной отделки МШ</t>
         </is>
       </c>
       <c r="K151" s="53" t="n"/>
@@ -13650,16 +13666,8 @@
       <c r="Q151" s="48" t="n"/>
       <c r="R151" s="49" t="n"/>
       <c r="S151" s="49" t="n"/>
-      <c r="T151" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U151" s="55" t="inlineStr">
-        <is>
-          <t>п.11 Прил.№2: монтаж, наладка, техническое обслуживание, ремонт электроустановок.</t>
-        </is>
-      </c>
+      <c r="T151" s="49" t="n"/>
+      <c r="U151" s="55" t="n"/>
       <c r="V151" s="49" t="n"/>
       <c r="W151" s="49" t="n"/>
       <c r="X151" s="48" t="n"/>
@@ -13701,36 +13709,36 @@
     <row r="152" ht="12.75" customHeight="1">
       <c r="A152" s="45" t="inlineStr">
         <is>
-          <t>Шабалин Александр Сергеевич</t>
+          <t>Долинская Валерия Александровна</t>
         </is>
       </c>
       <c r="B152" s="46" t="inlineStr">
         <is>
-          <t>16.01.1963</t>
+          <t>08.08.1973</t>
         </is>
       </c>
       <c r="C152" s="47" t="n"/>
       <c r="D152" s="48" t="inlineStr">
         <is>
-          <t>192-436-177 81</t>
+          <t>042-780-361 49</t>
         </is>
       </c>
       <c r="E152" s="49" t="n"/>
       <c r="F152" s="50" t="n"/>
       <c r="G152" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.4.9, п.5.1, п.5.2, п.6.2, п.9</t>
+          <t>п.1.14.2, п.1.36, п.1.37.1, п.1.45.1, п.1.45.2, п.1.50, п.4.3.1, п.4.4, п.5.1, п.17</t>
         </is>
       </c>
       <c r="H152" s="49" t="n"/>
       <c r="I152" s="52" t="inlineStr">
         <is>
-          <t>Электромонтажник 5 разряда</t>
+          <t>Маляр 4 разряда</t>
         </is>
       </c>
       <c r="J152" s="52" t="inlineStr">
         <is>
-          <t>Участок РЭО МШ</t>
+          <t>Участок декоративной отделки МШ</t>
         </is>
       </c>
       <c r="K152" s="53" t="n"/>
@@ -13742,16 +13750,8 @@
       <c r="Q152" s="48" t="n"/>
       <c r="R152" s="49" t="n"/>
       <c r="S152" s="49" t="n"/>
-      <c r="T152" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U152" s="55" t="inlineStr">
-        <is>
-          <t>п.11 Прил.№2: монтаж, наладка, техническое обслуживание, ремонт электроустановок.</t>
-        </is>
-      </c>
+      <c r="T152" s="49" t="n"/>
+      <c r="U152" s="55" t="n"/>
       <c r="V152" s="49" t="n"/>
       <c r="W152" s="49" t="n"/>
       <c r="X152" s="48" t="n"/>
@@ -13793,31 +13793,31 @@
     <row r="153" ht="12.75" customHeight="1">
       <c r="A153" s="45" t="inlineStr">
         <is>
-          <t>Алманова Дойна Виореловна</t>
+          <t>Калинкин Анатолий Сергеевич</t>
         </is>
       </c>
       <c r="B153" s="46" t="inlineStr">
         <is>
-          <t>11.06.1974</t>
+          <t>14.03.1986</t>
         </is>
       </c>
       <c r="C153" s="47" t="n"/>
       <c r="D153" s="48" t="inlineStr">
         <is>
-          <t>063-582-034 56</t>
+          <t>118-488-714 95</t>
         </is>
       </c>
       <c r="E153" s="49" t="n"/>
       <c r="F153" s="50" t="n"/>
       <c r="G153" s="51" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.4, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="H153" s="49" t="n"/>
       <c r="I153" s="52" t="inlineStr">
         <is>
-          <t>Облицовщик деталей мебели 4 разряда</t>
+          <t>Бригадир</t>
         </is>
       </c>
       <c r="J153" s="52" t="inlineStr">
@@ -13877,31 +13877,31 @@
     <row r="154" ht="12.75" customHeight="1">
       <c r="A154" s="45" t="inlineStr">
         <is>
-          <t>Габбасов Евгений Рафисович</t>
+          <t>Караваев Игорь Александрович</t>
         </is>
       </c>
       <c r="B154" s="46" t="inlineStr">
         <is>
-          <t>11.10.1984</t>
+          <t>04.09.1975</t>
         </is>
       </c>
       <c r="C154" s="47" t="n"/>
       <c r="D154" s="48" t="inlineStr">
         <is>
-          <t>071-662-070 50</t>
+          <t>001-499-520 30</t>
         </is>
       </c>
       <c r="E154" s="49" t="n"/>
       <c r="F154" s="50" t="n"/>
       <c r="G154" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.1.14.2, п.1.36, п.1.37.1, п.1.45.1, п.1.45.2, п.1.50, п.4.3.1, п.4.4, п.5.1, п.17</t>
         </is>
       </c>
       <c r="H154" s="49" t="n"/>
       <c r="I154" s="52" t="inlineStr">
         <is>
-          <t>Бригадир</t>
+          <t>Техник 6 разряда</t>
         </is>
       </c>
       <c r="J154" s="52" t="inlineStr">
@@ -13961,18 +13961,18 @@
     <row r="155" ht="12.75" customHeight="1">
       <c r="A155" s="45" t="inlineStr">
         <is>
-          <t>Долинская Валерия Александровна</t>
+          <t>Китов Алексей Геннадьевич</t>
         </is>
       </c>
       <c r="B155" s="46" t="inlineStr">
         <is>
-          <t>08.08.1973</t>
+          <t>05.04.2003</t>
         </is>
       </c>
       <c r="C155" s="47" t="n"/>
       <c r="D155" s="48" t="inlineStr">
         <is>
-          <t>042-780-361 49</t>
+          <t>172-961-460 90</t>
         </is>
       </c>
       <c r="E155" s="49" t="n"/>
@@ -13985,7 +13985,7 @@
       <c r="H155" s="49" t="n"/>
       <c r="I155" s="52" t="inlineStr">
         <is>
-          <t>Маляр 4 разряда</t>
+          <t>Техник 3 разряда</t>
         </is>
       </c>
       <c r="J155" s="52" t="inlineStr">
@@ -14045,31 +14045,31 @@
     <row r="156" ht="12.75" customHeight="1">
       <c r="A156" s="45" t="inlineStr">
         <is>
-          <t>Калинкин Анатолий Сергеевич</t>
+          <t>Лисовский Александр Валерьевич</t>
         </is>
       </c>
       <c r="B156" s="46" t="inlineStr">
         <is>
-          <t>14.03.1986</t>
+          <t>15.06.1970</t>
         </is>
       </c>
       <c r="C156" s="47" t="n"/>
       <c r="D156" s="48" t="inlineStr">
         <is>
-          <t>118-488-714 95</t>
+          <t>001-428-997 24</t>
         </is>
       </c>
       <c r="E156" s="49" t="n"/>
       <c r="F156" s="50" t="n"/>
       <c r="G156" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.1.14.2, п.1.36, п.1.37.1, п.1.45.1, п.1.45.2, п.1.50, п.4.3.1, п.4.4, п.5.1, п.17</t>
         </is>
       </c>
       <c r="H156" s="49" t="n"/>
       <c r="I156" s="52" t="inlineStr">
         <is>
-          <t>Бригадир</t>
+          <t>Техник 6 разряда</t>
         </is>
       </c>
       <c r="J156" s="52" t="inlineStr">
@@ -14129,18 +14129,18 @@
     <row r="157" ht="12.75" customHeight="1">
       <c r="A157" s="45" t="inlineStr">
         <is>
-          <t>Караваев Игорь Александрович</t>
+          <t>Лысенко Анатолий Алексеевич</t>
         </is>
       </c>
       <c r="B157" s="46" t="inlineStr">
         <is>
-          <t>04.09.1975</t>
+          <t>26.03.1992</t>
         </is>
       </c>
       <c r="C157" s="47" t="n"/>
       <c r="D157" s="48" t="inlineStr">
         <is>
-          <t>001-499-520 30</t>
+          <t>110-851-697 36</t>
         </is>
       </c>
       <c r="E157" s="49" t="n"/>
@@ -14213,31 +14213,31 @@
     <row r="158" ht="12.75" customHeight="1">
       <c r="A158" s="45" t="inlineStr">
         <is>
-          <t>Китов Алексей Геннадьевич</t>
+          <t>Морев Александр Михайлович</t>
         </is>
       </c>
       <c r="B158" s="46" t="inlineStr">
         <is>
-          <t>05.04.2003</t>
+          <t>28.10.1958</t>
         </is>
       </c>
       <c r="C158" s="47" t="n"/>
       <c r="D158" s="48" t="inlineStr">
         <is>
-          <t>172-961-460 90</t>
+          <t>030-708-026 07</t>
         </is>
       </c>
       <c r="E158" s="49" t="n"/>
       <c r="F158" s="50" t="n"/>
       <c r="G158" s="51" t="inlineStr">
         <is>
-          <t>п.1.14.2, п.1.36, п.1.37.1, п.1.45.1, п.1.45.2, п.1.50, п.4.3.1, п.4.4, п.5.1, п.17</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H158" s="49" t="n"/>
       <c r="I158" s="52" t="inlineStr">
         <is>
-          <t>Техник 3 разряда</t>
+          <t>Облицовщик деталей мебели 6 разряда</t>
         </is>
       </c>
       <c r="J158" s="52" t="inlineStr">
@@ -14297,31 +14297,31 @@
     <row r="159" ht="12.75" customHeight="1">
       <c r="A159" s="45" t="inlineStr">
         <is>
-          <t>Лисовский Александр Валерьевич</t>
+          <t>Морев Владимир Александрович</t>
         </is>
       </c>
       <c r="B159" s="46" t="inlineStr">
         <is>
-          <t>15.06.1970</t>
+          <t>15.09.1981</t>
         </is>
       </c>
       <c r="C159" s="47" t="n"/>
       <c r="D159" s="48" t="inlineStr">
         <is>
-          <t>001-428-997 24</t>
+          <t>038-864-601 92</t>
         </is>
       </c>
       <c r="E159" s="49" t="n"/>
       <c r="F159" s="50" t="n"/>
       <c r="G159" s="51" t="inlineStr">
         <is>
-          <t>п.1.14.2, п.1.36, п.1.37.1, п.1.45.1, п.1.45.2, п.1.50, п.4.3.1, п.4.4, п.5.1, п.17</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H159" s="49" t="n"/>
       <c r="I159" s="52" t="inlineStr">
         <is>
-          <t>Техник 6 разряда</t>
+          <t>Облицовщик деталей мебели 6 разряда</t>
         </is>
       </c>
       <c r="J159" s="52" t="inlineStr">
@@ -14381,18 +14381,18 @@
     <row r="160" ht="12.75" customHeight="1">
       <c r="A160" s="45" t="inlineStr">
         <is>
-          <t>Лысенко Анатолий Алексеевич</t>
+          <t>Никитин Марат Николаевич</t>
         </is>
       </c>
       <c r="B160" s="46" t="inlineStr">
         <is>
-          <t>26.03.1992</t>
+          <t>12.05.1992</t>
         </is>
       </c>
       <c r="C160" s="47" t="n"/>
       <c r="D160" s="48" t="inlineStr">
         <is>
-          <t>110-851-697 36</t>
+          <t>118-093-421 46</t>
         </is>
       </c>
       <c r="E160" s="49" t="n"/>
@@ -14405,7 +14405,7 @@
       <c r="H160" s="49" t="n"/>
       <c r="I160" s="52" t="inlineStr">
         <is>
-          <t>Техник 6 разряда</t>
+          <t>Техник 5 разряда</t>
         </is>
       </c>
       <c r="J160" s="52" t="inlineStr">
@@ -14465,31 +14465,31 @@
     <row r="161" ht="12.75" customHeight="1">
       <c r="A161" s="45" t="inlineStr">
         <is>
-          <t>Морев Александр Михайлович</t>
+          <t>Ожерельев Сергей Николаевич</t>
         </is>
       </c>
       <c r="B161" s="46" t="inlineStr">
         <is>
-          <t>28.10.1958</t>
+          <t>02.12.1980</t>
         </is>
       </c>
       <c r="C161" s="47" t="n"/>
       <c r="D161" s="48" t="inlineStr">
         <is>
-          <t>030-708-026 07</t>
+          <t>109-219-547 54</t>
         </is>
       </c>
       <c r="E161" s="49" t="n"/>
       <c r="F161" s="50" t="n"/>
       <c r="G161" s="51" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.1.14.2, п.1.36, п.1.37.1, п.1.45.1, п.1.45.2, п.1.50, п.4.3.1, п.4.4, п.5.1, п.17</t>
         </is>
       </c>
       <c r="H161" s="49" t="n"/>
       <c r="I161" s="52" t="inlineStr">
         <is>
-          <t>Облицовщик деталей мебели 6 разряда</t>
+          <t>Техник 5 разряда</t>
         </is>
       </c>
       <c r="J161" s="52" t="inlineStr">
@@ -14549,31 +14549,31 @@
     <row r="162" ht="12.75" customHeight="1">
       <c r="A162" s="45" t="inlineStr">
         <is>
-          <t>Морев Владимир Александрович</t>
+          <t>Первушин Максим Александрович</t>
         </is>
       </c>
       <c r="B162" s="46" t="inlineStr">
         <is>
-          <t>15.09.1981</t>
+          <t>03.10.1991</t>
         </is>
       </c>
       <c r="C162" s="47" t="n"/>
       <c r="D162" s="48" t="inlineStr">
         <is>
-          <t>038-864-601 92</t>
+          <t>135-651-925 68</t>
         </is>
       </c>
       <c r="E162" s="49" t="n"/>
       <c r="F162" s="50" t="n"/>
       <c r="G162" s="51" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.1.14.2, п.1.36, п.1.37.1, п.1.45.1, п.1.45.2, п.1.50, п.4.3.1, п.4.4, п.5.1, п.17</t>
         </is>
       </c>
       <c r="H162" s="49" t="n"/>
       <c r="I162" s="52" t="inlineStr">
         <is>
-          <t>Облицовщик деталей мебели 6 разряда</t>
+          <t>Техник 6 разряда</t>
         </is>
       </c>
       <c r="J162" s="52" t="inlineStr">
@@ -14633,31 +14633,31 @@
     <row r="163" ht="12.75" customHeight="1">
       <c r="A163" s="45" t="inlineStr">
         <is>
-          <t>Никитин Марат Николаевич</t>
+          <t>Попов Виктор Михайлович</t>
         </is>
       </c>
       <c r="B163" s="46" t="inlineStr">
         <is>
-          <t>12.05.1992</t>
+          <t>13.01.1986</t>
         </is>
       </c>
       <c r="C163" s="47" t="n"/>
       <c r="D163" s="48" t="inlineStr">
         <is>
-          <t>118-093-421 46</t>
+          <t>134-348-484 62</t>
         </is>
       </c>
       <c r="E163" s="49" t="n"/>
       <c r="F163" s="50" t="n"/>
       <c r="G163" s="51" t="inlineStr">
         <is>
-          <t>п.1.14.2, п.1.36, п.1.37.1, п.1.45.1, п.1.45.2, п.1.50, п.4.3.1, п.4.4, п.5.1, п.17</t>
+          <t>п.4.4, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="H163" s="49" t="n"/>
       <c r="I163" s="52" t="inlineStr">
         <is>
-          <t>Техник 5 разряда</t>
+          <t>Мастер участка</t>
         </is>
       </c>
       <c r="J163" s="52" t="inlineStr">
@@ -14717,18 +14717,18 @@
     <row r="164" ht="12.75" customHeight="1">
       <c r="A164" s="45" t="inlineStr">
         <is>
-          <t>Ожерельев Сергей Николаевич</t>
+          <t>Пухова Жанна Аслановна</t>
         </is>
       </c>
       <c r="B164" s="46" t="inlineStr">
         <is>
-          <t>02.12.1980</t>
+          <t>16.05.2002</t>
         </is>
       </c>
       <c r="C164" s="47" t="n"/>
       <c r="D164" s="48" t="inlineStr">
         <is>
-          <t>109-219-547 54</t>
+          <t>187-870-897 52</t>
         </is>
       </c>
       <c r="E164" s="49" t="n"/>
@@ -14741,7 +14741,7 @@
       <c r="H164" s="49" t="n"/>
       <c r="I164" s="52" t="inlineStr">
         <is>
-          <t>Техник 5 разряда</t>
+          <t>Техник 2 разряда</t>
         </is>
       </c>
       <c r="J164" s="52" t="inlineStr">
@@ -14801,18 +14801,18 @@
     <row r="165" ht="12.75" customHeight="1">
       <c r="A165" s="45" t="inlineStr">
         <is>
-          <t>Первушин Максим Александрович</t>
+          <t>Симонова Виктория Александровна</t>
         </is>
       </c>
       <c r="B165" s="46" t="inlineStr">
         <is>
-          <t>03.10.1991</t>
+          <t>09.10.2004</t>
         </is>
       </c>
       <c r="C165" s="47" t="n"/>
       <c r="D165" s="48" t="inlineStr">
         <is>
-          <t>135-651-925 68</t>
+          <t>195-171-820 88</t>
         </is>
       </c>
       <c r="E165" s="49" t="n"/>
@@ -14825,7 +14825,7 @@
       <c r="H165" s="49" t="n"/>
       <c r="I165" s="52" t="inlineStr">
         <is>
-          <t>Техник 6 разряда</t>
+          <t>Маляр 4 разряда</t>
         </is>
       </c>
       <c r="J165" s="52" t="inlineStr">
@@ -14885,31 +14885,31 @@
     <row r="166" ht="12.75" customHeight="1">
       <c r="A166" s="45" t="inlineStr">
         <is>
-          <t>Попов Виктор Михайлович</t>
+          <t>Солодков Максим Юрьевич</t>
         </is>
       </c>
       <c r="B166" s="46" t="inlineStr">
         <is>
-          <t>13.01.1986</t>
+          <t>13.05.1988</t>
         </is>
       </c>
       <c r="C166" s="47" t="n"/>
       <c r="D166" s="48" t="inlineStr">
         <is>
-          <t>134-348-484 62</t>
+          <t>112-495-624 45</t>
         </is>
       </c>
       <c r="E166" s="49" t="n"/>
       <c r="F166" s="50" t="n"/>
       <c r="G166" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.1.14.2, п.1.36, п.1.37.1, п.1.45.1, п.1.45.2, п.1.50, п.4.3.1, п.4.4, п.5.1, п.17</t>
         </is>
       </c>
       <c r="H166" s="49" t="n"/>
       <c r="I166" s="52" t="inlineStr">
         <is>
-          <t>Мастер участка</t>
+          <t>Маляр 6 разряда</t>
         </is>
       </c>
       <c r="J166" s="52" t="inlineStr">
@@ -14969,18 +14969,18 @@
     <row r="167" ht="12.75" customHeight="1">
       <c r="A167" s="45" t="inlineStr">
         <is>
-          <t>Пухова Жанна Аслановна</t>
+          <t>Тимохин Александр Владимирович</t>
         </is>
       </c>
       <c r="B167" s="46" t="inlineStr">
         <is>
-          <t>16.05.2002</t>
+          <t>12.02.1981</t>
         </is>
       </c>
       <c r="C167" s="47" t="n"/>
       <c r="D167" s="48" t="inlineStr">
         <is>
-          <t>187-870-897 52</t>
+          <t>027-659-219 78</t>
         </is>
       </c>
       <c r="E167" s="49" t="n"/>
@@ -14993,7 +14993,7 @@
       <c r="H167" s="49" t="n"/>
       <c r="I167" s="52" t="inlineStr">
         <is>
-          <t>Техник 2 разряда</t>
+          <t>Техник 4 разряда</t>
         </is>
       </c>
       <c r="J167" s="52" t="inlineStr">
@@ -15053,36 +15053,36 @@
     <row r="168" ht="12.75" customHeight="1">
       <c r="A168" s="45" t="inlineStr">
         <is>
-          <t>Симонова Виктория Александровна</t>
+          <t>Болденкова Анна Сергеевна</t>
         </is>
       </c>
       <c r="B168" s="46" t="inlineStr">
         <is>
-          <t>09.10.2004</t>
+          <t>09.10.1992</t>
         </is>
       </c>
       <c r="C168" s="47" t="n"/>
       <c r="D168" s="48" t="inlineStr">
         <is>
-          <t>195-171-820 88</t>
+          <t>134-855-108 64</t>
         </is>
       </c>
       <c r="E168" s="49" t="n"/>
       <c r="F168" s="50" t="n"/>
       <c r="G168" s="51" t="inlineStr">
         <is>
-          <t>п.1.14.2, п.1.36, п.1.37.1, п.1.45.1, п.1.45.2, п.1.50, п.4.3.1, п.4.4, п.5.1, п.17</t>
+          <t>п.1.48, п.4.3.1, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="H168" s="49" t="n"/>
       <c r="I168" s="52" t="inlineStr">
         <is>
-          <t>Маляр 4 разряда</t>
+          <t>Уборщик служебных помещений</t>
         </is>
       </c>
       <c r="J168" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Административно-хозяйственный отдел Р</t>
         </is>
       </c>
       <c r="K168" s="53" t="n"/>
@@ -15111,7 +15111,7 @@
       </c>
       <c r="AE168" s="49" t="inlineStr">
         <is>
-          <t>Машково</t>
+          <t>Руднево</t>
         </is>
       </c>
       <c r="AF168" s="6" t="n"/>
@@ -15137,36 +15137,36 @@
     <row r="169" ht="12.75" customHeight="1">
       <c r="A169" s="45" t="inlineStr">
         <is>
-          <t>Солодков Максим Юрьевич</t>
+          <t>Иванова Светлана Васильевна</t>
         </is>
       </c>
       <c r="B169" s="46" t="inlineStr">
         <is>
-          <t>13.05.1988</t>
+          <t>15.03.1967</t>
         </is>
       </c>
       <c r="C169" s="47" t="n"/>
       <c r="D169" s="48" t="inlineStr">
         <is>
-          <t>112-495-624 45</t>
+          <t>037-460-182 47</t>
         </is>
       </c>
       <c r="E169" s="49" t="n"/>
       <c r="F169" s="50" t="n"/>
       <c r="G169" s="51" t="inlineStr">
         <is>
-          <t>п.1.14.2, п.1.36, п.1.37.1, п.1.45.1, п.1.45.2, п.1.50, п.4.3.1, п.4.4, п.5.1, п.17</t>
+          <t>п.1.48, п.4.3.1, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="H169" s="49" t="n"/>
       <c r="I169" s="52" t="inlineStr">
         <is>
-          <t>Маляр 6 разряда</t>
+          <t>Уборщик производственных и служебных помещений</t>
         </is>
       </c>
       <c r="J169" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Административно-хозяйственный отдел Р</t>
         </is>
       </c>
       <c r="K169" s="53" t="n"/>
@@ -15195,7 +15195,7 @@
       </c>
       <c r="AE169" s="49" t="inlineStr">
         <is>
-          <t>Машково</t>
+          <t>Руднево</t>
         </is>
       </c>
       <c r="AF169" s="6" t="n"/>
@@ -15221,36 +15221,36 @@
     <row r="170" ht="12.75" customHeight="1">
       <c r="A170" s="45" t="inlineStr">
         <is>
-          <t>Тимохин Александр Владимирович</t>
+          <t>Терешкина Татьяна Викторовна</t>
         </is>
       </c>
       <c r="B170" s="46" t="inlineStr">
         <is>
-          <t>12.02.1981</t>
+          <t>29.06.1980</t>
         </is>
       </c>
       <c r="C170" s="47" t="n"/>
       <c r="D170" s="48" t="inlineStr">
         <is>
-          <t>027-659-219 78</t>
+          <t>038-836-561 94</t>
         </is>
       </c>
       <c r="E170" s="49" t="n"/>
       <c r="F170" s="50" t="n"/>
       <c r="G170" s="51" t="inlineStr">
         <is>
-          <t>п.1.14.2, п.1.36, п.1.37.1, п.1.45.1, п.1.45.2, п.1.50, п.4.3.1, п.4.4, п.5.1, п.17</t>
+          <t>п.1.48, п.4.3.1, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="H170" s="49" t="n"/>
       <c r="I170" s="52" t="inlineStr">
         <is>
-          <t>Техник 4 разряда</t>
+          <t>Уборщик производственных и служебных помещений</t>
         </is>
       </c>
       <c r="J170" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Административно-хозяйственный отдел Р</t>
         </is>
       </c>
       <c r="K170" s="53" t="n"/>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="AE170" s="49" t="inlineStr">
         <is>
-          <t>Машково</t>
+          <t>Руднево</t>
         </is>
       </c>
       <c r="AF170" s="6" t="n"/>
@@ -15305,18 +15305,18 @@
     <row r="171" ht="12.75" customHeight="1">
       <c r="A171" s="45" t="inlineStr">
         <is>
-          <t>Болденкова Анна Сергеевна</t>
+          <t>Шибатина Елена Васильевна</t>
         </is>
       </c>
       <c r="B171" s="46" t="inlineStr">
         <is>
-          <t>09.10.1992</t>
+          <t>25.01.1968</t>
         </is>
       </c>
       <c r="C171" s="47" t="n"/>
       <c r="D171" s="48" t="inlineStr">
         <is>
-          <t>134-855-108 64</t>
+          <t>041-135-891 22</t>
         </is>
       </c>
       <c r="E171" s="49" t="n"/>
@@ -15329,7 +15329,7 @@
       <c r="H171" s="49" t="n"/>
       <c r="I171" s="52" t="inlineStr">
         <is>
-          <t>Уборщик служебных помещений</t>
+          <t>Уборщик производственных и служебных помещений</t>
         </is>
       </c>
       <c r="J171" s="52" t="inlineStr">
@@ -15389,36 +15389,36 @@
     <row r="172" ht="12.75" customHeight="1">
       <c r="A172" s="45" t="inlineStr">
         <is>
-          <t>Иванова Светлана Васильевна</t>
+          <t>Андреев Кирилл Владимирович</t>
         </is>
       </c>
       <c r="B172" s="46" t="inlineStr">
         <is>
-          <t>15.03.1967</t>
+          <t>10.10.2002</t>
         </is>
       </c>
       <c r="C172" s="47" t="n"/>
       <c r="D172" s="48" t="inlineStr">
         <is>
-          <t>037-460-182 47</t>
+          <t>179-812-577 23</t>
         </is>
       </c>
       <c r="E172" s="49" t="n"/>
       <c r="F172" s="50" t="n"/>
       <c r="G172" s="51" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.3.1, п.4.4, п.5.1</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="H172" s="49" t="n"/>
       <c r="I172" s="52" t="inlineStr">
         <is>
-          <t>Уборщик производственных и служебных помещений</t>
+          <t>Оператор станков с ЧПУ 4 разряда</t>
         </is>
       </c>
       <c r="J172" s="52" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел Р</t>
+          <t>Механический участок Р</t>
         </is>
       </c>
       <c r="K172" s="53" t="n"/>
@@ -15473,36 +15473,36 @@
     <row r="173" ht="12.75" customHeight="1">
       <c r="A173" s="45" t="inlineStr">
         <is>
-          <t>Терешкина Татьяна Викторовна</t>
+          <t>Воркунов Егор Дмитриевич</t>
         </is>
       </c>
       <c r="B173" s="46" t="inlineStr">
         <is>
-          <t>29.06.1980</t>
+          <t>24.07.2003</t>
         </is>
       </c>
       <c r="C173" s="47" t="n"/>
       <c r="D173" s="48" t="inlineStr">
         <is>
-          <t>038-836-561 94</t>
+          <t>193-533-904 89</t>
         </is>
       </c>
       <c r="E173" s="49" t="n"/>
       <c r="F173" s="50" t="n"/>
       <c r="G173" s="51" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.3.1, п.4.4, п.5.1</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="H173" s="49" t="n"/>
       <c r="I173" s="52" t="inlineStr">
         <is>
-          <t>Уборщик производственных и служебных помещений</t>
+          <t>Оператор станков с ЧПУ 4 разряда</t>
         </is>
       </c>
       <c r="J173" s="52" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел Р</t>
+          <t>Механический участок Р</t>
         </is>
       </c>
       <c r="K173" s="53" t="n"/>
@@ -15557,36 +15557,36 @@
     <row r="174" ht="12.75" customHeight="1">
       <c r="A174" s="45" t="inlineStr">
         <is>
-          <t>Шибатина Елена Васильевна</t>
+          <t>Герасимов Александр Александрович</t>
         </is>
       </c>
       <c r="B174" s="46" t="inlineStr">
         <is>
-          <t>25.01.1968</t>
+          <t>05.02.1975</t>
         </is>
       </c>
       <c r="C174" s="47" t="n"/>
       <c r="D174" s="48" t="inlineStr">
         <is>
-          <t>041-135-891 22</t>
+          <t>056-468-953 06</t>
         </is>
       </c>
       <c r="E174" s="49" t="n"/>
       <c r="F174" s="50" t="n"/>
       <c r="G174" s="51" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.3.1, п.4.4, п.5.1</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="H174" s="49" t="n"/>
       <c r="I174" s="52" t="inlineStr">
         <is>
-          <t>Уборщик производственных и служебных помещений</t>
+          <t>Токарь 5 разряда</t>
         </is>
       </c>
       <c r="J174" s="52" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел Р</t>
+          <t>Механический участок Р</t>
         </is>
       </c>
       <c r="K174" s="53" t="n"/>
@@ -15641,18 +15641,18 @@
     <row r="175" ht="12.75" customHeight="1">
       <c r="A175" s="45" t="inlineStr">
         <is>
-          <t>Андреев Кирилл Владимирович</t>
+          <t>Геращенко Сергей Владимирович</t>
         </is>
       </c>
       <c r="B175" s="46" t="inlineStr">
         <is>
-          <t>10.10.2002</t>
+          <t>19.03.2001</t>
         </is>
       </c>
       <c r="C175" s="47" t="n"/>
       <c r="D175" s="48" t="inlineStr">
         <is>
-          <t>179-812-577 23</t>
+          <t>173-009-514 42</t>
         </is>
       </c>
       <c r="E175" s="49" t="n"/>
@@ -15665,7 +15665,7 @@
       <c r="H175" s="49" t="n"/>
       <c r="I175" s="52" t="inlineStr">
         <is>
-          <t>Оператор станков с ЧПУ 4 разряда</t>
+          <t>Оператор-наладчик станков с ЧПУ</t>
         </is>
       </c>
       <c r="J175" s="52" t="inlineStr">
@@ -15725,18 +15725,18 @@
     <row r="176" ht="12.75" customHeight="1">
       <c r="A176" s="45" t="inlineStr">
         <is>
-          <t>Воркунов Егор Дмитриевич</t>
+          <t>Горнеев Никита Сергеевич</t>
         </is>
       </c>
       <c r="B176" s="46" t="inlineStr">
         <is>
-          <t>24.07.2003</t>
+          <t>18.08.1998</t>
         </is>
       </c>
       <c r="C176" s="47" t="n"/>
       <c r="D176" s="48" t="inlineStr">
         <is>
-          <t>193-533-904 89</t>
+          <t>207-658-166 80</t>
         </is>
       </c>
       <c r="E176" s="49" t="n"/>
@@ -15809,18 +15809,18 @@
     <row r="177" ht="12.75" customHeight="1">
       <c r="A177" s="45" t="inlineStr">
         <is>
-          <t>Герасимов Александр Александрович</t>
+          <t>Кашкаров Сергей Евгеньевич</t>
         </is>
       </c>
       <c r="B177" s="46" t="inlineStr">
         <is>
-          <t>05.02.1975</t>
+          <t>16.06.1981</t>
         </is>
       </c>
       <c r="C177" s="47" t="n"/>
       <c r="D177" s="48" t="inlineStr">
         <is>
-          <t>056-468-953 06</t>
+          <t>076-896-465 42</t>
         </is>
       </c>
       <c r="E177" s="49" t="n"/>
@@ -15893,18 +15893,18 @@
     <row r="178" ht="12.75" customHeight="1">
       <c r="A178" s="45" t="inlineStr">
         <is>
-          <t>Геращенко Сергей Владимирович</t>
+          <t>Куликов Сергей Сергеевич</t>
         </is>
       </c>
       <c r="B178" s="46" t="inlineStr">
         <is>
-          <t>19.03.2001</t>
+          <t>26.05.2000</t>
         </is>
       </c>
       <c r="C178" s="47" t="n"/>
       <c r="D178" s="48" t="inlineStr">
         <is>
-          <t>173-009-514 42</t>
+          <t>146-724-576 85</t>
         </is>
       </c>
       <c r="E178" s="49" t="n"/>
@@ -15977,18 +15977,18 @@
     <row r="179" ht="12.75" customHeight="1">
       <c r="A179" s="45" t="inlineStr">
         <is>
-          <t>Горнеев Никита Сергеевич</t>
+          <t>Павозков Евгений Александрович</t>
         </is>
       </c>
       <c r="B179" s="46" t="inlineStr">
         <is>
-          <t>18.08.1998</t>
+          <t>06.04.1982</t>
         </is>
       </c>
       <c r="C179" s="47" t="n"/>
       <c r="D179" s="48" t="inlineStr">
         <is>
-          <t>207-658-166 80</t>
+          <t>079-329-368 10</t>
         </is>
       </c>
       <c r="E179" s="49" t="n"/>
@@ -16001,7 +16001,7 @@
       <c r="H179" s="49" t="n"/>
       <c r="I179" s="52" t="inlineStr">
         <is>
-          <t>Оператор станков с ЧПУ 4 разряда</t>
+          <t>Токарь 5 разряда</t>
         </is>
       </c>
       <c r="J179" s="52" t="inlineStr">
@@ -16061,18 +16061,18 @@
     <row r="180" ht="12.75" customHeight="1">
       <c r="A180" s="45" t="inlineStr">
         <is>
-          <t>Кашкаров Сергей Евгеньевич</t>
+          <t>Пак Игорь Трофимович</t>
         </is>
       </c>
       <c r="B180" s="46" t="inlineStr">
         <is>
-          <t>16.06.1981</t>
+          <t>28.10.1984</t>
         </is>
       </c>
       <c r="C180" s="47" t="n"/>
       <c r="D180" s="48" t="inlineStr">
         <is>
-          <t>076-896-465 42</t>
+          <t>157-610-031 45</t>
         </is>
       </c>
       <c r="E180" s="49" t="n"/>
@@ -16085,7 +16085,7 @@
       <c r="H180" s="49" t="n"/>
       <c r="I180" s="52" t="inlineStr">
         <is>
-          <t>Токарь 5 разряда</t>
+          <t>Оператор станков с ЧПУ 5 разряда</t>
         </is>
       </c>
       <c r="J180" s="52" t="inlineStr">
@@ -16145,18 +16145,18 @@
     <row r="181" ht="12.75" customHeight="1">
       <c r="A181" s="45" t="inlineStr">
         <is>
-          <t>Куликов Сергей Сергеевич</t>
+          <t>Панков Иван Валерьевич</t>
         </is>
       </c>
       <c r="B181" s="46" t="inlineStr">
         <is>
-          <t>26.05.2000</t>
+          <t>03.01.1983</t>
         </is>
       </c>
       <c r="C181" s="47" t="n"/>
       <c r="D181" s="48" t="inlineStr">
         <is>
-          <t>146-724-576 85</t>
+          <t>067-559-164 05</t>
         </is>
       </c>
       <c r="E181" s="49" t="n"/>
@@ -16169,7 +16169,7 @@
       <c r="H181" s="49" t="n"/>
       <c r="I181" s="52" t="inlineStr">
         <is>
-          <t>Оператор-наладчик станков с ЧПУ</t>
+          <t>Оператор станков с ЧПУ 5 разряда</t>
         </is>
       </c>
       <c r="J181" s="52" t="inlineStr">
@@ -16229,18 +16229,18 @@
     <row r="182" ht="12.75" customHeight="1">
       <c r="A182" s="45" t="inlineStr">
         <is>
-          <t>Павозков Евгений Александрович</t>
+          <t>Поливанов Иван Юрьевич</t>
         </is>
       </c>
       <c r="B182" s="46" t="inlineStr">
         <is>
-          <t>06.04.1982</t>
+          <t>27.03.1979</t>
         </is>
       </c>
       <c r="C182" s="47" t="n"/>
       <c r="D182" s="48" t="inlineStr">
         <is>
-          <t>079-329-368 10</t>
+          <t>061-620-141 12</t>
         </is>
       </c>
       <c r="E182" s="49" t="n"/>
@@ -16253,7 +16253,7 @@
       <c r="H182" s="49" t="n"/>
       <c r="I182" s="52" t="inlineStr">
         <is>
-          <t>Токарь 5 разряда</t>
+          <t>Оператор станков с ЧПУ 4 разряда</t>
         </is>
       </c>
       <c r="J182" s="52" t="inlineStr">
@@ -16313,18 +16313,18 @@
     <row r="183" ht="12.75" customHeight="1">
       <c r="A183" s="45" t="inlineStr">
         <is>
-          <t>Пак Игорь Трофимович</t>
+          <t>Семячко Константин Григорьевич</t>
         </is>
       </c>
       <c r="B183" s="46" t="inlineStr">
         <is>
-          <t>28.10.1984</t>
+          <t>04.03.1988</t>
         </is>
       </c>
       <c r="C183" s="47" t="n"/>
       <c r="D183" s="48" t="inlineStr">
         <is>
-          <t>157-610-031 45</t>
+          <t>123-797-630 84</t>
         </is>
       </c>
       <c r="E183" s="49" t="n"/>
@@ -16337,7 +16337,7 @@
       <c r="H183" s="49" t="n"/>
       <c r="I183" s="52" t="inlineStr">
         <is>
-          <t>Оператор станков с ЧПУ 5 разряда</t>
+          <t>Оператор-наладчик станков с ЧПУ</t>
         </is>
       </c>
       <c r="J183" s="52" t="inlineStr">
@@ -16397,18 +16397,18 @@
     <row r="184" ht="12.75" customHeight="1">
       <c r="A184" s="45" t="inlineStr">
         <is>
-          <t>Панков Иван Валерьевич</t>
+          <t>Янышев Тимур Ильгизович</t>
         </is>
       </c>
       <c r="B184" s="46" t="inlineStr">
         <is>
-          <t>03.01.1983</t>
+          <t>21.08.2000</t>
         </is>
       </c>
       <c r="C184" s="47" t="n"/>
       <c r="D184" s="48" t="inlineStr">
         <is>
-          <t>067-559-164 05</t>
+          <t>164-961-104 79</t>
         </is>
       </c>
       <c r="E184" s="49" t="n"/>
@@ -16421,7 +16421,7 @@
       <c r="H184" s="49" t="n"/>
       <c r="I184" s="52" t="inlineStr">
         <is>
-          <t>Оператор станков с ЧПУ 5 разряда</t>
+          <t>Оператор станков с ЧПУ 4 разряда</t>
         </is>
       </c>
       <c r="J184" s="52" t="inlineStr">
@@ -16481,36 +16481,36 @@
     <row r="185" ht="12.75" customHeight="1">
       <c r="A185" s="45" t="inlineStr">
         <is>
-          <t>Поливанов Иван Юрьевич</t>
+          <t>Милованов Александр Сергеевич</t>
         </is>
       </c>
       <c r="B185" s="46" t="inlineStr">
         <is>
-          <t>27.03.1979</t>
+          <t>06.06.1988</t>
         </is>
       </c>
       <c r="C185" s="47" t="n"/>
       <c r="D185" s="48" t="inlineStr">
         <is>
-          <t>061-620-141 12</t>
+          <t>123-371-997 54</t>
         </is>
       </c>
       <c r="E185" s="49" t="n"/>
       <c r="F185" s="50" t="n"/>
       <c r="G185" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.4.4, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="H185" s="49" t="n"/>
       <c r="I185" s="52" t="inlineStr">
         <is>
-          <t>Оператор станков с ЧПУ 4 разряда</t>
+          <t>Инженер 1 категории</t>
         </is>
       </c>
       <c r="J185" s="52" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Отдел технического контроля Р</t>
         </is>
       </c>
       <c r="K185" s="53" t="n"/>
@@ -16565,36 +16565,36 @@
     <row r="186" ht="12.75" customHeight="1">
       <c r="A186" s="45" t="inlineStr">
         <is>
-          <t>Семячко Константин Григорьевич</t>
+          <t>Оболонина Ирина Валерьевна</t>
         </is>
       </c>
       <c r="B186" s="46" t="inlineStr">
         <is>
-          <t>04.03.1988</t>
+          <t>30.09.1982</t>
         </is>
       </c>
       <c r="C186" s="47" t="n"/>
       <c r="D186" s="48" t="inlineStr">
         <is>
-          <t>123-797-630 84</t>
+          <t>095-257-608 97</t>
         </is>
       </c>
       <c r="E186" s="49" t="n"/>
       <c r="F186" s="50" t="n"/>
       <c r="G186" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.4.4, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="H186" s="49" t="n"/>
       <c r="I186" s="52" t="inlineStr">
         <is>
-          <t>Оператор-наладчик станков с ЧПУ</t>
+          <t>Ведущий диспетчер</t>
         </is>
       </c>
       <c r="J186" s="52" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Планово-диспетчерский отдел Р</t>
         </is>
       </c>
       <c r="K186" s="53" t="n"/>
@@ -16649,36 +16649,36 @@
     <row r="187" ht="12.75" customHeight="1">
       <c r="A187" s="45" t="inlineStr">
         <is>
-          <t>Янышев Тимур Ильгизович</t>
+          <t>Рузайкин Юрий Андреевич</t>
         </is>
       </c>
       <c r="B187" s="46" t="inlineStr">
         <is>
-          <t>21.08.2000</t>
+          <t>04.08.1986</t>
         </is>
       </c>
       <c r="C187" s="47" t="n"/>
       <c r="D187" s="48" t="inlineStr">
         <is>
-          <t>164-961-104 79</t>
+          <t>135-472-404 50</t>
         </is>
       </c>
       <c r="E187" s="49" t="n"/>
       <c r="F187" s="50" t="n"/>
       <c r="G187" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.4.4, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="H187" s="49" t="n"/>
       <c r="I187" s="52" t="inlineStr">
         <is>
-          <t>Оператор станков с ЧПУ 4 разряда</t>
+          <t>Инженер</t>
         </is>
       </c>
       <c r="J187" s="52" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Планово-диспетчерский отдел Р</t>
         </is>
       </c>
       <c r="K187" s="53" t="n"/>
@@ -16733,18 +16733,18 @@
     <row r="188" ht="12.75" customHeight="1">
       <c r="A188" s="45" t="inlineStr">
         <is>
-          <t>Милованов Александр Сергеевич</t>
+          <t>Стребкова Наталья Ивановна</t>
         </is>
       </c>
       <c r="B188" s="46" t="inlineStr">
         <is>
-          <t>06.06.1988</t>
+          <t>30.01.1983</t>
         </is>
       </c>
       <c r="C188" s="47" t="n"/>
       <c r="D188" s="48" t="inlineStr">
         <is>
-          <t>123-371-997 54</t>
+          <t>062-969-478 14</t>
         </is>
       </c>
       <c r="E188" s="49" t="n"/>
@@ -16757,12 +16757,12 @@
       <c r="H188" s="49" t="n"/>
       <c r="I188" s="52" t="inlineStr">
         <is>
-          <t>Инженер 1 категории</t>
+          <t>Диспетчер</t>
         </is>
       </c>
       <c r="J188" s="52" t="inlineStr">
         <is>
-          <t>Отдел технического контроля Р</t>
+          <t>Планово-диспетчерский отдел Р</t>
         </is>
       </c>
       <c r="K188" s="53" t="n"/>
@@ -16817,18 +16817,18 @@
     <row r="189" ht="12.75" customHeight="1">
       <c r="A189" s="45" t="inlineStr">
         <is>
-          <t>Оболонина Ирина Валерьевна</t>
+          <t>Яковлева Анастасия Юрьевна</t>
         </is>
       </c>
       <c r="B189" s="46" t="inlineStr">
         <is>
-          <t>30.09.1982</t>
+          <t>28.01.1974</t>
         </is>
       </c>
       <c r="C189" s="47" t="n"/>
       <c r="D189" s="48" t="inlineStr">
         <is>
-          <t>095-257-608 97</t>
+          <t>035-995-049 94</t>
         </is>
       </c>
       <c r="E189" s="49" t="n"/>
@@ -16841,7 +16841,7 @@
       <c r="H189" s="49" t="n"/>
       <c r="I189" s="52" t="inlineStr">
         <is>
-          <t>Ведущий диспетчер</t>
+          <t>Ведущий инженер</t>
         </is>
       </c>
       <c r="J189" s="52" t="inlineStr">
@@ -16901,36 +16901,36 @@
     <row r="190" ht="12.75" customHeight="1">
       <c r="A190" s="45" t="inlineStr">
         <is>
-          <t>Решилова Юлия Евгеньевна</t>
+          <t>Садыгова Елена Васильевна</t>
         </is>
       </c>
       <c r="B190" s="46" t="inlineStr">
         <is>
-          <t>28.02.1988</t>
+          <t>16.06.1984</t>
         </is>
       </c>
       <c r="C190" s="47" t="n"/>
       <c r="D190" s="48" t="inlineStr">
         <is>
-          <t>157-584-922 15</t>
+          <t>126-987-347 11</t>
         </is>
       </c>
       <c r="E190" s="49" t="n"/>
       <c r="F190" s="50" t="n"/>
       <c r="G190" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.1, п.6.2</t>
         </is>
       </c>
       <c r="H190" s="49" t="n"/>
       <c r="I190" s="52" t="inlineStr">
         <is>
-          <t>Диспетчер</t>
+          <t>Кладовщик</t>
         </is>
       </c>
       <c r="J190" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел Р</t>
+          <t>Склад Р</t>
         </is>
       </c>
       <c r="K190" s="53" t="n"/>
@@ -16985,36 +16985,36 @@
     <row r="191" ht="12.75" customHeight="1">
       <c r="A191" s="45" t="inlineStr">
         <is>
-          <t>Рузайкин Юрий Андреевич</t>
+          <t>Юдина Анна Владимировна</t>
         </is>
       </c>
       <c r="B191" s="46" t="inlineStr">
         <is>
-          <t>04.08.1986</t>
+          <t>18.09.1990</t>
         </is>
       </c>
       <c r="C191" s="47" t="n"/>
       <c r="D191" s="48" t="inlineStr">
         <is>
-          <t>135-472-404 50</t>
+          <t>145-019-092 36</t>
         </is>
       </c>
       <c r="E191" s="49" t="n"/>
       <c r="F191" s="50" t="n"/>
       <c r="G191" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.1, п.6.2</t>
         </is>
       </c>
       <c r="H191" s="49" t="n"/>
       <c r="I191" s="52" t="inlineStr">
         <is>
-          <t>Инженер</t>
+          <t>Старший кладовщик</t>
         </is>
       </c>
       <c r="J191" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел Р</t>
+          <t>Склад Р</t>
         </is>
       </c>
       <c r="K191" s="53" t="n"/>
@@ -17069,36 +17069,36 @@
     <row r="192" ht="12.75" customHeight="1">
       <c r="A192" s="45" t="inlineStr">
         <is>
-          <t>Стребкова Наталья Ивановна</t>
+          <t>Баев Сергей Александрович</t>
         </is>
       </c>
       <c r="B192" s="46" t="inlineStr">
         <is>
-          <t>30.01.1983</t>
+          <t>08.08.1981</t>
         </is>
       </c>
       <c r="C192" s="47" t="n"/>
       <c r="D192" s="48" t="inlineStr">
         <is>
-          <t>062-969-478 14</t>
+          <t>052-011-489 00</t>
         </is>
       </c>
       <c r="E192" s="49" t="n"/>
       <c r="F192" s="50" t="n"/>
       <c r="G192" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H192" s="49" t="n"/>
       <c r="I192" s="52" t="inlineStr">
         <is>
-          <t>Диспетчер</t>
+          <t>Слесарь механосборочных работ 6 разряда</t>
         </is>
       </c>
       <c r="J192" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел Р</t>
+          <t>Слесарный участок Р</t>
         </is>
       </c>
       <c r="K192" s="53" t="n"/>
@@ -17153,36 +17153,36 @@
     <row r="193" ht="12.75" customHeight="1">
       <c r="A193" s="45" t="inlineStr">
         <is>
-          <t>Яковлева Анастасия Юрьевна</t>
+          <t>Гришин Алексей Валерьевич</t>
         </is>
       </c>
       <c r="B193" s="46" t="inlineStr">
         <is>
-          <t>28.01.1974</t>
+          <t>16.08.1984</t>
         </is>
       </c>
       <c r="C193" s="47" t="n"/>
       <c r="D193" s="48" t="inlineStr">
         <is>
-          <t>035-995-049 94</t>
+          <t>122-075-617 20</t>
         </is>
       </c>
       <c r="E193" s="49" t="n"/>
       <c r="F193" s="50" t="n"/>
       <c r="G193" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H193" s="49" t="n"/>
       <c r="I193" s="52" t="inlineStr">
         <is>
-          <t>Ведущий инженер</t>
+          <t>Слесарь механосборочных работ 5 разряда</t>
         </is>
       </c>
       <c r="J193" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел Р</t>
+          <t>Слесарный участок Р</t>
         </is>
       </c>
       <c r="K193" s="53" t="n"/>
@@ -17237,36 +17237,36 @@
     <row r="194" ht="12.75" customHeight="1">
       <c r="A194" s="45" t="inlineStr">
         <is>
-          <t>Садыгова Елена Васильевна</t>
+          <t>Козлов Алексей Викторович</t>
         </is>
       </c>
       <c r="B194" s="46" t="inlineStr">
         <is>
-          <t>16.06.1984</t>
+          <t>19.11.1981</t>
         </is>
       </c>
       <c r="C194" s="47" t="n"/>
       <c r="D194" s="48" t="inlineStr">
         <is>
-          <t>126-987-347 11</t>
+          <t>117-452-085 43</t>
         </is>
       </c>
       <c r="E194" s="49" t="n"/>
       <c r="F194" s="50" t="n"/>
       <c r="G194" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.6.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H194" s="49" t="n"/>
       <c r="I194" s="52" t="inlineStr">
         <is>
-          <t>Кладовщик</t>
+          <t>Слесарь механосборочных работ 6 разряда</t>
         </is>
       </c>
       <c r="J194" s="52" t="inlineStr">
         <is>
-          <t>Склад Р</t>
+          <t>Слесарный участок Р</t>
         </is>
       </c>
       <c r="K194" s="53" t="n"/>
@@ -17321,36 +17321,36 @@
     <row r="195" ht="12.75" customHeight="1">
       <c r="A195" s="45" t="inlineStr">
         <is>
-          <t>Юдина Анна Владимировна</t>
+          <t>Корнеев Виктор Николаевич</t>
         </is>
       </c>
       <c r="B195" s="46" t="inlineStr">
         <is>
-          <t>18.09.1990</t>
+          <t>25.06.1954</t>
         </is>
       </c>
       <c r="C195" s="47" t="n"/>
       <c r="D195" s="48" t="inlineStr">
         <is>
-          <t>145-019-092 36</t>
+          <t>001-525-262 87</t>
         </is>
       </c>
       <c r="E195" s="49" t="n"/>
       <c r="F195" s="50" t="n"/>
       <c r="G195" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.6.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="H195" s="49" t="n"/>
       <c r="I195" s="52" t="inlineStr">
         <is>
-          <t>Старший кладовщик</t>
+          <t>Слесарь механосборочных работ 5 разряда</t>
         </is>
       </c>
       <c r="J195" s="52" t="inlineStr">
         <is>
-          <t>Склад Р</t>
+          <t>Слесарный участок Р</t>
         </is>
       </c>
       <c r="K195" s="53" t="n"/>
@@ -17405,18 +17405,18 @@
     <row r="196" ht="12.75" customHeight="1">
       <c r="A196" s="45" t="inlineStr">
         <is>
-          <t>Баев Сергей Александрович</t>
+          <t>Федышен Валерий Васильевич</t>
         </is>
       </c>
       <c r="B196" s="46" t="inlineStr">
         <is>
-          <t>08.08.1981</t>
+          <t>11.11.1968</t>
         </is>
       </c>
       <c r="C196" s="47" t="n"/>
       <c r="D196" s="48" t="inlineStr">
         <is>
-          <t>052-011-489 00</t>
+          <t>149-051-996 83</t>
         </is>
       </c>
       <c r="E196" s="49" t="n"/>
@@ -17429,7 +17429,7 @@
       <c r="H196" s="49" t="n"/>
       <c r="I196" s="52" t="inlineStr">
         <is>
-          <t>Слесарь механосборочных работ 6 разряда</t>
+          <t>Слесарь механосборочных работ 5 разряда</t>
         </is>
       </c>
       <c r="J196" s="52" t="inlineStr">
@@ -17489,36 +17489,36 @@
     <row r="197" ht="12.75" customHeight="1">
       <c r="A197" s="45" t="inlineStr">
         <is>
-          <t>Гришин Алексей Валерьевич</t>
+          <t>Балковский Сергей Вадимович</t>
         </is>
       </c>
       <c r="B197" s="46" t="inlineStr">
         <is>
-          <t>16.08.1984</t>
+          <t>18.01.1972</t>
         </is>
       </c>
       <c r="C197" s="47" t="n"/>
       <c r="D197" s="48" t="inlineStr">
         <is>
-          <t>122-075-617 20</t>
+          <t>068-677-920 32</t>
         </is>
       </c>
       <c r="E197" s="49" t="n"/>
       <c r="F197" s="50" t="n"/>
       <c r="G197" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.15</t>
         </is>
       </c>
       <c r="H197" s="49" t="n"/>
       <c r="I197" s="52" t="inlineStr">
         <is>
-          <t>Слесарь механосборочных работ 5 разряда</t>
+          <t>Слесарь-сборщик 4 разряда</t>
         </is>
       </c>
       <c r="J197" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок Р</t>
+          <t>Участок сборки Р</t>
         </is>
       </c>
       <c r="K197" s="53" t="n"/>
@@ -17573,36 +17573,36 @@
     <row r="198" ht="12.75" customHeight="1">
       <c r="A198" s="45" t="inlineStr">
         <is>
-          <t>Козлов Алексей Викторович</t>
+          <t>Бузаев Дмитрий Анатольевич</t>
         </is>
       </c>
       <c r="B198" s="46" t="inlineStr">
         <is>
-          <t>19.11.1981</t>
+          <t>22.10.1981</t>
         </is>
       </c>
       <c r="C198" s="47" t="n"/>
       <c r="D198" s="48" t="inlineStr">
         <is>
-          <t>117-452-085 43</t>
+          <t>110-735-963 35</t>
         </is>
       </c>
       <c r="E198" s="49" t="n"/>
       <c r="F198" s="50" t="n"/>
       <c r="G198" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.15</t>
         </is>
       </c>
       <c r="H198" s="49" t="n"/>
       <c r="I198" s="52" t="inlineStr">
         <is>
-          <t>Слесарь механосборочных работ 6 разряда</t>
+          <t>Слесарь-сборщик 5 разряда</t>
         </is>
       </c>
       <c r="J198" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок Р</t>
+          <t>Участок сборки Р</t>
         </is>
       </c>
       <c r="K198" s="53" t="n"/>
@@ -17657,36 +17657,36 @@
     <row r="199" ht="12.75" customHeight="1">
       <c r="A199" s="45" t="inlineStr">
         <is>
-          <t>Корнеев Виктор Николаевич</t>
+          <t>Гурьянов Евгений Николаевич</t>
         </is>
       </c>
       <c r="B199" s="46" t="inlineStr">
         <is>
-          <t>25.06.1954</t>
+          <t>24.08.1980</t>
         </is>
       </c>
       <c r="C199" s="47" t="n"/>
       <c r="D199" s="48" t="inlineStr">
         <is>
-          <t>001-525-262 87</t>
+          <t>106-689-527 88</t>
         </is>
       </c>
       <c r="E199" s="49" t="n"/>
       <c r="F199" s="50" t="n"/>
       <c r="G199" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.15</t>
         </is>
       </c>
       <c r="H199" s="49" t="n"/>
       <c r="I199" s="52" t="inlineStr">
         <is>
-          <t>Слесарь механосборочных работ 5 разряда</t>
+          <t>Слесарь-сборщик 4 разряда</t>
         </is>
       </c>
       <c r="J199" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок Р</t>
+          <t>Участок сборки Р</t>
         </is>
       </c>
       <c r="K199" s="53" t="n"/>
@@ -17741,36 +17741,36 @@
     <row r="200" ht="12.75" customHeight="1">
       <c r="A200" s="45" t="inlineStr">
         <is>
-          <t>Федышен Валерий Васильевич</t>
+          <t>Еремеев Сергей Анатольевич</t>
         </is>
       </c>
       <c r="B200" s="46" t="inlineStr">
         <is>
-          <t>11.11.1968</t>
+          <t>10.11.1968</t>
         </is>
       </c>
       <c r="C200" s="47" t="n"/>
       <c r="D200" s="48" t="inlineStr">
         <is>
-          <t>149-051-996 83</t>
+          <t>143-266-272 49</t>
         </is>
       </c>
       <c r="E200" s="49" t="n"/>
       <c r="F200" s="50" t="n"/>
       <c r="G200" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.15</t>
         </is>
       </c>
       <c r="H200" s="49" t="n"/>
       <c r="I200" s="52" t="inlineStr">
         <is>
-          <t>Слесарь механосборочных работ 5 разряда</t>
+          <t>Слесарь-сборщик 5 разряда</t>
         </is>
       </c>
       <c r="J200" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок Р</t>
+          <t>Участок сборки Р</t>
         </is>
       </c>
       <c r="K200" s="53" t="n"/>
@@ -17825,18 +17825,18 @@
     <row r="201" ht="12.75" customHeight="1">
       <c r="A201" s="45" t="inlineStr">
         <is>
-          <t>Балковский Сергей Вадимович</t>
+          <t>Житников Андрей Николаевич</t>
         </is>
       </c>
       <c r="B201" s="46" t="inlineStr">
         <is>
-          <t>18.01.1972</t>
+          <t>30.09.2004</t>
         </is>
       </c>
       <c r="C201" s="47" t="n"/>
       <c r="D201" s="48" t="inlineStr">
         <is>
-          <t>068-677-920 32</t>
+          <t>167-936-806 27</t>
         </is>
       </c>
       <c r="E201" s="49" t="n"/>
@@ -17849,7 +17849,7 @@
       <c r="H201" s="49" t="n"/>
       <c r="I201" s="52" t="inlineStr">
         <is>
-          <t>Слесарь-сборщик 4 разряда</t>
+          <t>Слесарь-сборщик 3 разряда</t>
         </is>
       </c>
       <c r="J201" s="52" t="inlineStr">
@@ -17909,18 +17909,18 @@
     <row r="202" ht="12.75" customHeight="1">
       <c r="A202" s="45" t="inlineStr">
         <is>
-          <t>Бузаев Дмитрий Анатольевич</t>
+          <t>Зайцев Дмитрий Евгеньевич</t>
         </is>
       </c>
       <c r="B202" s="46" t="inlineStr">
         <is>
-          <t>22.10.1981</t>
+          <t>27.04.1996</t>
         </is>
       </c>
       <c r="C202" s="47" t="n"/>
       <c r="D202" s="48" t="inlineStr">
         <is>
-          <t>110-735-963 35</t>
+          <t>144-685-068 84</t>
         </is>
       </c>
       <c r="E202" s="49" t="n"/>
@@ -17933,7 +17933,7 @@
       <c r="H202" s="49" t="n"/>
       <c r="I202" s="52" t="inlineStr">
         <is>
-          <t>Слесарь-сборщик 5 разряда</t>
+          <t>Слесарь-сборщик 3 разряда</t>
         </is>
       </c>
       <c r="J202" s="52" t="inlineStr">
@@ -17993,18 +17993,18 @@
     <row r="203" ht="12.75" customHeight="1">
       <c r="A203" s="45" t="inlineStr">
         <is>
-          <t>Гурьянов Евгений Николаевич</t>
+          <t>Зайцев Евгений Геннадьевич</t>
         </is>
       </c>
       <c r="B203" s="46" t="inlineStr">
         <is>
-          <t>24.08.1980</t>
+          <t>09.05.1973</t>
         </is>
       </c>
       <c r="C203" s="47" t="n"/>
       <c r="D203" s="48" t="inlineStr">
         <is>
-          <t>106-689-527 88</t>
+          <t>064-564-206 63</t>
         </is>
       </c>
       <c r="E203" s="49" t="n"/>
@@ -18077,18 +18077,18 @@
     <row r="204" ht="12.75" customHeight="1">
       <c r="A204" s="45" t="inlineStr">
         <is>
-          <t>Еремеев Сергей Анатольевич</t>
+          <t>Николаев Никита Андреевич</t>
         </is>
       </c>
       <c r="B204" s="46" t="inlineStr">
         <is>
-          <t>10.11.1968</t>
+          <t>29.06.2004</t>
         </is>
       </c>
       <c r="C204" s="47" t="n"/>
       <c r="D204" s="48" t="inlineStr">
         <is>
-          <t>143-266-272 49</t>
+          <t>164-342-983 76</t>
         </is>
       </c>
       <c r="E204" s="49" t="n"/>
@@ -18101,7 +18101,7 @@
       <c r="H204" s="49" t="n"/>
       <c r="I204" s="52" t="inlineStr">
         <is>
-          <t>Слесарь-сборщик 5 разряда</t>
+          <t>Слесарь-сборщик 3 разряда</t>
         </is>
       </c>
       <c r="J204" s="52" t="inlineStr">
@@ -18161,18 +18161,18 @@
     <row r="205" ht="12.75" customHeight="1">
       <c r="A205" s="45" t="inlineStr">
         <is>
-          <t>Житников Андрей Николаевич</t>
+          <t>Чепуштанов Александр Геннадьевич</t>
         </is>
       </c>
       <c r="B205" s="46" t="inlineStr">
         <is>
-          <t>30.09.2004</t>
+          <t>17.03.1979</t>
         </is>
       </c>
       <c r="C205" s="47" t="n"/>
       <c r="D205" s="48" t="inlineStr">
         <is>
-          <t>167-936-806 27</t>
+          <t>116-713-887 64</t>
         </is>
       </c>
       <c r="E205" s="49" t="n"/>
@@ -18185,7 +18185,7 @@
       <c r="H205" s="49" t="n"/>
       <c r="I205" s="52" t="inlineStr">
         <is>
-          <t>Слесарь-сборщик 3 разряда</t>
+          <t>Слесарь-сборщик 6 разряда</t>
         </is>
       </c>
       <c r="J205" s="52" t="inlineStr">
@@ -18245,18 +18245,18 @@
     <row r="206" ht="12.75" customHeight="1">
       <c r="A206" s="45" t="inlineStr">
         <is>
-          <t>Зайцев Дмитрий Евгеньевич</t>
+          <t>Швецов Андрей Витальевич</t>
         </is>
       </c>
       <c r="B206" s="46" t="inlineStr">
         <is>
-          <t>27.04.1996</t>
+          <t>09.10.1976</t>
         </is>
       </c>
       <c r="C206" s="47" t="n"/>
       <c r="D206" s="48" t="inlineStr">
         <is>
-          <t>144-685-068 84</t>
+          <t>152-559-821 82</t>
         </is>
       </c>
       <c r="E206" s="49" t="n"/>
@@ -18269,7 +18269,7 @@
       <c r="H206" s="49" t="n"/>
       <c r="I206" s="52" t="inlineStr">
         <is>
-          <t>Слесарь-сборщик 3 разряда</t>
+          <t>Слесарь-сборщик 4 разряда</t>
         </is>
       </c>
       <c r="J206" s="52" t="inlineStr">
@@ -18329,36 +18329,36 @@
     <row r="207" ht="12.75" customHeight="1">
       <c r="A207" s="45" t="inlineStr">
         <is>
-          <t>Зайцев Евгений Геннадьевич</t>
+          <t>Андрякова Надежда Дмитриевна</t>
         </is>
       </c>
       <c r="B207" s="46" t="inlineStr">
         <is>
-          <t>09.05.1973</t>
+          <t>03.01.1991</t>
         </is>
       </c>
       <c r="C207" s="47" t="n"/>
       <c r="D207" s="48" t="inlineStr">
         <is>
-          <t>064-564-206 63</t>
+          <t>173-547-161 79</t>
         </is>
       </c>
       <c r="E207" s="49" t="n"/>
       <c r="F207" s="50" t="n"/>
       <c r="G207" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.15</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="H207" s="49" t="n"/>
       <c r="I207" s="52" t="inlineStr">
         <is>
-          <t>Слесарь-сборщик 4 разряда</t>
+          <t>Специалист по пошиву 5 разряда</t>
         </is>
       </c>
       <c r="J207" s="52" t="inlineStr">
         <is>
-          <t>Участок сборки Р</t>
+          <t>Швейный участок Р</t>
         </is>
       </c>
       <c r="K207" s="53" t="n"/>
@@ -18413,36 +18413,36 @@
     <row r="208" ht="12.75" customHeight="1">
       <c r="A208" s="45" t="inlineStr">
         <is>
-          <t>Николаев Никита Андреевич</t>
+          <t>Антонова Елена Анатольевна</t>
         </is>
       </c>
       <c r="B208" s="46" t="inlineStr">
         <is>
-          <t>29.06.2004</t>
+          <t>22.01.1971</t>
         </is>
       </c>
       <c r="C208" s="47" t="n"/>
       <c r="D208" s="48" t="inlineStr">
         <is>
-          <t>164-342-983 76</t>
+          <t>019-124-361 24</t>
         </is>
       </c>
       <c r="E208" s="49" t="n"/>
       <c r="F208" s="50" t="n"/>
       <c r="G208" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.15</t>
+          <t>п.4.4, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="H208" s="49" t="n"/>
       <c r="I208" s="52" t="inlineStr">
         <is>
-          <t>Слесарь-сборщик 3 разряда</t>
+          <t>Мастер участка</t>
         </is>
       </c>
       <c r="J208" s="52" t="inlineStr">
         <is>
-          <t>Участок сборки Р</t>
+          <t>Швейный участок Р</t>
         </is>
       </c>
       <c r="K208" s="53" t="n"/>
@@ -18497,36 +18497,36 @@
     <row r="209" ht="12.75" customHeight="1">
       <c r="A209" s="45" t="inlineStr">
         <is>
-          <t>Чепуштанов Александр Геннадьевич</t>
+          <t>Ахмедов Яшар Закир Оглы</t>
         </is>
       </c>
       <c r="B209" s="46" t="inlineStr">
         <is>
-          <t>17.03.1979</t>
+          <t>04.05.1956</t>
         </is>
       </c>
       <c r="C209" s="47" t="n"/>
       <c r="D209" s="48" t="inlineStr">
         <is>
-          <t>116-713-887 64</t>
+          <t>112-436-131 03</t>
         </is>
       </c>
       <c r="E209" s="49" t="n"/>
       <c r="F209" s="50" t="n"/>
       <c r="G209" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.15</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="H209" s="49" t="n"/>
       <c r="I209" s="52" t="inlineStr">
         <is>
-          <t>Слесарь-сборщик 6 разряда</t>
+          <t>Специалист по пошиву 5 разряда</t>
         </is>
       </c>
       <c r="J209" s="52" t="inlineStr">
         <is>
-          <t>Участок сборки Р</t>
+          <t>Швейный участок Р</t>
         </is>
       </c>
       <c r="K209" s="53" t="n"/>
@@ -18581,36 +18581,36 @@
     <row r="210" ht="12.75" customHeight="1">
       <c r="A210" s="45" t="inlineStr">
         <is>
-          <t>Швецов Андрей Витальевич</t>
+          <t>Богатырева Наталья Геннадьевна</t>
         </is>
       </c>
       <c r="B210" s="46" t="inlineStr">
         <is>
-          <t>09.10.1976</t>
+          <t>29.10.1968</t>
         </is>
       </c>
       <c r="C210" s="47" t="n"/>
       <c r="D210" s="48" t="inlineStr">
         <is>
-          <t>152-559-821 82</t>
+          <t>123-446-092 33</t>
         </is>
       </c>
       <c r="E210" s="49" t="n"/>
       <c r="F210" s="50" t="n"/>
       <c r="G210" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.15</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="H210" s="49" t="n"/>
       <c r="I210" s="52" t="inlineStr">
         <is>
-          <t>Слесарь-сборщик 4 разряда</t>
+          <t>Старший специалист по пошиву</t>
         </is>
       </c>
       <c r="J210" s="52" t="inlineStr">
         <is>
-          <t>Участок сборки Р</t>
+          <t>Швейный участок Р</t>
         </is>
       </c>
       <c r="K210" s="53" t="n"/>
@@ -18665,18 +18665,18 @@
     <row r="211" ht="12.75" customHeight="1">
       <c r="A211" s="45" t="inlineStr">
         <is>
-          <t>Андрякова Надежда Дмитриевна</t>
+          <t>Большаков Сергей Александрович</t>
         </is>
       </c>
       <c r="B211" s="46" t="inlineStr">
         <is>
-          <t>03.01.1991</t>
+          <t>02.08.1973</t>
         </is>
       </c>
       <c r="C211" s="47" t="n"/>
       <c r="D211" s="48" t="inlineStr">
         <is>
-          <t>173-547-161 79</t>
+          <t>017-273-436 39</t>
         </is>
       </c>
       <c r="E211" s="49" t="n"/>
@@ -18689,7 +18689,7 @@
       <c r="H211" s="49" t="n"/>
       <c r="I211" s="52" t="inlineStr">
         <is>
-          <t>Специалист по пошиву 5 разряда</t>
+          <t>Старший специалист по пошиву</t>
         </is>
       </c>
       <c r="J211" s="52" t="inlineStr">
@@ -18749,31 +18749,31 @@
     <row r="212" ht="12.75" customHeight="1">
       <c r="A212" s="45" t="inlineStr">
         <is>
-          <t>Антонова Елена Анатольевна</t>
+          <t>Горбушина Венера Энверовна</t>
         </is>
       </c>
       <c r="B212" s="46" t="inlineStr">
         <is>
-          <t>22.01.1971</t>
+          <t>27.09.1990</t>
         </is>
       </c>
       <c r="C212" s="47" t="n"/>
       <c r="D212" s="48" t="inlineStr">
         <is>
-          <t>019-124-361 24</t>
+          <t>140-699-679 98</t>
         </is>
       </c>
       <c r="E212" s="49" t="n"/>
       <c r="F212" s="50" t="n"/>
       <c r="G212" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="H212" s="49" t="n"/>
       <c r="I212" s="52" t="inlineStr">
         <is>
-          <t>Мастер участка</t>
+          <t>Специалист по пошиву 4 разряда</t>
         </is>
       </c>
       <c r="J212" s="52" t="inlineStr">
@@ -18833,18 +18833,18 @@
     <row r="213" ht="12.75" customHeight="1">
       <c r="A213" s="45" t="inlineStr">
         <is>
-          <t>Ахмедов Яшар Закир Оглы</t>
+          <t>Долженко Ольга Васильевна</t>
         </is>
       </c>
       <c r="B213" s="46" t="inlineStr">
         <is>
-          <t>04.05.1956</t>
+          <t>08.02.1963</t>
         </is>
       </c>
       <c r="C213" s="47" t="n"/>
       <c r="D213" s="48" t="inlineStr">
         <is>
-          <t>112-436-131 03</t>
+          <t>171-022-713 15</t>
         </is>
       </c>
       <c r="E213" s="49" t="n"/>
@@ -18857,7 +18857,7 @@
       <c r="H213" s="49" t="n"/>
       <c r="I213" s="52" t="inlineStr">
         <is>
-          <t>Специалист по пошиву 5 разряда</t>
+          <t>Старший специалист по пошиву</t>
         </is>
       </c>
       <c r="J213" s="52" t="inlineStr">
@@ -18917,18 +18917,18 @@
     <row r="214" ht="12.75" customHeight="1">
       <c r="A214" s="45" t="inlineStr">
         <is>
-          <t>Богатырева Наталья Геннадьевна</t>
+          <t>Долматова Екатерина Владимировна</t>
         </is>
       </c>
       <c r="B214" s="46" t="inlineStr">
         <is>
-          <t>29.10.1968</t>
+          <t>04.05.1980</t>
         </is>
       </c>
       <c r="C214" s="47" t="n"/>
       <c r="D214" s="48" t="inlineStr">
         <is>
-          <t>123-446-092 33</t>
+          <t>128-046-255 45</t>
         </is>
       </c>
       <c r="E214" s="49" t="n"/>
@@ -18941,7 +18941,7 @@
       <c r="H214" s="49" t="n"/>
       <c r="I214" s="52" t="inlineStr">
         <is>
-          <t>Старший специалист по пошиву</t>
+          <t>Специалист по пошиву 5 разряда</t>
         </is>
       </c>
       <c r="J214" s="52" t="inlineStr">
@@ -19001,18 +19001,18 @@
     <row r="215" ht="12.75" customHeight="1">
       <c r="A215" s="45" t="inlineStr">
         <is>
-          <t>Большаков Сергей Александрович</t>
+          <t>Китаева Венера Минигалеевна</t>
         </is>
       </c>
       <c r="B215" s="46" t="inlineStr">
         <is>
-          <t>02.08.1973</t>
+          <t>20.01.1982</t>
         </is>
       </c>
       <c r="C215" s="47" t="n"/>
       <c r="D215" s="48" t="inlineStr">
         <is>
-          <t>017-273-436 39</t>
+          <t>137-939-293 12</t>
         </is>
       </c>
       <c r="E215" s="49" t="n"/>
@@ -19025,7 +19025,7 @@
       <c r="H215" s="49" t="n"/>
       <c r="I215" s="52" t="inlineStr">
         <is>
-          <t>Старший специалист по пошиву</t>
+          <t>Специалист по пошиву 5 разряда</t>
         </is>
       </c>
       <c r="J215" s="52" t="inlineStr">
@@ -19085,18 +19085,18 @@
     <row r="216" ht="12.75" customHeight="1">
       <c r="A216" s="45" t="inlineStr">
         <is>
-          <t>Горбушина Венера Энверовна</t>
+          <t>Кулешова Виктория Викторовна</t>
         </is>
       </c>
       <c r="B216" s="46" t="inlineStr">
         <is>
-          <t>27.09.1990</t>
+          <t>26.12.1970</t>
         </is>
       </c>
       <c r="C216" s="47" t="n"/>
       <c r="D216" s="48" t="inlineStr">
         <is>
-          <t>140-699-679 98</t>
+          <t>044-054-282 24</t>
         </is>
       </c>
       <c r="E216" s="49" t="n"/>
@@ -19169,18 +19169,18 @@
     <row r="217" ht="12.75" customHeight="1">
       <c r="A217" s="45" t="inlineStr">
         <is>
-          <t>Долженко Ольга Васильевна</t>
+          <t>Кульков Павел Петрович</t>
         </is>
       </c>
       <c r="B217" s="46" t="inlineStr">
         <is>
-          <t>08.02.1963</t>
+          <t>29.01.1982</t>
         </is>
       </c>
       <c r="C217" s="47" t="n"/>
       <c r="D217" s="48" t="inlineStr">
         <is>
-          <t>171-022-713 15</t>
+          <t>071-694-847 98</t>
         </is>
       </c>
       <c r="E217" s="49" t="n"/>
@@ -19253,18 +19253,18 @@
     <row r="218" ht="12.75" customHeight="1">
       <c r="A218" s="45" t="inlineStr">
         <is>
-          <t>Долматова Екатерина Владимировна</t>
+          <t>Пичугина Оксана Валерьевна</t>
         </is>
       </c>
       <c r="B218" s="46" t="inlineStr">
         <is>
-          <t>04.05.1980</t>
+          <t>17.02.1983</t>
         </is>
       </c>
       <c r="C218" s="47" t="n"/>
       <c r="D218" s="48" t="inlineStr">
         <is>
-          <t>128-046-255 45</t>
+          <t>126-547-755 80</t>
         </is>
       </c>
       <c r="E218" s="49" t="n"/>
@@ -19337,18 +19337,18 @@
     <row r="219" ht="12.75" customHeight="1">
       <c r="A219" s="45" t="inlineStr">
         <is>
-          <t>Зайцев Антон Валерьевич</t>
+          <t>Путилина Ирина Михайловна</t>
         </is>
       </c>
       <c r="B219" s="46" t="inlineStr">
         <is>
-          <t>30.10.1981</t>
+          <t>14.07.1971</t>
         </is>
       </c>
       <c r="C219" s="47" t="n"/>
       <c r="D219" s="48" t="inlineStr">
         <is>
-          <t>057-121-178 33</t>
+          <t>077-826-209 00</t>
         </is>
       </c>
       <c r="E219" s="49" t="n"/>
@@ -19361,7 +19361,7 @@
       <c r="H219" s="49" t="n"/>
       <c r="I219" s="52" t="inlineStr">
         <is>
-          <t>Специалист по пошиву 4 разряда</t>
+          <t>Старший специалист по пошиву</t>
         </is>
       </c>
       <c r="J219" s="52" t="inlineStr">
@@ -19421,18 +19421,18 @@
     <row r="220" ht="12.75" customHeight="1">
       <c r="A220" s="45" t="inlineStr">
         <is>
-          <t>Китаева Венера Минигалеевна</t>
+          <t>Треусов Сергей Юрьевич</t>
         </is>
       </c>
       <c r="B220" s="46" t="inlineStr">
         <is>
-          <t>20.01.1982</t>
+          <t>31.10.1965</t>
         </is>
       </c>
       <c r="C220" s="47" t="n"/>
       <c r="D220" s="48" t="inlineStr">
         <is>
-          <t>137-939-293 12</t>
+          <t>068-782-527 18</t>
         </is>
       </c>
       <c r="E220" s="49" t="n"/>
@@ -19505,36 +19505,32 @@
     <row r="221" ht="12.75" customHeight="1">
       <c r="A221" s="45" t="inlineStr">
         <is>
-          <t>Кулешова Виктория Викторовна</t>
+          <t>Кокорев Анатолий Сергеевич</t>
         </is>
       </c>
       <c r="B221" s="46" t="inlineStr">
         <is>
-          <t>26.12.1970</t>
+          <t>19.06.1987</t>
         </is>
       </c>
       <c r="C221" s="47" t="n"/>
       <c r="D221" s="48" t="inlineStr">
         <is>
-          <t>044-054-282 24</t>
+          <t>133-055-324 15</t>
         </is>
       </c>
       <c r="E221" s="49" t="n"/>
       <c r="F221" s="50" t="n"/>
-      <c r="G221" s="51" t="inlineStr">
-        <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
-        </is>
-      </c>
+      <c r="G221" s="51" t="n"/>
       <c r="H221" s="49" t="n"/>
       <c r="I221" s="52" t="inlineStr">
         <is>
-          <t>Специалист по пошиву 4 разряда</t>
+          <t>Мастер участка</t>
         </is>
       </c>
       <c r="J221" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Участок РЭО МШ</t>
         </is>
       </c>
       <c r="K221" s="53" t="n"/>
@@ -19546,8 +19542,16 @@
       <c r="Q221" s="48" t="n"/>
       <c r="R221" s="49" t="n"/>
       <c r="S221" s="49" t="n"/>
-      <c r="T221" s="49" t="n"/>
-      <c r="U221" s="55" t="n"/>
+      <c r="T221" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U221" s="55" t="inlineStr">
+        <is>
+          <t>п.11 Прил.№2: руководство работами по монтажу, наладке, ремонту электроустановок. Относится также мастер участка РЭО.</t>
+        </is>
+      </c>
       <c r="V221" s="49" t="n"/>
       <c r="W221" s="49" t="n"/>
       <c r="X221" s="48" t="n"/>
@@ -19563,7 +19567,7 @@
       </c>
       <c r="AE221" s="49" t="inlineStr">
         <is>
-          <t>Руднево</t>
+          <t>Машково</t>
         </is>
       </c>
       <c r="AF221" s="6" t="n"/>
@@ -19589,36 +19593,32 @@
     <row r="222" ht="12.75" customHeight="1">
       <c r="A222" s="45" t="inlineStr">
         <is>
-          <t>Кульков Павел Петрович</t>
+          <t>Гагарин Алексей Владимирович</t>
         </is>
       </c>
       <c r="B222" s="46" t="inlineStr">
         <is>
-          <t>29.01.1982</t>
+          <t>30.03.1987</t>
         </is>
       </c>
       <c r="C222" s="47" t="n"/>
       <c r="D222" s="48" t="inlineStr">
         <is>
-          <t>071-694-847 98</t>
+          <t>137-353-721 62</t>
         </is>
       </c>
       <c r="E222" s="49" t="n"/>
       <c r="F222" s="50" t="n"/>
-      <c r="G222" s="51" t="inlineStr">
-        <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
-        </is>
-      </c>
+      <c r="G222" s="51" t="n"/>
       <c r="H222" s="49" t="n"/>
       <c r="I222" s="52" t="inlineStr">
         <is>
-          <t>Старший специалист по пошиву</t>
+          <t>Кладовщик-комплектовщик</t>
         </is>
       </c>
       <c r="J222" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Склад Р</t>
         </is>
       </c>
       <c r="K222" s="53" t="n"/>
@@ -19630,8 +19630,16 @@
       <c r="Q222" s="48" t="n"/>
       <c r="R222" s="49" t="n"/>
       <c r="S222" s="49" t="n"/>
-      <c r="T222" s="49" t="n"/>
-      <c r="U222" s="55" t="n"/>
+      <c r="T222" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U222" s="55" t="inlineStr">
+        <is>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+        </is>
+      </c>
       <c r="V222" s="49" t="n"/>
       <c r="W222" s="49" t="n"/>
       <c r="X222" s="48" t="n"/>
@@ -19673,36 +19681,32 @@
     <row r="223" ht="12.75" customHeight="1">
       <c r="A223" s="45" t="inlineStr">
         <is>
-          <t>Пичугина Оксана Валерьевна</t>
+          <t>Иванов Дмитрий Сергеевич</t>
         </is>
       </c>
       <c r="B223" s="46" t="inlineStr">
         <is>
-          <t>17.02.1983</t>
+          <t>15.07.1996</t>
         </is>
       </c>
       <c r="C223" s="47" t="n"/>
       <c r="D223" s="48" t="inlineStr">
         <is>
-          <t>126-547-755 80</t>
+          <t>165-320-758 58</t>
         </is>
       </c>
       <c r="E223" s="49" t="n"/>
       <c r="F223" s="50" t="n"/>
-      <c r="G223" s="51" t="inlineStr">
-        <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
-        </is>
-      </c>
+      <c r="G223" s="51" t="n"/>
       <c r="H223" s="49" t="n"/>
       <c r="I223" s="52" t="inlineStr">
         <is>
-          <t>Специалист по пошиву 5 разряда</t>
+          <t>Кладовщик-комплектовщик</t>
         </is>
       </c>
       <c r="J223" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Склад Р</t>
         </is>
       </c>
       <c r="K223" s="53" t="n"/>
@@ -19714,8 +19718,16 @@
       <c r="Q223" s="48" t="n"/>
       <c r="R223" s="49" t="n"/>
       <c r="S223" s="49" t="n"/>
-      <c r="T223" s="49" t="n"/>
-      <c r="U223" s="55" t="n"/>
+      <c r="T223" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U223" s="55" t="inlineStr">
+        <is>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+        </is>
+      </c>
       <c r="V223" s="49" t="n"/>
       <c r="W223" s="49" t="n"/>
       <c r="X223" s="48" t="n"/>
@@ -19757,36 +19769,32 @@
     <row r="224" ht="12.75" customHeight="1">
       <c r="A224" s="45" t="inlineStr">
         <is>
-          <t>Путилина Ирина Михайловна</t>
+          <t>Поляков Александр Валентинович</t>
         </is>
       </c>
       <c r="B224" s="46" t="inlineStr">
         <is>
-          <t>14.07.1971</t>
+          <t>08.01.1984</t>
         </is>
       </c>
       <c r="C224" s="47" t="n"/>
       <c r="D224" s="48" t="inlineStr">
         <is>
-          <t>077-826-209 00</t>
+          <t>114-455-402 27</t>
         </is>
       </c>
       <c r="E224" s="49" t="n"/>
       <c r="F224" s="50" t="n"/>
-      <c r="G224" s="51" t="inlineStr">
-        <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
-        </is>
-      </c>
+      <c r="G224" s="51" t="n"/>
       <c r="H224" s="49" t="n"/>
       <c r="I224" s="52" t="inlineStr">
         <is>
-          <t>Старший специалист по пошиву</t>
+          <t>Кладовщик-комплектовщик</t>
         </is>
       </c>
       <c r="J224" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Склад Р</t>
         </is>
       </c>
       <c r="K224" s="53" t="n"/>
@@ -19798,8 +19806,16 @@
       <c r="Q224" s="48" t="n"/>
       <c r="R224" s="49" t="n"/>
       <c r="S224" s="49" t="n"/>
-      <c r="T224" s="49" t="n"/>
-      <c r="U224" s="55" t="n"/>
+      <c r="T224" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U224" s="55" t="inlineStr">
+        <is>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+        </is>
+      </c>
       <c r="V224" s="49" t="n"/>
       <c r="W224" s="49" t="n"/>
       <c r="X224" s="48" t="n"/>
@@ -19841,36 +19857,32 @@
     <row r="225" ht="12.75" customHeight="1">
       <c r="A225" s="45" t="inlineStr">
         <is>
-          <t>Треусов Сергей Юрьевич</t>
+          <t>Улумбеков Руслан Бинарович</t>
         </is>
       </c>
       <c r="B225" s="46" t="inlineStr">
         <is>
-          <t>31.10.1965</t>
+          <t>30.06.1978</t>
         </is>
       </c>
       <c r="C225" s="47" t="n"/>
       <c r="D225" s="48" t="inlineStr">
         <is>
-          <t>068-782-527 18</t>
+          <t>053-851-554 66</t>
         </is>
       </c>
       <c r="E225" s="49" t="n"/>
       <c r="F225" s="50" t="n"/>
-      <c r="G225" s="51" t="inlineStr">
-        <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
-        </is>
-      </c>
+      <c r="G225" s="51" t="n"/>
       <c r="H225" s="49" t="n"/>
       <c r="I225" s="52" t="inlineStr">
         <is>
-          <t>Специалист по пошиву 5 разряда</t>
+          <t>Электромонтер по ремонту и обслуживанию электрооборудования 4 разряда</t>
         </is>
       </c>
       <c r="J225" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Служба главного инженера Р</t>
         </is>
       </c>
       <c r="K225" s="53" t="n"/>
@@ -19882,8 +19894,16 @@
       <c r="Q225" s="48" t="n"/>
       <c r="R225" s="49" t="n"/>
       <c r="S225" s="49" t="n"/>
-      <c r="T225" s="49" t="n"/>
-      <c r="U225" s="55" t="n"/>
+      <c r="T225" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U225" s="55" t="inlineStr">
+        <is>
+          <t>п.11 Прил.№2: обслуживание электроустановок предприятия.</t>
+        </is>
+      </c>
       <c r="V225" s="49" t="n"/>
       <c r="W225" s="49" t="n"/>
       <c r="X225" s="48" t="n"/>
@@ -19923,73 +19943,37 @@
       <c r="AX225" s="6" t="n"/>
     </row>
     <row r="226" ht="12.75" customHeight="1">
-      <c r="A226" s="45" t="inlineStr">
-        <is>
-          <t>Кокорев Анатолий Сергеевич</t>
-        </is>
-      </c>
-      <c r="B226" s="46" t="inlineStr">
-        <is>
-          <t>19.06.1987</t>
-        </is>
-      </c>
-      <c r="C226" s="47" t="n"/>
-      <c r="D226" s="48" t="inlineStr">
-        <is>
-          <t>133-055-324 15</t>
-        </is>
-      </c>
-      <c r="E226" s="49" t="n"/>
-      <c r="F226" s="50" t="n"/>
-      <c r="G226" s="51" t="n"/>
-      <c r="H226" s="49" t="n"/>
-      <c r="I226" s="52" t="inlineStr">
-        <is>
-          <t>Мастер участка</t>
-        </is>
-      </c>
-      <c r="J226" s="52" t="inlineStr">
-        <is>
-          <t>Участок РЭО МШ</t>
-        </is>
-      </c>
-      <c r="K226" s="53" t="n"/>
-      <c r="L226" s="54" t="n"/>
-      <c r="M226" s="55" t="n"/>
-      <c r="N226" s="55" t="n"/>
-      <c r="O226" s="49" t="n"/>
-      <c r="P226" s="49" t="n"/>
-      <c r="Q226" s="48" t="n"/>
-      <c r="R226" s="49" t="n"/>
-      <c r="S226" s="49" t="n"/>
-      <c r="T226" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U226" s="55" t="inlineStr">
-        <is>
-          <t>п.11 Прил.№2: руководство работами по монтажу, наладке, ремонту электроустановок. Относится также мастер участка РЭО.</t>
-        </is>
-      </c>
-      <c r="V226" s="49" t="n"/>
-      <c r="W226" s="49" t="n"/>
-      <c r="X226" s="48" t="n"/>
-      <c r="Y226" s="49" t="n"/>
-      <c r="Z226" s="49" t="n"/>
-      <c r="AA226" s="49" t="n"/>
-      <c r="AB226" s="49" t="n"/>
-      <c r="AC226" s="49" t="n"/>
-      <c r="AD226" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ООО "Авиационные интерьеры -СН" </t>
-        </is>
-      </c>
-      <c r="AE226" s="49" t="inlineStr">
-        <is>
-          <t>Машково</t>
-        </is>
-      </c>
+      <c r="A226" s="41" t="n"/>
+      <c r="B226" s="42" t="n"/>
+      <c r="C226" s="32" t="n"/>
+      <c r="D226" s="40" t="n"/>
+      <c r="E226" s="32" t="n"/>
+      <c r="F226" s="31" t="n"/>
+      <c r="G226" s="43" t="n"/>
+      <c r="H226" s="44" t="n"/>
+      <c r="I226" s="42" t="n"/>
+      <c r="J226" s="44" t="n"/>
+      <c r="K226" s="31" t="n"/>
+      <c r="L226" s="31" t="n"/>
+      <c r="M226" s="31" t="n"/>
+      <c r="N226" s="31" t="n"/>
+      <c r="O226" s="32" t="n"/>
+      <c r="P226" s="32" t="n"/>
+      <c r="Q226" s="32" t="n"/>
+      <c r="R226" s="32" t="n"/>
+      <c r="S226" s="32" t="n"/>
+      <c r="T226" s="32" t="n"/>
+      <c r="U226" s="32" t="n"/>
+      <c r="V226" s="32" t="n"/>
+      <c r="W226" s="32" t="n"/>
+      <c r="X226" s="32" t="n"/>
+      <c r="Y226" s="32" t="n"/>
+      <c r="Z226" s="32" t="n"/>
+      <c r="AA226" s="32" t="n"/>
+      <c r="AB226" s="32" t="n"/>
+      <c r="AC226" s="32" t="n"/>
+      <c r="AD226" s="31" t="n"/>
+      <c r="AE226" s="6" t="n"/>
       <c r="AF226" s="6" t="n"/>
       <c r="AG226" s="6" t="n"/>
       <c r="AH226" s="6" t="n"/>
@@ -20011,73 +19995,37 @@
       <c r="AX226" s="6" t="n"/>
     </row>
     <row r="227" ht="12.75" customHeight="1">
-      <c r="A227" s="45" t="inlineStr">
-        <is>
-          <t>Гагарин Алексей Владимирович</t>
-        </is>
-      </c>
-      <c r="B227" s="46" t="inlineStr">
-        <is>
-          <t>30.03.1987</t>
-        </is>
-      </c>
-      <c r="C227" s="47" t="n"/>
-      <c r="D227" s="48" t="inlineStr">
-        <is>
-          <t>137-353-721 62</t>
-        </is>
-      </c>
-      <c r="E227" s="49" t="n"/>
-      <c r="F227" s="50" t="n"/>
-      <c r="G227" s="51" t="n"/>
-      <c r="H227" s="49" t="n"/>
-      <c r="I227" s="52" t="inlineStr">
-        <is>
-          <t>Кладовщик-комплектовщик</t>
-        </is>
-      </c>
-      <c r="J227" s="52" t="inlineStr">
-        <is>
-          <t>Склад Р</t>
-        </is>
-      </c>
-      <c r="K227" s="53" t="n"/>
-      <c r="L227" s="54" t="n"/>
-      <c r="M227" s="55" t="n"/>
-      <c r="N227" s="55" t="n"/>
-      <c r="O227" s="49" t="n"/>
-      <c r="P227" s="49" t="n"/>
-      <c r="Q227" s="48" t="n"/>
-      <c r="R227" s="49" t="n"/>
-      <c r="S227" s="49" t="n"/>
-      <c r="T227" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U227" s="55" t="inlineStr">
-        <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
-        </is>
-      </c>
-      <c r="V227" s="49" t="n"/>
-      <c r="W227" s="49" t="n"/>
-      <c r="X227" s="48" t="n"/>
-      <c r="Y227" s="49" t="n"/>
-      <c r="Z227" s="49" t="n"/>
-      <c r="AA227" s="49" t="n"/>
-      <c r="AB227" s="49" t="n"/>
-      <c r="AC227" s="49" t="n"/>
-      <c r="AD227" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ООО "Авиационные интерьеры -СН" </t>
-        </is>
-      </c>
-      <c r="AE227" s="49" t="inlineStr">
-        <is>
-          <t>Руднево</t>
-        </is>
-      </c>
+      <c r="A227" s="41" t="n"/>
+      <c r="B227" s="42" t="n"/>
+      <c r="C227" s="32" t="n"/>
+      <c r="D227" s="40" t="n"/>
+      <c r="E227" s="32" t="n"/>
+      <c r="F227" s="31" t="n"/>
+      <c r="G227" s="43" t="n"/>
+      <c r="H227" s="44" t="n"/>
+      <c r="I227" s="42" t="n"/>
+      <c r="J227" s="44" t="n"/>
+      <c r="K227" s="31" t="n"/>
+      <c r="L227" s="31" t="n"/>
+      <c r="M227" s="31" t="n"/>
+      <c r="N227" s="31" t="n"/>
+      <c r="O227" s="32" t="n"/>
+      <c r="P227" s="32" t="n"/>
+      <c r="Q227" s="32" t="n"/>
+      <c r="R227" s="32" t="n"/>
+      <c r="S227" s="32" t="n"/>
+      <c r="T227" s="32" t="n"/>
+      <c r="U227" s="32" t="n"/>
+      <c r="V227" s="32" t="n"/>
+      <c r="W227" s="32" t="n"/>
+      <c r="X227" s="32" t="n"/>
+      <c r="Y227" s="32" t="n"/>
+      <c r="Z227" s="32" t="n"/>
+      <c r="AA227" s="32" t="n"/>
+      <c r="AB227" s="32" t="n"/>
+      <c r="AC227" s="32" t="n"/>
+      <c r="AD227" s="31" t="n"/>
+      <c r="AE227" s="6" t="n"/>
       <c r="AF227" s="6" t="n"/>
       <c r="AG227" s="6" t="n"/>
       <c r="AH227" s="6" t="n"/>
@@ -20099,73 +20047,37 @@
       <c r="AX227" s="6" t="n"/>
     </row>
     <row r="228" ht="12.75" customHeight="1">
-      <c r="A228" s="45" t="inlineStr">
-        <is>
-          <t>Иванов Дмитрий Сергеевич</t>
-        </is>
-      </c>
-      <c r="B228" s="46" t="inlineStr">
-        <is>
-          <t>15.07.1996</t>
-        </is>
-      </c>
-      <c r="C228" s="47" t="n"/>
-      <c r="D228" s="48" t="inlineStr">
-        <is>
-          <t>165-320-758 58</t>
-        </is>
-      </c>
-      <c r="E228" s="49" t="n"/>
-      <c r="F228" s="50" t="n"/>
-      <c r="G228" s="51" t="n"/>
-      <c r="H228" s="49" t="n"/>
-      <c r="I228" s="52" t="inlineStr">
-        <is>
-          <t>Кладовщик-комплектовщик</t>
-        </is>
-      </c>
-      <c r="J228" s="52" t="inlineStr">
-        <is>
-          <t>Склад Р</t>
-        </is>
-      </c>
-      <c r="K228" s="53" t="n"/>
-      <c r="L228" s="54" t="n"/>
-      <c r="M228" s="55" t="n"/>
-      <c r="N228" s="55" t="n"/>
-      <c r="O228" s="49" t="n"/>
-      <c r="P228" s="49" t="n"/>
-      <c r="Q228" s="48" t="n"/>
-      <c r="R228" s="49" t="n"/>
-      <c r="S228" s="49" t="n"/>
-      <c r="T228" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U228" s="55" t="inlineStr">
-        <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
-        </is>
-      </c>
-      <c r="V228" s="49" t="n"/>
-      <c r="W228" s="49" t="n"/>
-      <c r="X228" s="48" t="n"/>
-      <c r="Y228" s="49" t="n"/>
-      <c r="Z228" s="49" t="n"/>
-      <c r="AA228" s="49" t="n"/>
-      <c r="AB228" s="49" t="n"/>
-      <c r="AC228" s="49" t="n"/>
-      <c r="AD228" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ООО "Авиационные интерьеры -СН" </t>
-        </is>
-      </c>
-      <c r="AE228" s="49" t="inlineStr">
-        <is>
-          <t>Руднево</t>
-        </is>
-      </c>
+      <c r="A228" s="41" t="n"/>
+      <c r="B228" s="42" t="n"/>
+      <c r="C228" s="32" t="n"/>
+      <c r="D228" s="40" t="n"/>
+      <c r="E228" s="32" t="n"/>
+      <c r="F228" s="31" t="n"/>
+      <c r="G228" s="43" t="n"/>
+      <c r="H228" s="44" t="n"/>
+      <c r="I228" s="42" t="n"/>
+      <c r="J228" s="44" t="n"/>
+      <c r="K228" s="31" t="n"/>
+      <c r="L228" s="31" t="n"/>
+      <c r="M228" s="31" t="n"/>
+      <c r="N228" s="31" t="n"/>
+      <c r="O228" s="32" t="n"/>
+      <c r="P228" s="32" t="n"/>
+      <c r="Q228" s="32" t="n"/>
+      <c r="R228" s="32" t="n"/>
+      <c r="S228" s="32" t="n"/>
+      <c r="T228" s="32" t="n"/>
+      <c r="U228" s="32" t="n"/>
+      <c r="V228" s="32" t="n"/>
+      <c r="W228" s="32" t="n"/>
+      <c r="X228" s="32" t="n"/>
+      <c r="Y228" s="32" t="n"/>
+      <c r="Z228" s="32" t="n"/>
+      <c r="AA228" s="32" t="n"/>
+      <c r="AB228" s="32" t="n"/>
+      <c r="AC228" s="32" t="n"/>
+      <c r="AD228" s="31" t="n"/>
+      <c r="AE228" s="6" t="n"/>
       <c r="AF228" s="6" t="n"/>
       <c r="AG228" s="6" t="n"/>
       <c r="AH228" s="6" t="n"/>
@@ -20187,73 +20099,37 @@
       <c r="AX228" s="6" t="n"/>
     </row>
     <row r="229" ht="12.75" customHeight="1">
-      <c r="A229" s="45" t="inlineStr">
-        <is>
-          <t>Поляков Александр Валентинович</t>
-        </is>
-      </c>
-      <c r="B229" s="46" t="inlineStr">
-        <is>
-          <t>08.01.1984</t>
-        </is>
-      </c>
-      <c r="C229" s="47" t="n"/>
-      <c r="D229" s="48" t="inlineStr">
-        <is>
-          <t>114-455-402 27</t>
-        </is>
-      </c>
-      <c r="E229" s="49" t="n"/>
-      <c r="F229" s="50" t="n"/>
-      <c r="G229" s="51" t="n"/>
-      <c r="H229" s="49" t="n"/>
-      <c r="I229" s="52" t="inlineStr">
-        <is>
-          <t>Кладовщик-комплектовщик</t>
-        </is>
-      </c>
-      <c r="J229" s="52" t="inlineStr">
-        <is>
-          <t>Склад Р</t>
-        </is>
-      </c>
-      <c r="K229" s="53" t="n"/>
-      <c r="L229" s="54" t="n"/>
-      <c r="M229" s="55" t="n"/>
-      <c r="N229" s="55" t="n"/>
-      <c r="O229" s="49" t="n"/>
-      <c r="P229" s="49" t="n"/>
-      <c r="Q229" s="48" t="n"/>
-      <c r="R229" s="49" t="n"/>
-      <c r="S229" s="49" t="n"/>
-      <c r="T229" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U229" s="55" t="inlineStr">
-        <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
-        </is>
-      </c>
-      <c r="V229" s="49" t="n"/>
-      <c r="W229" s="49" t="n"/>
-      <c r="X229" s="48" t="n"/>
-      <c r="Y229" s="49" t="n"/>
-      <c r="Z229" s="49" t="n"/>
-      <c r="AA229" s="49" t="n"/>
-      <c r="AB229" s="49" t="n"/>
-      <c r="AC229" s="49" t="n"/>
-      <c r="AD229" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ООО "Авиационные интерьеры -СН" </t>
-        </is>
-      </c>
-      <c r="AE229" s="49" t="inlineStr">
-        <is>
-          <t>Руднево</t>
-        </is>
-      </c>
+      <c r="A229" s="41" t="n"/>
+      <c r="B229" s="42" t="n"/>
+      <c r="C229" s="32" t="n"/>
+      <c r="D229" s="40" t="n"/>
+      <c r="E229" s="32" t="n"/>
+      <c r="F229" s="31" t="n"/>
+      <c r="G229" s="43" t="n"/>
+      <c r="H229" s="44" t="n"/>
+      <c r="I229" s="42" t="n"/>
+      <c r="J229" s="44" t="n"/>
+      <c r="K229" s="31" t="n"/>
+      <c r="L229" s="31" t="n"/>
+      <c r="M229" s="31" t="n"/>
+      <c r="N229" s="31" t="n"/>
+      <c r="O229" s="32" t="n"/>
+      <c r="P229" s="32" t="n"/>
+      <c r="Q229" s="32" t="n"/>
+      <c r="R229" s="32" t="n"/>
+      <c r="S229" s="32" t="n"/>
+      <c r="T229" s="32" t="n"/>
+      <c r="U229" s="32" t="n"/>
+      <c r="V229" s="32" t="n"/>
+      <c r="W229" s="32" t="n"/>
+      <c r="X229" s="32" t="n"/>
+      <c r="Y229" s="32" t="n"/>
+      <c r="Z229" s="32" t="n"/>
+      <c r="AA229" s="32" t="n"/>
+      <c r="AB229" s="32" t="n"/>
+      <c r="AC229" s="32" t="n"/>
+      <c r="AD229" s="31" t="n"/>
+      <c r="AE229" s="6" t="n"/>
       <c r="AF229" s="6" t="n"/>
       <c r="AG229" s="6" t="n"/>
       <c r="AH229" s="6" t="n"/>
@@ -20275,73 +20151,37 @@
       <c r="AX229" s="6" t="n"/>
     </row>
     <row r="230" ht="12.75" customHeight="1">
-      <c r="A230" s="45" t="inlineStr">
-        <is>
-          <t>Улумбеков Руслан Бинарович</t>
-        </is>
-      </c>
-      <c r="B230" s="46" t="inlineStr">
-        <is>
-          <t>30.06.1978</t>
-        </is>
-      </c>
-      <c r="C230" s="47" t="n"/>
-      <c r="D230" s="48" t="inlineStr">
-        <is>
-          <t>053-851-554 66</t>
-        </is>
-      </c>
-      <c r="E230" s="49" t="n"/>
-      <c r="F230" s="50" t="n"/>
-      <c r="G230" s="51" t="n"/>
-      <c r="H230" s="49" t="n"/>
-      <c r="I230" s="52" t="inlineStr">
-        <is>
-          <t>Электромонтер по ремонту и обслуживанию электрооборудования 4 разряда</t>
-        </is>
-      </c>
-      <c r="J230" s="52" t="inlineStr">
-        <is>
-          <t>Служба главного инженера Р</t>
-        </is>
-      </c>
-      <c r="K230" s="53" t="n"/>
-      <c r="L230" s="54" t="n"/>
-      <c r="M230" s="55" t="n"/>
-      <c r="N230" s="55" t="n"/>
-      <c r="O230" s="49" t="n"/>
-      <c r="P230" s="49" t="n"/>
-      <c r="Q230" s="48" t="n"/>
-      <c r="R230" s="49" t="n"/>
-      <c r="S230" s="49" t="n"/>
-      <c r="T230" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U230" s="55" t="inlineStr">
-        <is>
-          <t>п.11 Прил.№2: обслуживание электроустановок предприятия.</t>
-        </is>
-      </c>
-      <c r="V230" s="49" t="n"/>
-      <c r="W230" s="49" t="n"/>
-      <c r="X230" s="48" t="n"/>
-      <c r="Y230" s="49" t="n"/>
-      <c r="Z230" s="49" t="n"/>
-      <c r="AA230" s="49" t="n"/>
-      <c r="AB230" s="49" t="n"/>
-      <c r="AC230" s="49" t="n"/>
-      <c r="AD230" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ООО "Авиационные интерьеры -СН" </t>
-        </is>
-      </c>
-      <c r="AE230" s="49" t="inlineStr">
-        <is>
-          <t>Руднево</t>
-        </is>
-      </c>
+      <c r="A230" s="41" t="n"/>
+      <c r="B230" s="42" t="n"/>
+      <c r="C230" s="32" t="n"/>
+      <c r="D230" s="40" t="n"/>
+      <c r="E230" s="32" t="n"/>
+      <c r="F230" s="31" t="n"/>
+      <c r="G230" s="43" t="n"/>
+      <c r="H230" s="44" t="n"/>
+      <c r="I230" s="42" t="n"/>
+      <c r="J230" s="44" t="n"/>
+      <c r="K230" s="31" t="n"/>
+      <c r="L230" s="31" t="n"/>
+      <c r="M230" s="31" t="n"/>
+      <c r="N230" s="31" t="n"/>
+      <c r="O230" s="32" t="n"/>
+      <c r="P230" s="32" t="n"/>
+      <c r="Q230" s="32" t="n"/>
+      <c r="R230" s="32" t="n"/>
+      <c r="S230" s="32" t="n"/>
+      <c r="T230" s="32" t="n"/>
+      <c r="U230" s="32" t="n"/>
+      <c r="V230" s="32" t="n"/>
+      <c r="W230" s="32" t="n"/>
+      <c r="X230" s="32" t="n"/>
+      <c r="Y230" s="32" t="n"/>
+      <c r="Z230" s="32" t="n"/>
+      <c r="AA230" s="32" t="n"/>
+      <c r="AB230" s="32" t="n"/>
+      <c r="AC230" s="32" t="n"/>
+      <c r="AD230" s="31" t="n"/>
+      <c r="AE230" s="6" t="n"/>
       <c r="AF230" s="6" t="n"/>
       <c r="AG230" s="6" t="n"/>
       <c r="AH230" s="6" t="n"/>

--- a/МО 19.10.2026/Шаблон ЛМК проф ОПО — Машково и Руднево (ред. 19.10.2026).xlsx
+++ b/МО 19.10.2026/Шаблон ЛМК проф ОПО — Машково и Руднево (ред. 19.10.2026).xlsx
@@ -1027,7 +1027,7 @@
       <c r="F3" s="50" t="n"/>
       <c r="G3" s="51" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.3.1, п.4.4, п.5.1</t>
+          <t>п.1.48, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="H3" s="49" t="n"/>
@@ -1111,7 +1111,7 @@
       <c r="F4" s="50" t="n"/>
       <c r="G4" s="51" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.3.1, п.4.4, п.5.1</t>
+          <t>п.1.48, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="H4" s="49" t="n"/>
@@ -1195,7 +1195,7 @@
       <c r="F5" s="50" t="n"/>
       <c r="G5" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H5" s="49" t="n"/>
@@ -1279,7 +1279,7 @@
       <c r="F6" s="50" t="n"/>
       <c r="G6" s="51" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.3.1, п.4.4, п.5.1</t>
+          <t>п.1.48, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="H6" s="49" t="n"/>
@@ -1363,7 +1363,7 @@
       <c r="F7" s="50" t="n"/>
       <c r="G7" s="51" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.3.1, п.4.4, п.5.1</t>
+          <t>п.1.48, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="H7" s="49" t="n"/>
@@ -1447,7 +1447,7 @@
       <c r="F8" s="50" t="n"/>
       <c r="G8" s="51" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.3.1, п.4.4, п.5.1</t>
+          <t>п.1.48, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="H8" s="49" t="n"/>
@@ -1531,7 +1531,7 @@
       <c r="F9" s="50" t="n"/>
       <c r="G9" s="51" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.3.1, п.4.4, п.5.1</t>
+          <t>п.1.48, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="H9" s="49" t="n"/>
@@ -3547,7 +3547,7 @@
       <c r="F33" s="50" t="n"/>
       <c r="G33" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H33" s="49" t="n"/>
@@ -3631,7 +3631,7 @@
       <c r="F34" s="50" t="n"/>
       <c r="G34" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H34" s="49" t="n"/>
@@ -6067,7 +6067,7 @@
       <c r="F63" s="50" t="n"/>
       <c r="G63" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H63" s="49" t="n"/>
@@ -7075,7 +7075,7 @@
       <c r="F75" s="50" t="n"/>
       <c r="G75" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H75" s="49" t="n"/>
@@ -7159,7 +7159,7 @@
       <c r="F76" s="50" t="n"/>
       <c r="G76" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H76" s="49" t="n"/>
@@ -7243,7 +7243,7 @@
       <c r="F77" s="50" t="n"/>
       <c r="G77" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H77" s="49" t="n"/>
@@ -7327,7 +7327,7 @@
       <c r="F78" s="50" t="n"/>
       <c r="G78" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H78" s="49" t="n"/>
@@ -7411,7 +7411,7 @@
       <c r="F79" s="50" t="n"/>
       <c r="G79" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H79" s="49" t="n"/>
@@ -7495,7 +7495,7 @@
       <c r="F80" s="50" t="n"/>
       <c r="G80" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H80" s="49" t="n"/>
@@ -7579,7 +7579,7 @@
       <c r="F81" s="50" t="n"/>
       <c r="G81" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18.2</t>
         </is>
       </c>
       <c r="H81" s="49" t="n"/>
@@ -7671,7 +7671,7 @@
       <c r="F82" s="50" t="n"/>
       <c r="G82" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18.1</t>
         </is>
       </c>
       <c r="H82" s="49" t="n"/>
@@ -7763,7 +7763,7 @@
       <c r="F83" s="50" t="n"/>
       <c r="G83" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18.1</t>
         </is>
       </c>
       <c r="H83" s="49" t="n"/>
@@ -7855,7 +7855,7 @@
       <c r="F84" s="50" t="n"/>
       <c r="G84" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18.2</t>
         </is>
       </c>
       <c r="H84" s="49" t="n"/>
@@ -7947,7 +7947,7 @@
       <c r="F85" s="50" t="n"/>
       <c r="G85" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18.1</t>
         </is>
       </c>
       <c r="H85" s="49" t="n"/>
@@ -8039,7 +8039,7 @@
       <c r="F86" s="50" t="n"/>
       <c r="G86" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18.1</t>
         </is>
       </c>
       <c r="H86" s="49" t="n"/>
@@ -8131,7 +8131,7 @@
       <c r="F87" s="50" t="n"/>
       <c r="G87" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18.2</t>
         </is>
       </c>
       <c r="H87" s="49" t="n"/>
@@ -8223,7 +8223,7 @@
       <c r="F88" s="50" t="n"/>
       <c r="G88" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18.1</t>
         </is>
       </c>
       <c r="H88" s="49" t="n"/>
@@ -8315,7 +8315,7 @@
       <c r="F89" s="50" t="n"/>
       <c r="G89" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.18.1</t>
         </is>
       </c>
       <c r="H89" s="49" t="n"/>
@@ -8407,7 +8407,7 @@
       <c r="F90" s="50" t="n"/>
       <c r="G90" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H90" s="49" t="n"/>
@@ -8491,7 +8491,7 @@
       <c r="F91" s="50" t="n"/>
       <c r="G91" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H91" s="49" t="n"/>
@@ -8575,7 +8575,7 @@
       <c r="F92" s="50" t="n"/>
       <c r="G92" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H92" s="49" t="n"/>
@@ -8659,7 +8659,7 @@
       <c r="F93" s="50" t="n"/>
       <c r="G93" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H93" s="49" t="n"/>
@@ -8743,7 +8743,7 @@
       <c r="F94" s="50" t="n"/>
       <c r="G94" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H94" s="49" t="n"/>
@@ -8827,7 +8827,7 @@
       <c r="F95" s="50" t="n"/>
       <c r="G95" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H95" s="49" t="n"/>
@@ -8911,7 +8911,7 @@
       <c r="F96" s="50" t="n"/>
       <c r="G96" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H96" s="49" t="n"/>
@@ -8995,7 +8995,7 @@
       <c r="F97" s="50" t="n"/>
       <c r="G97" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H97" s="49" t="n"/>
@@ -9079,7 +9079,7 @@
       <c r="F98" s="50" t="n"/>
       <c r="G98" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H98" s="49" t="n"/>
@@ -9163,7 +9163,7 @@
       <c r="F99" s="50" t="n"/>
       <c r="G99" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H99" s="49" t="n"/>
@@ -9247,7 +9247,7 @@
       <c r="F100" s="50" t="n"/>
       <c r="G100" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H100" s="49" t="n"/>
@@ -9331,7 +9331,7 @@
       <c r="F101" s="50" t="n"/>
       <c r="G101" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H101" s="49" t="n"/>
@@ -9415,7 +9415,7 @@
       <c r="F102" s="50" t="n"/>
       <c r="G102" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H102" s="49" t="n"/>
@@ -14651,7 +14651,7 @@
       <c r="F163" s="50" t="n"/>
       <c r="G163" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H163" s="49" t="n"/>
@@ -15071,7 +15071,7 @@
       <c r="F168" s="50" t="n"/>
       <c r="G168" s="51" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.3.1, п.4.4, п.5.1</t>
+          <t>п.1.48, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="H168" s="49" t="n"/>
@@ -15155,7 +15155,7 @@
       <c r="F169" s="50" t="n"/>
       <c r="G169" s="51" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.3.1, п.4.4, п.5.1</t>
+          <t>п.1.48, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="H169" s="49" t="n"/>
@@ -15239,7 +15239,7 @@
       <c r="F170" s="50" t="n"/>
       <c r="G170" s="51" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.3.1, п.4.4, п.5.1</t>
+          <t>п.1.48, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="H170" s="49" t="n"/>
@@ -15323,7 +15323,7 @@
       <c r="F171" s="50" t="n"/>
       <c r="G171" s="51" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.3.1, п.4.4, п.5.1</t>
+          <t>п.1.48, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="H171" s="49" t="n"/>
@@ -16499,7 +16499,7 @@
       <c r="F185" s="50" t="n"/>
       <c r="G185" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H185" s="49" t="n"/>
@@ -16583,7 +16583,7 @@
       <c r="F186" s="50" t="n"/>
       <c r="G186" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H186" s="49" t="n"/>
@@ -16667,7 +16667,7 @@
       <c r="F187" s="50" t="n"/>
       <c r="G187" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H187" s="49" t="n"/>
@@ -16751,7 +16751,7 @@
       <c r="F188" s="50" t="n"/>
       <c r="G188" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H188" s="49" t="n"/>
@@ -16835,7 +16835,7 @@
       <c r="F189" s="50" t="n"/>
       <c r="G189" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H189" s="49" t="n"/>
@@ -18431,7 +18431,7 @@
       <c r="F208" s="50" t="n"/>
       <c r="G208" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H208" s="49" t="n"/>

--- a/МО 19.10.2026/Шаблон ЛМК проф ОПО — Машково и Руднево (ред. 19.10.2026).xlsx
+++ b/МО 19.10.2026/Шаблон ЛМК проф ОПО — Машково и Руднево (ред. 19.10.2026).xlsx
@@ -1038,7 +1038,7 @@
       </c>
       <c r="J3" s="52" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел МШ</t>
+          <t>Административно-хозяйственный отдел</t>
         </is>
       </c>
       <c r="K3" s="53" t="n"/>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="J4" s="52" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел МШ</t>
+          <t>Административно-хозяйственный отдел</t>
         </is>
       </c>
       <c r="K4" s="53" t="n"/>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="J5" s="52" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел МШ</t>
+          <t>Административно-хозяйственный отдел</t>
         </is>
       </c>
       <c r="K5" s="53" t="n"/>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J6" s="52" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел МШ</t>
+          <t>Административно-хозяйственный отдел</t>
         </is>
       </c>
       <c r="K6" s="53" t="n"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="J7" s="52" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел МШ</t>
+          <t>Административно-хозяйственный отдел</t>
         </is>
       </c>
       <c r="K7" s="53" t="n"/>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="J8" s="52" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел МШ</t>
+          <t>Административно-хозяйственный отдел</t>
         </is>
       </c>
       <c r="K8" s="53" t="n"/>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="J9" s="52" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел МШ</t>
+          <t>Административно-хозяйственный отдел</t>
         </is>
       </c>
       <c r="K9" s="53" t="n"/>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="J10" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K10" s="53" t="n"/>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="J11" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K11" s="53" t="n"/>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="J12" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K12" s="53" t="n"/>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="J13" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K13" s="53" t="n"/>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="J14" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K14" s="53" t="n"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="J15" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K15" s="53" t="n"/>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="J16" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K16" s="53" t="n"/>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="J17" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K17" s="53" t="n"/>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="J18" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K18" s="53" t="n"/>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="J19" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K19" s="53" t="n"/>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="J20" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K20" s="53" t="n"/>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="J21" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K21" s="53" t="n"/>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="J22" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K22" s="53" t="n"/>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="J23" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K23" s="53" t="n"/>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="J24" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K24" s="53" t="n"/>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="J25" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K25" s="53" t="n"/>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="J26" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K26" s="53" t="n"/>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="J27" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K27" s="53" t="n"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="J28" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K28" s="53" t="n"/>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="J29" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K29" s="53" t="n"/>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="J30" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K30" s="53" t="n"/>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="J31" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K31" s="53" t="n"/>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="J32" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K32" s="53" t="n"/>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="J33" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K33" s="53" t="n"/>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="J34" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K34" s="53" t="n"/>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="J35" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K35" s="53" t="n"/>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="J36" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K36" s="53" t="n"/>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="J37" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K37" s="53" t="n"/>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="J38" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K38" s="53" t="n"/>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="J39" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K39" s="53" t="n"/>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="J40" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K40" s="53" t="n"/>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="J41" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K41" s="53" t="n"/>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="J42" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K42" s="53" t="n"/>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="J43" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K43" s="53" t="n"/>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="J44" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K44" s="53" t="n"/>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="J45" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K45" s="53" t="n"/>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="J46" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K46" s="53" t="n"/>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="J47" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K47" s="53" t="n"/>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="J48" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K48" s="53" t="n"/>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="J49" s="52" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="K49" s="53" t="n"/>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="J50" s="52" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K50" s="53" t="n"/>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="J51" s="52" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K51" s="53" t="n"/>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="J52" s="52" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K52" s="53" t="n"/>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="J53" s="52" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K53" s="53" t="n"/>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="J54" s="52" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K54" s="53" t="n"/>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="J55" s="52" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K55" s="53" t="n"/>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="J56" s="52" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K56" s="53" t="n"/>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="J57" s="52" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K57" s="53" t="n"/>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="J58" s="52" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K58" s="53" t="n"/>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="J59" s="52" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K59" s="53" t="n"/>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="J60" s="52" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K60" s="53" t="n"/>
@@ -5881,18 +5881,18 @@
     <row r="61" ht="12.75" customHeight="1">
       <c r="A61" s="45" t="inlineStr">
         <is>
-          <t>Саранцев Петр Дмитриевич</t>
+          <t>Птицын Юрий Юрьевич</t>
         </is>
       </c>
       <c r="B61" s="46" t="inlineStr">
         <is>
-          <t>16.05.2001</t>
+          <t>26.01.1988</t>
         </is>
       </c>
       <c r="C61" s="47" t="n"/>
       <c r="D61" s="48" t="inlineStr">
         <is>
-          <t>150-514-561 27</t>
+          <t>128-866-839 20</t>
         </is>
       </c>
       <c r="E61" s="49" t="n"/>
@@ -5905,12 +5905,12 @@
       <c r="H61" s="49" t="n"/>
       <c r="I61" s="52" t="inlineStr">
         <is>
-          <t>Токарь 5 разряда</t>
+          <t>Оператор-наладчик станков с ЧПУ</t>
         </is>
       </c>
       <c r="J61" s="52" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K61" s="53" t="n"/>
@@ -5965,18 +5965,18 @@
     <row r="62" ht="12.75" customHeight="1">
       <c r="A62" s="45" t="inlineStr">
         <is>
-          <t>Тарасов Борис Анатольевич</t>
+          <t>Саранцев Петр Дмитриевич</t>
         </is>
       </c>
       <c r="B62" s="46" t="inlineStr">
         <is>
-          <t>20.04.1959</t>
+          <t>16.05.2001</t>
         </is>
       </c>
       <c r="C62" s="47" t="n"/>
       <c r="D62" s="48" t="inlineStr">
         <is>
-          <t>013-505-131 89</t>
+          <t>150-514-561 27</t>
         </is>
       </c>
       <c r="E62" s="49" t="n"/>
@@ -5989,12 +5989,12 @@
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="52" t="inlineStr">
         <is>
-          <t>Фрезеровщик 6 разряда</t>
+          <t>Токарь 5 разряда</t>
         </is>
       </c>
       <c r="J62" s="52" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K62" s="53" t="n"/>
@@ -6049,36 +6049,36 @@
     <row r="63" ht="12.75" customHeight="1">
       <c r="A63" s="45" t="inlineStr">
         <is>
-          <t>Фокина Светлана Геннадиевна</t>
+          <t>Тарасов Борис Анатольевич</t>
         </is>
       </c>
       <c r="B63" s="46" t="inlineStr">
         <is>
-          <t>18.10.1975</t>
+          <t>20.04.1959</t>
         </is>
       </c>
       <c r="C63" s="47" t="n"/>
       <c r="D63" s="48" t="inlineStr">
         <is>
-          <t>108-330-307 13</t>
+          <t>013-505-131 89</t>
         </is>
       </c>
       <c r="E63" s="49" t="n"/>
       <c r="F63" s="50" t="n"/>
       <c r="G63" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="H63" s="49" t="n"/>
       <c r="I63" s="52" t="inlineStr">
         <is>
-          <t>Мастер участка</t>
+          <t>Фрезеровщик 6 разряда</t>
         </is>
       </c>
       <c r="J63" s="52" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K63" s="53" t="n"/>
@@ -6133,36 +6133,36 @@
     <row r="64" ht="12.75" customHeight="1">
       <c r="A64" s="45" t="inlineStr">
         <is>
-          <t>Юдаков Алексей Викторович</t>
+          <t>Фокина Светлана Геннадиевна</t>
         </is>
       </c>
       <c r="B64" s="46" t="inlineStr">
         <is>
-          <t>26.03.1980</t>
+          <t>18.10.1975</t>
         </is>
       </c>
       <c r="C64" s="47" t="n"/>
       <c r="D64" s="48" t="inlineStr">
         <is>
-          <t>043-924-645 63</t>
+          <t>108-330-307 13</t>
         </is>
       </c>
       <c r="E64" s="49" t="n"/>
       <c r="F64" s="50" t="n"/>
       <c r="G64" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="H64" s="49" t="n"/>
       <c r="I64" s="52" t="inlineStr">
         <is>
-          <t>Токарь 5 разряда</t>
+          <t>Мастер участка</t>
         </is>
       </c>
       <c r="J64" s="52" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K64" s="53" t="n"/>
@@ -6217,18 +6217,18 @@
     <row r="65" ht="12.75" customHeight="1">
       <c r="A65" s="45" t="inlineStr">
         <is>
-          <t>Птицын Юрий Юрьевич</t>
+          <t>Юдаков Алексей Викторович</t>
         </is>
       </c>
       <c r="B65" s="46" t="inlineStr">
         <is>
-          <t>26.01.1988</t>
+          <t>26.03.1980</t>
         </is>
       </c>
       <c r="C65" s="47" t="n"/>
       <c r="D65" s="48" t="inlineStr">
         <is>
-          <t>128-866-839 20</t>
+          <t>043-924-645 63</t>
         </is>
       </c>
       <c r="E65" s="49" t="n"/>
@@ -6241,12 +6241,12 @@
       <c r="H65" s="49" t="n"/>
       <c r="I65" s="52" t="inlineStr">
         <is>
-          <t>Оператор-наладчик станков с ЧПУ</t>
+          <t>Токарь 5 разряда</t>
         </is>
       </c>
       <c r="J65" s="52" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K65" s="53" t="n"/>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="J66" s="52" t="inlineStr">
         <is>
-          <t>Отдел режима МШ</t>
+          <t>Отдел режима</t>
         </is>
       </c>
       <c r="K66" s="53" t="n"/>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="J67" s="52" t="inlineStr">
         <is>
-          <t>Отдел режима МШ</t>
+          <t>Отдел режима</t>
         </is>
       </c>
       <c r="K67" s="53" t="n"/>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="J68" s="52" t="inlineStr">
         <is>
-          <t>Отдел режима МШ</t>
+          <t>Отдел режима</t>
         </is>
       </c>
       <c r="K68" s="53" t="n"/>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="J69" s="52" t="inlineStr">
         <is>
-          <t>Отдел режима МШ</t>
+          <t>Отдел режима</t>
         </is>
       </c>
       <c r="K69" s="53" t="n"/>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="J70" s="52" t="inlineStr">
         <is>
-          <t>Отдел режима МШ</t>
+          <t>Отдел режима</t>
         </is>
       </c>
       <c r="K70" s="53" t="n"/>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="J71" s="52" t="inlineStr">
         <is>
-          <t>Отдел режима МШ</t>
+          <t>Отдел режима</t>
         </is>
       </c>
       <c r="K71" s="53" t="n"/>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="J72" s="52" t="inlineStr">
         <is>
-          <t>Отдел режима МШ</t>
+          <t>Отдел режима</t>
         </is>
       </c>
       <c r="K72" s="53" t="n"/>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="J73" s="52" t="inlineStr">
         <is>
-          <t>Отдел режима МШ</t>
+          <t>Отдел режима</t>
         </is>
       </c>
       <c r="K73" s="53" t="n"/>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="J74" s="52" t="inlineStr">
         <is>
-          <t>Отдел режима МШ</t>
+          <t>Отдел режима</t>
         </is>
       </c>
       <c r="K74" s="53" t="n"/>
@@ -7057,18 +7057,18 @@
     <row r="75" ht="12.75" customHeight="1">
       <c r="A75" s="45" t="inlineStr">
         <is>
-          <t>Ермакова Наталья Васильевна</t>
+          <t>Божьева Ирина Вячеславовна</t>
         </is>
       </c>
       <c r="B75" s="46" t="inlineStr">
         <is>
-          <t>15.03.1983</t>
+          <t>14.09.1983</t>
         </is>
       </c>
       <c r="C75" s="47" t="n"/>
       <c r="D75" s="48" t="inlineStr">
         <is>
-          <t>084-319-031 57</t>
+          <t>125-706-271 46</t>
         </is>
       </c>
       <c r="E75" s="49" t="n"/>
@@ -7081,12 +7081,12 @@
       <c r="H75" s="49" t="n"/>
       <c r="I75" s="52" t="inlineStr">
         <is>
-          <t>Контролер 1 категории</t>
+          <t>Инженер 3 категории</t>
         </is>
       </c>
       <c r="J75" s="52" t="inlineStr">
         <is>
-          <t>Отдел технического контроля М</t>
+          <t>Отдел технического контроля</t>
         </is>
       </c>
       <c r="K75" s="53" t="n"/>
@@ -7141,18 +7141,18 @@
     <row r="76" ht="12.75" customHeight="1">
       <c r="A76" s="45" t="inlineStr">
         <is>
-          <t>Шрамко Наталья Викторовна</t>
+          <t>Васильева Алина Владимировна</t>
         </is>
       </c>
       <c r="B76" s="46" t="inlineStr">
         <is>
-          <t>08.04.1980</t>
+          <t>28.02.1987</t>
         </is>
       </c>
       <c r="C76" s="47" t="n"/>
       <c r="D76" s="48" t="inlineStr">
         <is>
-          <t>209-966-113 96</t>
+          <t>126-910-880 65</t>
         </is>
       </c>
       <c r="E76" s="49" t="n"/>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="J76" s="52" t="inlineStr">
         <is>
-          <t>Отдел технического контроля М</t>
+          <t>Отдел технического контроля</t>
         </is>
       </c>
       <c r="K76" s="53" t="n"/>
@@ -7225,18 +7225,18 @@
     <row r="77" ht="12.75" customHeight="1">
       <c r="A77" s="45" t="inlineStr">
         <is>
-          <t>Ястребов Александр Сергеевич</t>
+          <t>Райкова Ирина Алексеевна</t>
         </is>
       </c>
       <c r="B77" s="46" t="inlineStr">
         <is>
-          <t>21.04.1985</t>
+          <t>27.04.2001</t>
         </is>
       </c>
       <c r="C77" s="47" t="n"/>
       <c r="D77" s="48" t="inlineStr">
         <is>
-          <t>077-644-645 06</t>
+          <t>171-161-045 24</t>
         </is>
       </c>
       <c r="E77" s="49" t="n"/>
@@ -7249,12 +7249,12 @@
       <c r="H77" s="49" t="n"/>
       <c r="I77" s="52" t="inlineStr">
         <is>
-          <t>Инженер 1 категории</t>
+          <t>Контролер 1 категории</t>
         </is>
       </c>
       <c r="J77" s="52" t="inlineStr">
         <is>
-          <t>Отдел технического контроля М</t>
+          <t>Отдел технического контроля</t>
         </is>
       </c>
       <c r="K77" s="53" t="n"/>
@@ -7309,18 +7309,18 @@
     <row r="78" ht="12.75" customHeight="1">
       <c r="A78" s="45" t="inlineStr">
         <is>
-          <t>Божьева Ирина Вячеславовна</t>
+          <t>Ермакова Наталья Васильевна</t>
         </is>
       </c>
       <c r="B78" s="46" t="inlineStr">
         <is>
-          <t>14.09.1983</t>
+          <t>15.03.1983</t>
         </is>
       </c>
       <c r="C78" s="47" t="n"/>
       <c r="D78" s="48" t="inlineStr">
         <is>
-          <t>125-706-271 46</t>
+          <t>084-319-031 57</t>
         </is>
       </c>
       <c r="E78" s="49" t="n"/>
@@ -7333,12 +7333,12 @@
       <c r="H78" s="49" t="n"/>
       <c r="I78" s="52" t="inlineStr">
         <is>
-          <t>Инженер 3 категории</t>
+          <t>Контролер 1 категории</t>
         </is>
       </c>
       <c r="J78" s="52" t="inlineStr">
         <is>
-          <t>Отдел технического контроля МШ</t>
+          <t>Отдел технического контроля М</t>
         </is>
       </c>
       <c r="K78" s="53" t="n"/>
@@ -7393,18 +7393,18 @@
     <row r="79" ht="12.75" customHeight="1">
       <c r="A79" s="45" t="inlineStr">
         <is>
-          <t>Васильева Алина Владимировна</t>
+          <t>Шрамко Наталья Викторовна</t>
         </is>
       </c>
       <c r="B79" s="46" t="inlineStr">
         <is>
-          <t>28.02.1987</t>
+          <t>08.04.1980</t>
         </is>
       </c>
       <c r="C79" s="47" t="n"/>
       <c r="D79" s="48" t="inlineStr">
         <is>
-          <t>126-910-880 65</t>
+          <t>209-966-113 96</t>
         </is>
       </c>
       <c r="E79" s="49" t="n"/>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="J79" s="52" t="inlineStr">
         <is>
-          <t>Отдел технического контроля МШ</t>
+          <t>Отдел технического контроля М</t>
         </is>
       </c>
       <c r="K79" s="53" t="n"/>
@@ -7477,18 +7477,18 @@
     <row r="80" ht="12.75" customHeight="1">
       <c r="A80" s="45" t="inlineStr">
         <is>
-          <t>Райкова Ирина Алексеевна</t>
+          <t>Ястребов Александр Сергеевич</t>
         </is>
       </c>
       <c r="B80" s="46" t="inlineStr">
         <is>
-          <t>27.04.2001</t>
+          <t>21.04.1985</t>
         </is>
       </c>
       <c r="C80" s="47" t="n"/>
       <c r="D80" s="48" t="inlineStr">
         <is>
-          <t>171-161-045 24</t>
+          <t>077-644-645 06</t>
         </is>
       </c>
       <c r="E80" s="49" t="n"/>
@@ -7501,12 +7501,12 @@
       <c r="H80" s="49" t="n"/>
       <c r="I80" s="52" t="inlineStr">
         <is>
-          <t>Контролер 1 категории</t>
+          <t>Инженер 1 категории</t>
         </is>
       </c>
       <c r="J80" s="52" t="inlineStr">
         <is>
-          <t>Отдел технического контроля МШ</t>
+          <t>Отдел технического контроля М</t>
         </is>
       </c>
       <c r="K80" s="53" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="J81" s="52" t="inlineStr">
         <is>
-          <t>Отдел транспортного обеспечения МШ</t>
+          <t>Отдел транспортного обеспечения</t>
         </is>
       </c>
       <c r="K81" s="53" t="n"/>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="J82" s="52" t="inlineStr">
         <is>
-          <t>Отдел транспортного обеспечения МШ</t>
+          <t>Отдел транспортного обеспечения</t>
         </is>
       </c>
       <c r="K82" s="53" t="n"/>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="J83" s="52" t="inlineStr">
         <is>
-          <t>Отдел транспортного обеспечения МШ</t>
+          <t>Отдел транспортного обеспечения</t>
         </is>
       </c>
       <c r="K83" s="53" t="n"/>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="J84" s="52" t="inlineStr">
         <is>
-          <t>Отдел транспортного обеспечения МШ</t>
+          <t>Отдел транспортного обеспечения</t>
         </is>
       </c>
       <c r="K84" s="53" t="n"/>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="J85" s="52" t="inlineStr">
         <is>
-          <t>Отдел транспортного обеспечения МШ</t>
+          <t>Отдел транспортного обеспечения</t>
         </is>
       </c>
       <c r="K85" s="53" t="n"/>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="J86" s="52" t="inlineStr">
         <is>
-          <t>Отдел транспортного обеспечения МШ</t>
+          <t>Отдел транспортного обеспечения</t>
         </is>
       </c>
       <c r="K86" s="53" t="n"/>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="J87" s="52" t="inlineStr">
         <is>
-          <t>Отдел транспортного обеспечения МШ</t>
+          <t>Отдел транспортного обеспечения</t>
         </is>
       </c>
       <c r="K87" s="53" t="n"/>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="J88" s="52" t="inlineStr">
         <is>
-          <t>Отдел транспортного обеспечения МШ</t>
+          <t>Отдел транспортного обеспечения</t>
         </is>
       </c>
       <c r="K88" s="53" t="n"/>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="J89" s="52" t="inlineStr">
         <is>
-          <t>Отдел транспортного обеспечения МШ</t>
+          <t>Отдел транспортного обеспечения</t>
         </is>
       </c>
       <c r="K89" s="53" t="n"/>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="J90" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел МШ</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="K90" s="53" t="n"/>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="J91" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел МШ</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="K91" s="53" t="n"/>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="J92" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел МШ</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="K92" s="53" t="n"/>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="J93" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел МШ</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="K93" s="53" t="n"/>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="J94" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел МШ</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="K94" s="53" t="n"/>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="J95" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел МШ</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="K95" s="53" t="n"/>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="J96" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел МШ</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="K96" s="53" t="n"/>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="J97" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел МШ</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="K97" s="53" t="n"/>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="J98" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел МШ</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="K98" s="53" t="n"/>
@@ -9174,7 +9174,7 @@
       </c>
       <c r="J99" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел МШ</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="K99" s="53" t="n"/>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="J100" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел МШ</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="K100" s="53" t="n"/>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="J101" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел МШ</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="K101" s="53" t="n"/>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="J102" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел МШ</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="K102" s="53" t="n"/>
@@ -9481,36 +9481,36 @@
     <row r="103" ht="12.75" customHeight="1">
       <c r="A103" s="45" t="inlineStr">
         <is>
-          <t>Петина Ирина Викторовна</t>
+          <t>Агалиев Рафаэл Рашидович</t>
         </is>
       </c>
       <c r="B103" s="46" t="inlineStr">
         <is>
-          <t>14.10.1990</t>
+          <t>22.03.1996</t>
         </is>
       </c>
       <c r="C103" s="47" t="n"/>
       <c r="D103" s="48" t="inlineStr">
         <is>
-          <t>138-565-749 05</t>
+          <t>184-005-664 54</t>
         </is>
       </c>
       <c r="E103" s="49" t="n"/>
       <c r="F103" s="50" t="n"/>
       <c r="G103" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.6.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1</t>
         </is>
       </c>
       <c r="H103" s="49" t="n"/>
       <c r="I103" s="52" t="inlineStr">
         <is>
-          <t>Оператор склада</t>
+          <t>Кладовщик-комплектовщик</t>
         </is>
       </c>
       <c r="J103" s="52" t="inlineStr">
         <is>
-          <t>Склад (МШ н/д)</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K103" s="53" t="n"/>
@@ -9522,8 +9522,16 @@
       <c r="Q103" s="48" t="n"/>
       <c r="R103" s="49" t="n"/>
       <c r="S103" s="49" t="n"/>
-      <c r="T103" s="49" t="n"/>
-      <c r="U103" s="55" t="n"/>
+      <c r="T103" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U103" s="55" t="inlineStr">
+        <is>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+        </is>
+      </c>
       <c r="V103" s="49" t="n"/>
       <c r="W103" s="49" t="n"/>
       <c r="X103" s="48" t="n"/>
@@ -9565,36 +9573,36 @@
     <row r="104" ht="12.75" customHeight="1">
       <c r="A104" s="45" t="inlineStr">
         <is>
-          <t>Агалиев Рафаэл Рашидович</t>
+          <t>Балкивская Людмила Алексеевна</t>
         </is>
       </c>
       <c r="B104" s="46" t="inlineStr">
         <is>
-          <t>22.03.1996</t>
+          <t>05.01.1960</t>
         </is>
       </c>
       <c r="C104" s="47" t="n"/>
       <c r="D104" s="48" t="inlineStr">
         <is>
-          <t>184-005-664 54</t>
+          <t>018-959-483 08</t>
         </is>
       </c>
       <c r="E104" s="49" t="n"/>
       <c r="F104" s="50" t="n"/>
       <c r="G104" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1</t>
+          <t>п.4.4, п.5.1, п.6.2</t>
         </is>
       </c>
       <c r="H104" s="49" t="n"/>
       <c r="I104" s="52" t="inlineStr">
         <is>
-          <t>Кладовщик-комплектовщик</t>
+          <t>Старший кладовщик</t>
         </is>
       </c>
       <c r="J104" s="52" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K104" s="53" t="n"/>
@@ -9606,16 +9614,8 @@
       <c r="Q104" s="48" t="n"/>
       <c r="R104" s="49" t="n"/>
       <c r="S104" s="49" t="n"/>
-      <c r="T104" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U104" s="55" t="inlineStr">
-        <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
-        </is>
-      </c>
+      <c r="T104" s="49" t="n"/>
+      <c r="U104" s="55" t="n"/>
       <c r="V104" s="49" t="n"/>
       <c r="W104" s="49" t="n"/>
       <c r="X104" s="48" t="n"/>
@@ -9657,36 +9657,36 @@
     <row r="105" ht="12.75" customHeight="1">
       <c r="A105" s="45" t="inlineStr">
         <is>
-          <t>Балкивская Людмила Алексеевна</t>
+          <t>Богатырев Николай Владимирович</t>
         </is>
       </c>
       <c r="B105" s="46" t="inlineStr">
         <is>
-          <t>05.01.1960</t>
+          <t>21.05.1976</t>
         </is>
       </c>
       <c r="C105" s="47" t="n"/>
       <c r="D105" s="48" t="inlineStr">
         <is>
-          <t>018-959-483 08</t>
+          <t>008-865-339 77</t>
         </is>
       </c>
       <c r="E105" s="49" t="n"/>
       <c r="F105" s="50" t="n"/>
       <c r="G105" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.6.2</t>
+          <t>п.1.49.2, п.1.49.14, п.1.50, п.4.3.1, п.4.4, п.6.2</t>
         </is>
       </c>
       <c r="H105" s="49" t="n"/>
       <c r="I105" s="52" t="inlineStr">
         <is>
-          <t>Старший кладовщик</t>
+          <t>Лаборант</t>
         </is>
       </c>
       <c r="J105" s="52" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K105" s="53" t="n"/>
@@ -9741,36 +9741,36 @@
     <row r="106" ht="12.75" customHeight="1">
       <c r="A106" s="45" t="inlineStr">
         <is>
-          <t>Богатырев Николай Владимирович</t>
+          <t>Густов Александр Витальевич</t>
         </is>
       </c>
       <c r="B106" s="46" t="inlineStr">
         <is>
-          <t>21.05.1976</t>
+          <t>03.01.1985</t>
         </is>
       </c>
       <c r="C106" s="47" t="n"/>
       <c r="D106" s="48" t="inlineStr">
         <is>
-          <t>008-865-339 77</t>
+          <t>134-854-450 71</t>
         </is>
       </c>
       <c r="E106" s="49" t="n"/>
       <c r="F106" s="50" t="n"/>
       <c r="G106" s="51" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.1.50, п.4.3.1, п.4.4, п.6.2</t>
+          <t>п.4.4, п.5.1, п.6.2</t>
         </is>
       </c>
       <c r="H106" s="49" t="n"/>
       <c r="I106" s="52" t="inlineStr">
         <is>
-          <t>Лаборант</t>
+          <t>Кладовщик</t>
         </is>
       </c>
       <c r="J106" s="52" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K106" s="53" t="n"/>
@@ -9825,18 +9825,18 @@
     <row r="107" ht="12.75" customHeight="1">
       <c r="A107" s="45" t="inlineStr">
         <is>
-          <t>Густов Александр Витальевич</t>
+          <t>Дягин Александр Александрович</t>
         </is>
       </c>
       <c r="B107" s="46" t="inlineStr">
         <is>
-          <t>03.01.1985</t>
+          <t>21.11.1996</t>
         </is>
       </c>
       <c r="C107" s="47" t="n"/>
       <c r="D107" s="48" t="inlineStr">
         <is>
-          <t>134-854-450 71</t>
+          <t>176-939-404 26</t>
         </is>
       </c>
       <c r="E107" s="49" t="n"/>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="J107" s="52" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K107" s="53" t="n"/>
@@ -9909,36 +9909,36 @@
     <row r="108" ht="12.75" customHeight="1">
       <c r="A108" s="45" t="inlineStr">
         <is>
-          <t>Дягин Александр Александрович</t>
+          <t>Каменев Дмитрий Викторович</t>
         </is>
       </c>
       <c r="B108" s="46" t="inlineStr">
         <is>
-          <t>21.11.1996</t>
+          <t>29.10.1975</t>
         </is>
       </c>
       <c r="C108" s="47" t="n"/>
       <c r="D108" s="48" t="inlineStr">
         <is>
-          <t>176-939-404 26</t>
+          <t>154-183-856 74</t>
         </is>
       </c>
       <c r="E108" s="49" t="n"/>
       <c r="F108" s="50" t="n"/>
       <c r="G108" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.6.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1</t>
         </is>
       </c>
       <c r="H108" s="49" t="n"/>
       <c r="I108" s="52" t="inlineStr">
         <is>
-          <t>Кладовщик</t>
+          <t>Кладовщик-комплектовщик</t>
         </is>
       </c>
       <c r="J108" s="52" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K108" s="53" t="n"/>
@@ -9950,8 +9950,16 @@
       <c r="Q108" s="48" t="n"/>
       <c r="R108" s="49" t="n"/>
       <c r="S108" s="49" t="n"/>
-      <c r="T108" s="49" t="n"/>
-      <c r="U108" s="55" t="n"/>
+      <c r="T108" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U108" s="55" t="inlineStr">
+        <is>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+        </is>
+      </c>
       <c r="V108" s="49" t="n"/>
       <c r="W108" s="49" t="n"/>
       <c r="X108" s="48" t="n"/>
@@ -9993,36 +10001,36 @@
     <row r="109" ht="12.75" customHeight="1">
       <c r="A109" s="45" t="inlineStr">
         <is>
-          <t>Каменев Дмитрий Викторович</t>
+          <t>Карпачева Татьяна Владимировна</t>
         </is>
       </c>
       <c r="B109" s="46" t="inlineStr">
         <is>
-          <t>29.10.1975</t>
+          <t>17.01.1985</t>
         </is>
       </c>
       <c r="C109" s="47" t="n"/>
       <c r="D109" s="48" t="inlineStr">
         <is>
-          <t>154-183-856 74</t>
+          <t>104-597-939 81</t>
         </is>
       </c>
       <c r="E109" s="49" t="n"/>
       <c r="F109" s="50" t="n"/>
       <c r="G109" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1</t>
+          <t>п.4.4, п.5.1, п.6.2</t>
         </is>
       </c>
       <c r="H109" s="49" t="n"/>
       <c r="I109" s="52" t="inlineStr">
         <is>
-          <t>Кладовщик-комплектовщик</t>
+          <t>Старший кладовщик</t>
         </is>
       </c>
       <c r="J109" s="52" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K109" s="53" t="n"/>
@@ -10034,16 +10042,8 @@
       <c r="Q109" s="48" t="n"/>
       <c r="R109" s="49" t="n"/>
       <c r="S109" s="49" t="n"/>
-      <c r="T109" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U109" s="55" t="inlineStr">
-        <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
-        </is>
-      </c>
+      <c r="T109" s="49" t="n"/>
+      <c r="U109" s="55" t="n"/>
       <c r="V109" s="49" t="n"/>
       <c r="W109" s="49" t="n"/>
       <c r="X109" s="48" t="n"/>
@@ -10085,18 +10085,18 @@
     <row r="110" ht="12.75" customHeight="1">
       <c r="A110" s="45" t="inlineStr">
         <is>
-          <t>Карпачева Татьяна Владимировна</t>
+          <t>Кирбенева Татьяна Александровна</t>
         </is>
       </c>
       <c r="B110" s="46" t="inlineStr">
         <is>
-          <t>17.01.1985</t>
+          <t>22.06.1987</t>
         </is>
       </c>
       <c r="C110" s="47" t="n"/>
       <c r="D110" s="48" t="inlineStr">
         <is>
-          <t>104-597-939 81</t>
+          <t>118-108-755 46</t>
         </is>
       </c>
       <c r="E110" s="49" t="n"/>
@@ -10109,12 +10109,12 @@
       <c r="H110" s="49" t="n"/>
       <c r="I110" s="52" t="inlineStr">
         <is>
-          <t>Старший кладовщик</t>
+          <t>Оператор склада</t>
         </is>
       </c>
       <c r="J110" s="52" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K110" s="53" t="n"/>
@@ -10169,36 +10169,36 @@
     <row r="111" ht="12.75" customHeight="1">
       <c r="A111" s="45" t="inlineStr">
         <is>
-          <t>Кирбенева Татьяна Александровна</t>
+          <t>Ласкавый Андрей Викторович</t>
         </is>
       </c>
       <c r="B111" s="46" t="inlineStr">
         <is>
-          <t>22.06.1987</t>
+          <t>03.01.1980</t>
         </is>
       </c>
       <c r="C111" s="47" t="n"/>
       <c r="D111" s="48" t="inlineStr">
         <is>
-          <t>118-108-755 46</t>
+          <t>171-022-718 20</t>
         </is>
       </c>
       <c r="E111" s="49" t="n"/>
       <c r="F111" s="50" t="n"/>
       <c r="G111" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.6.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1</t>
         </is>
       </c>
       <c r="H111" s="49" t="n"/>
       <c r="I111" s="52" t="inlineStr">
         <is>
-          <t>Оператор склада</t>
+          <t>Кладовщик-комплектовщик</t>
         </is>
       </c>
       <c r="J111" s="52" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K111" s="53" t="n"/>
@@ -10210,8 +10210,16 @@
       <c r="Q111" s="48" t="n"/>
       <c r="R111" s="49" t="n"/>
       <c r="S111" s="49" t="n"/>
-      <c r="T111" s="49" t="n"/>
-      <c r="U111" s="55" t="n"/>
+      <c r="T111" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U111" s="55" t="inlineStr">
+        <is>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+        </is>
+      </c>
       <c r="V111" s="49" t="n"/>
       <c r="W111" s="49" t="n"/>
       <c r="X111" s="48" t="n"/>
@@ -10253,36 +10261,36 @@
     <row r="112" ht="12.75" customHeight="1">
       <c r="A112" s="45" t="inlineStr">
         <is>
-          <t>Ласкавый Андрей Викторович</t>
+          <t>Лягинова Анастасия Витальевна</t>
         </is>
       </c>
       <c r="B112" s="46" t="inlineStr">
         <is>
-          <t>03.01.1980</t>
+          <t>31.01.1992</t>
         </is>
       </c>
       <c r="C112" s="47" t="n"/>
       <c r="D112" s="48" t="inlineStr">
         <is>
-          <t>171-022-718 20</t>
+          <t>133-655-426 56</t>
         </is>
       </c>
       <c r="E112" s="49" t="n"/>
       <c r="F112" s="50" t="n"/>
       <c r="G112" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1</t>
+          <t>п.4.4, п.5.1, п.6.2</t>
         </is>
       </c>
       <c r="H112" s="49" t="n"/>
       <c r="I112" s="52" t="inlineStr">
         <is>
-          <t>Кладовщик-комплектовщик</t>
+          <t>Оператор склада</t>
         </is>
       </c>
       <c r="J112" s="52" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K112" s="53" t="n"/>
@@ -10294,16 +10302,8 @@
       <c r="Q112" s="48" t="n"/>
       <c r="R112" s="49" t="n"/>
       <c r="S112" s="49" t="n"/>
-      <c r="T112" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U112" s="55" t="inlineStr">
-        <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
-        </is>
-      </c>
+      <c r="T112" s="49" t="n"/>
+      <c r="U112" s="55" t="n"/>
       <c r="V112" s="49" t="n"/>
       <c r="W112" s="49" t="n"/>
       <c r="X112" s="48" t="n"/>
@@ -10345,36 +10345,36 @@
     <row r="113" ht="12.75" customHeight="1">
       <c r="A113" s="45" t="inlineStr">
         <is>
-          <t>Лягинова Анастасия Витальевна</t>
+          <t>Моряков Константин Викторович</t>
         </is>
       </c>
       <c r="B113" s="46" t="inlineStr">
         <is>
-          <t>31.01.1992</t>
+          <t>06.04.1971</t>
         </is>
       </c>
       <c r="C113" s="47" t="n"/>
       <c r="D113" s="48" t="inlineStr">
         <is>
-          <t>133-655-426 56</t>
+          <t>116-163-416 26</t>
         </is>
       </c>
       <c r="E113" s="49" t="n"/>
       <c r="F113" s="50" t="n"/>
       <c r="G113" s="51" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.6.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1</t>
         </is>
       </c>
       <c r="H113" s="49" t="n"/>
       <c r="I113" s="52" t="inlineStr">
         <is>
-          <t>Оператор склада</t>
+          <t>Кладовщик-комплектовщик</t>
         </is>
       </c>
       <c r="J113" s="52" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K113" s="53" t="n"/>
@@ -10386,8 +10386,16 @@
       <c r="Q113" s="48" t="n"/>
       <c r="R113" s="49" t="n"/>
       <c r="S113" s="49" t="n"/>
-      <c r="T113" s="49" t="n"/>
-      <c r="U113" s="55" t="n"/>
+      <c r="T113" s="49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U113" s="55" t="inlineStr">
+        <is>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+        </is>
+      </c>
       <c r="V113" s="49" t="n"/>
       <c r="W113" s="49" t="n"/>
       <c r="X113" s="48" t="n"/>
@@ -10429,36 +10437,36 @@
     <row r="114" ht="12.75" customHeight="1">
       <c r="A114" s="45" t="inlineStr">
         <is>
-          <t>Моряков Константин Викторович</t>
+          <t>Нестеров Аркадий Николаевич</t>
         </is>
       </c>
       <c r="B114" s="46" t="inlineStr">
         <is>
-          <t>06.04.1971</t>
+          <t>07.04.1987</t>
         </is>
       </c>
       <c r="C114" s="47" t="n"/>
       <c r="D114" s="48" t="inlineStr">
         <is>
-          <t>116-163-416 26</t>
+          <t>168-793-135 24</t>
         </is>
       </c>
       <c r="E114" s="49" t="n"/>
       <c r="F114" s="50" t="n"/>
       <c r="G114" s="51" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1</t>
+          <t>п.4.4, п.5.1, п.6.2</t>
         </is>
       </c>
       <c r="H114" s="49" t="n"/>
       <c r="I114" s="52" t="inlineStr">
         <is>
-          <t>Кладовщик-комплектовщик</t>
+          <t>Старший кладовщик</t>
         </is>
       </c>
       <c r="J114" s="52" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K114" s="53" t="n"/>
@@ -10470,16 +10478,8 @@
       <c r="Q114" s="48" t="n"/>
       <c r="R114" s="49" t="n"/>
       <c r="S114" s="49" t="n"/>
-      <c r="T114" s="49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U114" s="55" t="inlineStr">
-        <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
-        </is>
-      </c>
+      <c r="T114" s="49" t="n"/>
+      <c r="U114" s="55" t="n"/>
       <c r="V114" s="49" t="n"/>
       <c r="W114" s="49" t="n"/>
       <c r="X114" s="48" t="n"/>
@@ -10521,18 +10521,18 @@
     <row r="115" ht="12.75" customHeight="1">
       <c r="A115" s="45" t="inlineStr">
         <is>
-          <t>Нестеров Аркадий Николаевич</t>
+          <t>Ноженко Екатерина Сергеевна</t>
         </is>
       </c>
       <c r="B115" s="46" t="inlineStr">
         <is>
-          <t>07.04.1987</t>
+          <t>09.04.1981</t>
         </is>
       </c>
       <c r="C115" s="47" t="n"/>
       <c r="D115" s="48" t="inlineStr">
         <is>
-          <t>168-793-135 24</t>
+          <t>075-854-992 25</t>
         </is>
       </c>
       <c r="E115" s="49" t="n"/>
@@ -10545,12 +10545,12 @@
       <c r="H115" s="49" t="n"/>
       <c r="I115" s="52" t="inlineStr">
         <is>
-          <t>Старший кладовщик</t>
+          <t>Кладовщик</t>
         </is>
       </c>
       <c r="J115" s="52" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K115" s="53" t="n"/>
@@ -10605,18 +10605,18 @@
     <row r="116" ht="12.75" customHeight="1">
       <c r="A116" s="45" t="inlineStr">
         <is>
-          <t>Ноженко Екатерина Сергеевна</t>
+          <t>Петина Ирина Викторовна</t>
         </is>
       </c>
       <c r="B116" s="46" t="inlineStr">
         <is>
-          <t>09.04.1981</t>
+          <t>14.10.1990</t>
         </is>
       </c>
       <c r="C116" s="47" t="n"/>
       <c r="D116" s="48" t="inlineStr">
         <is>
-          <t>075-854-992 25</t>
+          <t>138-565-749 05</t>
         </is>
       </c>
       <c r="E116" s="49" t="n"/>
@@ -10629,12 +10629,12 @@
       <c r="H116" s="49" t="n"/>
       <c r="I116" s="52" t="inlineStr">
         <is>
-          <t>Кладовщик</t>
+          <t>Оператор склада</t>
         </is>
       </c>
       <c r="J116" s="52" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K116" s="53" t="n"/>
@@ -10718,7 +10718,7 @@
       </c>
       <c r="J117" s="52" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K117" s="53" t="n"/>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="J118" s="52" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K118" s="53" t="n"/>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="J119" s="52" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K119" s="53" t="n"/>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="J120" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="K120" s="53" t="n"/>
@@ -11062,7 +11062,7 @@
       </c>
       <c r="J121" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="K121" s="53" t="n"/>
@@ -11146,7 +11146,7 @@
       </c>
       <c r="J122" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="K122" s="53" t="n"/>
@@ -11230,7 +11230,7 @@
       </c>
       <c r="J123" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="K123" s="53" t="n"/>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="J124" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="K124" s="53" t="n"/>
@@ -11398,7 +11398,7 @@
       </c>
       <c r="J125" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="K125" s="53" t="n"/>
@@ -11482,7 +11482,7 @@
       </c>
       <c r="J126" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="K126" s="53" t="n"/>
@@ -11566,7 +11566,7 @@
       </c>
       <c r="J127" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="K127" s="53" t="n"/>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="J128" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="K128" s="53" t="n"/>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="J129" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="K129" s="53" t="n"/>
@@ -11818,7 +11818,7 @@
       </c>
       <c r="J130" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="K130" s="53" t="n"/>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="J131" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="K131" s="53" t="n"/>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="J132" s="52" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="K132" s="53" t="n"/>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="J133" s="52" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="K133" s="53" t="n"/>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="J134" s="52" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="K134" s="53" t="n"/>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="J135" s="52" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="K135" s="53" t="n"/>
@@ -12346,7 +12346,7 @@
       </c>
       <c r="J136" s="52" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="K136" s="53" t="n"/>
@@ -12430,7 +12430,7 @@
       </c>
       <c r="J137" s="52" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="K137" s="53" t="n"/>
@@ -12522,7 +12522,7 @@
       </c>
       <c r="J138" s="52" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="K138" s="53" t="n"/>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="J139" s="52" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="K139" s="53" t="n"/>
@@ -12698,7 +12698,7 @@
       </c>
       <c r="J140" s="52" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="K140" s="53" t="n"/>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="J141" s="52" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="K141" s="53" t="n"/>
@@ -12866,7 +12866,7 @@
       </c>
       <c r="J142" s="52" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="K142" s="53" t="n"/>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="J143" s="52" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="K143" s="53" t="n"/>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="J144" s="52" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="K144" s="53" t="n"/>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="J145" s="52" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="K145" s="53" t="n"/>
@@ -13202,7 +13202,7 @@
       </c>
       <c r="J146" s="52" t="inlineStr">
         <is>
-          <t>Участок РЭО МШ</t>
+          <t>Участок РЭО</t>
         </is>
       </c>
       <c r="K146" s="53" t="n"/>
@@ -13294,7 +13294,7 @@
       </c>
       <c r="J147" s="52" t="inlineStr">
         <is>
-          <t>Участок РЭО МШ</t>
+          <t>Участок РЭО</t>
         </is>
       </c>
       <c r="K147" s="53" t="n"/>
@@ -13386,7 +13386,7 @@
       </c>
       <c r="J148" s="52" t="inlineStr">
         <is>
-          <t>Участок РЭО МШ</t>
+          <t>Участок РЭО</t>
         </is>
       </c>
       <c r="K148" s="53" t="n"/>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="J149" s="52" t="inlineStr">
         <is>
-          <t>Участок РЭО МШ</t>
+          <t>Участок РЭО</t>
         </is>
       </c>
       <c r="K149" s="53" t="n"/>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="J150" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="K150" s="53" t="n"/>
@@ -13654,7 +13654,7 @@
       </c>
       <c r="J151" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="K151" s="53" t="n"/>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="J152" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="K152" s="53" t="n"/>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="J153" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="K153" s="53" t="n"/>
@@ -13906,7 +13906,7 @@
       </c>
       <c r="J154" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="K154" s="53" t="n"/>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="J155" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="K155" s="53" t="n"/>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="J156" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="K156" s="53" t="n"/>
@@ -14158,7 +14158,7 @@
       </c>
       <c r="J157" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="K157" s="53" t="n"/>
@@ -14242,7 +14242,7 @@
       </c>
       <c r="J158" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="K158" s="53" t="n"/>
@@ -14326,7 +14326,7 @@
       </c>
       <c r="J159" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="K159" s="53" t="n"/>
@@ -14410,7 +14410,7 @@
       </c>
       <c r="J160" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="K160" s="53" t="n"/>
@@ -14494,7 +14494,7 @@
       </c>
       <c r="J161" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="K161" s="53" t="n"/>
@@ -14578,7 +14578,7 @@
       </c>
       <c r="J162" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="K162" s="53" t="n"/>
@@ -14662,7 +14662,7 @@
       </c>
       <c r="J163" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="K163" s="53" t="n"/>
@@ -14746,7 +14746,7 @@
       </c>
       <c r="J164" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="K164" s="53" t="n"/>
@@ -14830,7 +14830,7 @@
       </c>
       <c r="J165" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="K165" s="53" t="n"/>
@@ -14914,7 +14914,7 @@
       </c>
       <c r="J166" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="K166" s="53" t="n"/>
@@ -14998,7 +14998,7 @@
       </c>
       <c r="J167" s="52" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="K167" s="53" t="n"/>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="J168" s="52" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел Р</t>
+          <t>Административно-хозяйственный отдел</t>
         </is>
       </c>
       <c r="K168" s="53" t="n"/>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="J169" s="52" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел Р</t>
+          <t>Административно-хозяйственный отдел</t>
         </is>
       </c>
       <c r="K169" s="53" t="n"/>
@@ -15250,7 +15250,7 @@
       </c>
       <c r="J170" s="52" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел Р</t>
+          <t>Административно-хозяйственный отдел</t>
         </is>
       </c>
       <c r="K170" s="53" t="n"/>
@@ -15334,7 +15334,7 @@
       </c>
       <c r="J171" s="52" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел Р</t>
+          <t>Административно-хозяйственный отдел</t>
         </is>
       </c>
       <c r="K171" s="53" t="n"/>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="J172" s="52" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K172" s="53" t="n"/>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="J173" s="52" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K173" s="53" t="n"/>
@@ -15586,7 +15586,7 @@
       </c>
       <c r="J174" s="52" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K174" s="53" t="n"/>
@@ -15670,7 +15670,7 @@
       </c>
       <c r="J175" s="52" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K175" s="53" t="n"/>
@@ -15754,7 +15754,7 @@
       </c>
       <c r="J176" s="52" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K176" s="53" t="n"/>
@@ -15838,7 +15838,7 @@
       </c>
       <c r="J177" s="52" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K177" s="53" t="n"/>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="J178" s="52" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K178" s="53" t="n"/>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="J179" s="52" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K179" s="53" t="n"/>
@@ -16090,7 +16090,7 @@
       </c>
       <c r="J180" s="52" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K180" s="53" t="n"/>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="J181" s="52" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K181" s="53" t="n"/>
@@ -16258,7 +16258,7 @@
       </c>
       <c r="J182" s="52" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K182" s="53" t="n"/>
@@ -16342,7 +16342,7 @@
       </c>
       <c r="J183" s="52" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K183" s="53" t="n"/>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="J184" s="52" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="K184" s="53" t="n"/>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="J185" s="52" t="inlineStr">
         <is>
-          <t>Отдел технического контроля Р</t>
+          <t>Отдел технического контроля</t>
         </is>
       </c>
       <c r="K185" s="53" t="n"/>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="J186" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел Р</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="K186" s="53" t="n"/>
@@ -16678,7 +16678,7 @@
       </c>
       <c r="J187" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел Р</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="K187" s="53" t="n"/>
@@ -16762,7 +16762,7 @@
       </c>
       <c r="J188" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел Р</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="K188" s="53" t="n"/>
@@ -16846,7 +16846,7 @@
       </c>
       <c r="J189" s="52" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел Р</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="K189" s="53" t="n"/>
@@ -16930,7 +16930,7 @@
       </c>
       <c r="J190" s="52" t="inlineStr">
         <is>
-          <t>Склад Р</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K190" s="53" t="n"/>
@@ -17014,7 +17014,7 @@
       </c>
       <c r="J191" s="52" t="inlineStr">
         <is>
-          <t>Склад Р</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K191" s="53" t="n"/>
@@ -17098,7 +17098,7 @@
       </c>
       <c r="J192" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок Р</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="K192" s="53" t="n"/>
@@ -17182,7 +17182,7 @@
       </c>
       <c r="J193" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок Р</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="K193" s="53" t="n"/>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="J194" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок Р</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="K194" s="53" t="n"/>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="J195" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок Р</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="K195" s="53" t="n"/>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="J196" s="52" t="inlineStr">
         <is>
-          <t>Слесарный участок Р</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="K196" s="53" t="n"/>
@@ -17518,7 +17518,7 @@
       </c>
       <c r="J197" s="52" t="inlineStr">
         <is>
-          <t>Участок сборки Р</t>
+          <t>Участок сборки</t>
         </is>
       </c>
       <c r="K197" s="53" t="n"/>
@@ -17602,7 +17602,7 @@
       </c>
       <c r="J198" s="52" t="inlineStr">
         <is>
-          <t>Участок сборки Р</t>
+          <t>Участок сборки</t>
         </is>
       </c>
       <c r="K198" s="53" t="n"/>
@@ -17686,7 +17686,7 @@
       </c>
       <c r="J199" s="52" t="inlineStr">
         <is>
-          <t>Участок сборки Р</t>
+          <t>Участок сборки</t>
         </is>
       </c>
       <c r="K199" s="53" t="n"/>
@@ -17770,7 +17770,7 @@
       </c>
       <c r="J200" s="52" t="inlineStr">
         <is>
-          <t>Участок сборки Р</t>
+          <t>Участок сборки</t>
         </is>
       </c>
       <c r="K200" s="53" t="n"/>
@@ -17854,7 +17854,7 @@
       </c>
       <c r="J201" s="52" t="inlineStr">
         <is>
-          <t>Участок сборки Р</t>
+          <t>Участок сборки</t>
         </is>
       </c>
       <c r="K201" s="53" t="n"/>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="J202" s="52" t="inlineStr">
         <is>
-          <t>Участок сборки Р</t>
+          <t>Участок сборки</t>
         </is>
       </c>
       <c r="K202" s="53" t="n"/>
@@ -18022,7 +18022,7 @@
       </c>
       <c r="J203" s="52" t="inlineStr">
         <is>
-          <t>Участок сборки Р</t>
+          <t>Участок сборки</t>
         </is>
       </c>
       <c r="K203" s="53" t="n"/>
@@ -18106,7 +18106,7 @@
       </c>
       <c r="J204" s="52" t="inlineStr">
         <is>
-          <t>Участок сборки Р</t>
+          <t>Участок сборки</t>
         </is>
       </c>
       <c r="K204" s="53" t="n"/>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="J205" s="52" t="inlineStr">
         <is>
-          <t>Участок сборки Р</t>
+          <t>Участок сборки</t>
         </is>
       </c>
       <c r="K205" s="53" t="n"/>
@@ -18274,7 +18274,7 @@
       </c>
       <c r="J206" s="52" t="inlineStr">
         <is>
-          <t>Участок сборки Р</t>
+          <t>Участок сборки</t>
         </is>
       </c>
       <c r="K206" s="53" t="n"/>
@@ -18358,7 +18358,7 @@
       </c>
       <c r="J207" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Швейный участок</t>
         </is>
       </c>
       <c r="K207" s="53" t="n"/>
@@ -18442,7 +18442,7 @@
       </c>
       <c r="J208" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Швейный участок</t>
         </is>
       </c>
       <c r="K208" s="53" t="n"/>
@@ -18526,7 +18526,7 @@
       </c>
       <c r="J209" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Швейный участок</t>
         </is>
       </c>
       <c r="K209" s="53" t="n"/>
@@ -18610,7 +18610,7 @@
       </c>
       <c r="J210" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Швейный участок</t>
         </is>
       </c>
       <c r="K210" s="53" t="n"/>
@@ -18694,7 +18694,7 @@
       </c>
       <c r="J211" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Швейный участок</t>
         </is>
       </c>
       <c r="K211" s="53" t="n"/>
@@ -18778,7 +18778,7 @@
       </c>
       <c r="J212" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Швейный участок</t>
         </is>
       </c>
       <c r="K212" s="53" t="n"/>
@@ -18862,7 +18862,7 @@
       </c>
       <c r="J213" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Швейный участок</t>
         </is>
       </c>
       <c r="K213" s="53" t="n"/>
@@ -18946,7 +18946,7 @@
       </c>
       <c r="J214" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Швейный участок</t>
         </is>
       </c>
       <c r="K214" s="53" t="n"/>
@@ -19030,7 +19030,7 @@
       </c>
       <c r="J215" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Швейный участок</t>
         </is>
       </c>
       <c r="K215" s="53" t="n"/>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="J216" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Швейный участок</t>
         </is>
       </c>
       <c r="K216" s="53" t="n"/>
@@ -19198,7 +19198,7 @@
       </c>
       <c r="J217" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Швейный участок</t>
         </is>
       </c>
       <c r="K217" s="53" t="n"/>
@@ -19282,7 +19282,7 @@
       </c>
       <c r="J218" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Швейный участок</t>
         </is>
       </c>
       <c r="K218" s="53" t="n"/>
@@ -19366,7 +19366,7 @@
       </c>
       <c r="J219" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Швейный участок</t>
         </is>
       </c>
       <c r="K219" s="53" t="n"/>
@@ -19450,7 +19450,7 @@
       </c>
       <c r="J220" s="52" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Швейный участок</t>
         </is>
       </c>
       <c r="K220" s="53" t="n"/>
@@ -19530,7 +19530,7 @@
       </c>
       <c r="J221" s="52" t="inlineStr">
         <is>
-          <t>Участок РЭО МШ</t>
+          <t>Участок РЭО</t>
         </is>
       </c>
       <c r="K221" s="53" t="n"/>
@@ -19618,7 +19618,7 @@
       </c>
       <c r="J222" s="52" t="inlineStr">
         <is>
-          <t>Склад Р</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K222" s="53" t="n"/>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="J223" s="52" t="inlineStr">
         <is>
-          <t>Склад Р</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K223" s="53" t="n"/>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="J224" s="52" t="inlineStr">
         <is>
-          <t>Склад Р</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="K224" s="53" t="n"/>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="J225" s="52" t="inlineStr">
         <is>
-          <t>Служба главного инженера Р</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="K225" s="53" t="n"/>

--- a/МО 19.10.2026/Шаблон ЛМК проф ОПО — Машково и Руднево (ред. 19.10.2026).xlsx
+++ b/МО 19.10.2026/Шаблон ЛМК проф ОПО — Машково и Руднево (ред. 19.10.2026).xlsx
@@ -7225,18 +7225,18 @@
     <row r="77" ht="12.75" customHeight="1">
       <c r="A77" s="45" t="inlineStr">
         <is>
-          <t>Райкова Ирина Алексеевна</t>
+          <t>Ермакова Наталья Васильевна</t>
         </is>
       </c>
       <c r="B77" s="46" t="inlineStr">
         <is>
-          <t>27.04.2001</t>
+          <t>15.03.1983</t>
         </is>
       </c>
       <c r="C77" s="47" t="n"/>
       <c r="D77" s="48" t="inlineStr">
         <is>
-          <t>171-161-045 24</t>
+          <t>084-319-031 57</t>
         </is>
       </c>
       <c r="E77" s="49" t="n"/>
@@ -7309,18 +7309,18 @@
     <row r="78" ht="12.75" customHeight="1">
       <c r="A78" s="45" t="inlineStr">
         <is>
-          <t>Ермакова Наталья Васильевна</t>
+          <t>Райкова Ирина Алексеевна</t>
         </is>
       </c>
       <c r="B78" s="46" t="inlineStr">
         <is>
-          <t>15.03.1983</t>
+          <t>27.04.2001</t>
         </is>
       </c>
       <c r="C78" s="47" t="n"/>
       <c r="D78" s="48" t="inlineStr">
         <is>
-          <t>084-319-031 57</t>
+          <t>171-161-045 24</t>
         </is>
       </c>
       <c r="E78" s="49" t="n"/>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="J78" s="52" t="inlineStr">
         <is>
-          <t>Отдел технического контроля М</t>
+          <t>Отдел технического контроля</t>
         </is>
       </c>
       <c r="K78" s="53" t="n"/>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="J79" s="52" t="inlineStr">
         <is>
-          <t>Отдел технического контроля М</t>
+          <t>Отдел технического контроля</t>
         </is>
       </c>
       <c r="K79" s="53" t="n"/>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="J80" s="52" t="inlineStr">
         <is>
-          <t>Отдел технического контроля М</t>
+          <t>Отдел технического контроля</t>
         </is>
       </c>
       <c r="K80" s="53" t="n"/>

--- a/МО 19.10.2026/Шаблон ЛМК проф ОПО — Машково и Руднево (ред. 19.10.2026).xlsx
+++ b/МО 19.10.2026/Шаблон ЛМК проф ОПО — Машково и Руднево (ред. 19.10.2026).xlsx
@@ -9529,7 +9529,7 @@
       </c>
       <c r="U103" s="55" t="inlineStr">
         <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+          <t>п.1 Прил.№2: управление транспортными средствами.</t>
         </is>
       </c>
       <c r="V103" s="49" t="n"/>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="U108" s="55" t="inlineStr">
         <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+          <t>п.1 Прил.№2: управление транспортными средствами.</t>
         </is>
       </c>
       <c r="V108" s="49" t="n"/>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="U111" s="55" t="inlineStr">
         <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+          <t>п.1 Прил.№2: управление транспортными средствами.</t>
         </is>
       </c>
       <c r="V111" s="49" t="n"/>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="U113" s="55" t="inlineStr">
         <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+          <t>п.1 Прил.№2: управление транспортными средствами.</t>
         </is>
       </c>
       <c r="V113" s="49" t="n"/>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="U119" s="55" t="inlineStr">
         <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+          <t>п.1 Прил.№2: управление транспортными средствами.</t>
         </is>
       </c>
       <c r="V119" s="49" t="n"/>
@@ -19637,7 +19637,7 @@
       </c>
       <c r="U222" s="55" t="inlineStr">
         <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+          <t>п.1 Прил.№2: управление транспортными средствами.</t>
         </is>
       </c>
       <c r="V222" s="49" t="n"/>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="U223" s="55" t="inlineStr">
         <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+          <t>п.1 Прил.№2: управление транспортными средствами.</t>
         </is>
       </c>
       <c r="V223" s="49" t="n"/>
@@ -19813,7 +19813,7 @@
       </c>
       <c r="U224" s="55" t="inlineStr">
         <is>
-          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
+          <t>п.1 Прил.№2: управление транспортными средствами.</t>
         </is>
       </c>
       <c r="V224" s="49" t="n"/>

--- a/МО 19.10.2026/Шаблон ЛМК проф ОПО — Машково и Руднево (ред. 19.10.2026).xlsx
+++ b/МО 19.10.2026/Шаблон ЛМК проф ОПО — Машково и Руднево (ред. 19.10.2026).xlsx
@@ -9529,7 +9529,7 @@
       </c>
       <c r="U103" s="55" t="inlineStr">
         <is>
-          <t>п.1 Прил.№2: управление транспортными средствами.</t>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
         </is>
       </c>
       <c r="V103" s="49" t="n"/>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="U108" s="55" t="inlineStr">
         <is>
-          <t>п.1 Прил.№2: управление транспортными средствами.</t>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
         </is>
       </c>
       <c r="V108" s="49" t="n"/>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="U111" s="55" t="inlineStr">
         <is>
-          <t>п.1 Прил.№2: управление транспортными средствами.</t>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
         </is>
       </c>
       <c r="V111" s="49" t="n"/>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="U113" s="55" t="inlineStr">
         <is>
-          <t>п.1 Прил.№2: управление транспортными средствами.</t>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
         </is>
       </c>
       <c r="V113" s="49" t="n"/>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="U119" s="55" t="inlineStr">
         <is>
-          <t>п.1 Прил.№2: управление транспортными средствами.</t>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
         </is>
       </c>
       <c r="V119" s="49" t="n"/>
@@ -19637,7 +19637,7 @@
       </c>
       <c r="U222" s="55" t="inlineStr">
         <is>
-          <t>п.1 Прил.№2: управление транспортными средствами.</t>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
         </is>
       </c>
       <c r="V222" s="49" t="n"/>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="U223" s="55" t="inlineStr">
         <is>
-          <t>п.1 Прил.№2: управление транспортными средствами.</t>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
         </is>
       </c>
       <c r="V223" s="49" t="n"/>
@@ -19813,7 +19813,7 @@
       </c>
       <c r="U224" s="55" t="inlineStr">
         <is>
-          <t>п.1 Прил.№2: управление транспортными средствами.</t>
+          <t>п.1 Прил.№2: управление транспортными средствами (п.18.1 приложения к Приказу №29н).</t>
         </is>
       </c>
       <c r="V224" s="49" t="n"/>
